--- a/docs/downloads/KetQuaGiaoDich_latest.xlsx
+++ b/docs/downloads/KetQuaGiaoDich_latest.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>+9.04%</t>
+          <t>+6.02%</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1810</v>
+        <v>1760</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>561600</v>
+        <v>1029600</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1.016496</v>
+        <v>1.812096</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
@@ -567,10 +567,10 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1.12</v>
+        <v>0.96</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>7.27</v>
+        <v>7.46</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>30</v>
@@ -585,17 +585,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>+13.89%</t>
+          <t>+5.56%</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>410</v>
+        <v>380</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>406600</v>
+        <v>656300</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.166706</v>
+        <v>0.249394</v>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
         <v>6.82</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>32.11</v>
+        <v>34.56</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>19</v>
@@ -621,17 +621,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>+4.04%</t>
+          <t>+3.03%</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>83300</v>
+        <v>87900</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.085799</v>
+        <v>0.089658</v>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
@@ -639,10 +639,10 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>28.62</v>
+        <v>28.83</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>12.78</v>
+        <v>12.88</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>148</v>
@@ -657,17 +657,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>+4.76%</t>
+          <t>-4.76%</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>19400</v>
+        <v>123000</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.004268</v>
+        <v>0.0246</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
@@ -675,10 +675,10 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>11.6</v>
+        <v>11.54</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>29.92</v>
+        <v>32.83</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>47</v>
@@ -700,10 +700,10 @@
         <v>420</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>182900</v>
+        <v>194300</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.076818</v>
+        <v>0.081606</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>16.54</v>
+        <v>16.8</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>15.67</v>
+        <v>15.64</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>113</v>
@@ -736,10 +736,10 @@
         <v>700</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>5600</v>
+        <v>6000</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.00392</v>
+        <v>0.0042</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -747,10 +747,10 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>4.08</v>
+        <v>4.31</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>18.8</v>
+        <v>18.76</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>28</v>
@@ -765,17 +765,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>+5%</t>
+          <t>+8.33%</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1260</v>
+        <v>1300</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>600</v>
+        <v>30000</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.0007560000000000001</v>
+        <v>0.039</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -783,10 +783,10 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>8.33</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>10.45</v>
+        <v>10.1</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>93</v>
@@ -801,17 +801,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>+8.82%</t>
+          <t>+7.84%</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1110</v>
+        <v>1100</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>243700</v>
+        <v>377400</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.270507</v>
+        <v>0.41514</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>7.19</v>
+        <v>7.36</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>11.86</v>
+        <v>11.94</v>
       </c>
       <c r="I9" s="2" t="n">
         <v>98</v>
@@ -835,19 +835,15 @@
           <t>CACB2606</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>+1.20%</t>
-        </is>
-      </c>
+      <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="n">
-        <v>840</v>
+        <v>830</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>252400</v>
+        <v>337500</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.212016</v>
+        <v>0.280125</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -855,10 +851,10 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>7.73</v>
+        <v>7.81</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>7.84</v>
+        <v>7.91</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>107</v>
@@ -873,17 +869,17 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>+5.85%</t>
+          <t>+4.68%</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1810</v>
+        <v>1790</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>135900</v>
+        <v>182000</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.245979</v>
+        <v>0.32578</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -891,10 +887,10 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>7.95</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>7.27</v>
+        <v>7.34</v>
       </c>
       <c r="I11" s="2" t="n">
         <v>131</v>
@@ -909,17 +905,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>+15.87%</t>
+          <t>+18.25%</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>1460</v>
+        <v>1490</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>22500</v>
+        <v>35500</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.03285</v>
+        <v>0.052895</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -927,10 +923,10 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>4.15</v>
+        <v>4.61</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>9.02</v>
+        <v>8.81</v>
       </c>
       <c r="I12" s="2" t="n">
         <v>63</v>
@@ -945,17 +941,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>+8.33%</t>
+          <t>+4.17%</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>47400</v>
+        <v>146800</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.012324</v>
+        <v>0.0367</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
@@ -963,10 +959,10 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>14.67</v>
+        <v>14.73</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>20.26</v>
+        <v>21.02</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>55</v>
@@ -979,19 +975,15 @@
           <t>CACB2610</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>+3.03%</t>
-        </is>
-      </c>
+      <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="n">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>106400</v>
+        <v>112600</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.036176</v>
+        <v>0.037158</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
@@ -999,10 +991,10 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>20.83</v>
+        <v>20.91</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>15.49</v>
+        <v>15.92</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>98</v>
@@ -1017,17 +1009,17 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>+11.40%</t>
+          <t>+2.63%</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>1270</v>
+        <v>1170</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>354200</v>
+        <v>554400</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.449834</v>
+        <v>0.648648</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1035,10 +1027,10 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.79</v>
+        <v>0.25</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>10.39</v>
+        <v>11.26</v>
       </c>
       <c r="I15" s="2" t="n">
         <v>16</v>
@@ -1053,17 +1045,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>+12.66%</t>
+          <t>+8.86%</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>890</v>
+        <v>860</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>32300</v>
+        <v>119700</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.028747</v>
+        <v>0.102942</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1074,7 +1066,7 @@
         <v>1.71</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>14.83</v>
+        <v>15.31</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>16</v>
@@ -1089,17 +1081,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>+16.33%</t>
+          <t>+6.12%</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>570</v>
+        <v>520</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>173000</v>
+        <v>252100</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.09861</v>
+        <v>0.131092</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1107,10 +1099,10 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>3.08</v>
+        <v>2.93</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>23.15</v>
+        <v>25.32</v>
       </c>
       <c r="I17" s="2" t="n">
         <v>16</v>
@@ -1123,15 +1115,19 @@
           <t>CACB2614</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>+21.47%</t>
+        </is>
+      </c>
       <c r="C18" s="2" t="n">
-        <v>1910</v>
+        <v>2320</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v/>
+        <v>283600</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v/>
+        <v>0.657952</v>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
@@ -1139,10 +1135,10 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>9.74</v>
+        <v>11.79</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>11.88</v>
+        <v>9.76</v>
       </c>
       <c r="I18" s="2" t="n">
         <v>90</v>
@@ -1157,17 +1153,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>+3.74%</t>
+          <t>+2.67%</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>1940</v>
+        <v>1920</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>177100</v>
+        <v>248300</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.343574</v>
+        <v>0.476736</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1175,10 +1171,10 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>13.57</v>
+        <v>13.64</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>5.85</v>
+        <v>5.9</v>
       </c>
       <c r="I19" s="2" t="n">
         <v>186</v>
@@ -1193,17 +1189,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>+6.25%</t>
+          <t>+7.81%</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>680</v>
+        <v>690</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>24100</v>
+        <v>33700</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.016388</v>
+        <v>0.023253</v>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
@@ -1211,10 +1207,10 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>12.51</v>
+        <v>12.89</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>11.13</v>
+        <v>10.94</v>
       </c>
       <c r="I20" s="2" t="n">
         <v>103</v>
@@ -1227,15 +1223,19 @@
           <t>CACB2617</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>+4.17%</t>
+        </is>
+      </c>
       <c r="C21" s="2" t="n">
-        <v>960</v>
+        <v>1000</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v/>
+        <v>30000</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v/>
+        <v>0.03</v>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>9.779999999999999</v>
+        <v>10.38</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>11.82</v>
+        <v>11.32</v>
       </c>
       <c r="I21" s="2" t="n">
         <v>103</v>
@@ -1259,15 +1259,19 @@
           <t>CACB2618</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>+6.56%</t>
+        </is>
+      </c>
       <c r="C22" s="2" t="n">
-        <v>1220</v>
+        <v>1300</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v/>
+        <v>30000</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v/>
+        <v>0.039</v>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
@@ -1275,10 +1279,10 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>14.27</v>
+        <v>15.23</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="I22" s="2" t="n">
         <v>167</v>
@@ -1296,10 +1300,10 @@
         <v>10</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>2e-06</v>
+        <v>3e-06</v>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
@@ -1307,10 +1311,10 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>75.06</v>
+        <v>76.67</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>275</v>
+        <v>272.5</v>
       </c>
       <c r="I23" s="2" t="n">
         <v>6</v>
@@ -1323,19 +1327,15 @@
           <t>CFPT2518</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>+50%</t>
-        </is>
-      </c>
+      <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>295600</v>
+        <v>590700</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.008867999999999999</v>
+        <v>0.011814</v>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>48.04</v>
+        <v>47.72</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>277.62</v>
+        <v>417.02</v>
       </c>
       <c r="I24" s="2" t="n">
         <v>30</v>
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>27.79</v>
+        <v>27.61</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>150.93</v>
+        <v>151.14</v>
       </c>
       <c r="I25" s="2" t="n">
         <v>19</v>
@@ -1404,10 +1404,10 @@
         <v>380</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>66600</v>
+        <v>88300</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.025308</v>
+        <v>0.033554</v>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>51.75</v>
+        <v>51.54</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>23.83</v>
+        <v>23.86</v>
       </c>
       <c r="I26" s="2" t="n">
         <v>148</v>
@@ -1436,10 +1436,10 @@
         <v>50</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>156000</v>
+        <v>168500</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0.0078</v>
+        <v>0.008425</v>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>41.62</v>
+        <v>41.43</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>120.74</v>
+        <v>120.91</v>
       </c>
       <c r="I27" s="2" t="n">
         <v>47</v>
@@ -1468,10 +1468,10 @@
         <v>200</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>22200</v>
+        <v>42900</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.00444</v>
+        <v>0.008580000000000001</v>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>49.63</v>
+        <v>49.42</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>30.19</v>
+        <v>30.23</v>
       </c>
       <c r="I28" s="2" t="n">
         <v>113</v>
@@ -1495,19 +1495,15 @@
           <t>CFPT2602</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>-33.33%</t>
-        </is>
-      </c>
+      <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>264400</v>
+        <v>885600</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.005288</v>
+        <v>0.026568</v>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
@@ -1515,10 +1511,10 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>37.85</v>
+        <v>37.8</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>363.44</v>
+        <v>242.63</v>
       </c>
       <c r="I29" s="2" t="n">
         <v>28</v>
@@ -1533,17 +1529,17 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>+40%</t>
+          <t>+66.67%</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.00021</v>
+        <v>0.0003</v>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
@@ -1551,10 +1547,10 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>43.22</v>
+        <v>43.57</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>34.61</v>
+        <v>29.12</v>
       </c>
       <c r="I30" s="2" t="n">
         <v>93</v>
@@ -1576,10 +1572,10 @@
         <v>270</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>1200</v>
+        <v>5200</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0.000324</v>
+        <v>0.001404</v>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
@@ -1587,10 +1583,10 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>35.79</v>
+        <v>35.6</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>26.92</v>
+        <v>26.96</v>
       </c>
       <c r="I31" s="2" t="n">
         <v>98</v>
@@ -1603,15 +1599,19 @@
           <t>CFPT2606</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>-25%</t>
+        </is>
+      </c>
       <c r="C32" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>50000</v>
+        <v>93700</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0.002</v>
+        <v>0.002811</v>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>40.88</v>
+        <v>40.54</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>181.72</v>
+        <v>242.63</v>
       </c>
       <c r="I32" s="2" t="n">
         <v>35</v>
@@ -1635,19 +1635,15 @@
           <t>CFPT2608</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>+50%</t>
-        </is>
-      </c>
+      <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>14400</v>
+        <v>141900</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>0.000864</v>
+        <v>0.005676</v>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
@@ -1655,10 +1651,10 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>32.49</v>
+        <v>32.16</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>242.29</v>
+        <v>363.94</v>
       </c>
       <c r="I33" s="2" t="n">
         <v>34</v>
@@ -1676,10 +1672,10 @@
         <v>250</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>5800</v>
+        <v>13800</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0.00145</v>
+        <v>0.00345</v>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
@@ -1687,10 +1683,10 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>41.01</v>
+        <v>40.82</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>18.17</v>
+        <v>18.2</v>
       </c>
       <c r="I34" s="2" t="n">
         <v>107</v>
@@ -1703,15 +1699,19 @@
           <t>CFPT2610</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>+2.50%</t>
+        </is>
+      </c>
       <c r="C35" s="2" t="n">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>76700</v>
+        <v>175600</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>0.03068</v>
+        <v>0.071996</v>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>23.54</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>15.14</v>
+        <v>14.79</v>
       </c>
       <c r="I35" s="2" t="n">
         <v>133</v>
@@ -1744,10 +1744,10 @@
         <v>610</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>2100</v>
+        <v>5300</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0.001281</v>
+        <v>0.003233</v>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>29.99</v>
+        <v>29.81</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>5.88</v>
+        <v>5.89</v>
       </c>
       <c r="I36" s="2" t="n">
         <v>171</v>
@@ -1780,10 +1780,10 @@
         <v>490</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>4700</v>
+        <v>9000</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>0.002303</v>
+        <v>0.00441</v>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
@@ -1791,10 +1791,10 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>23.11</v>
+        <v>22.94</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>6.36</v>
+        <v>6.37</v>
       </c>
       <c r="I37" s="2" t="n">
         <v>148</v>
@@ -1816,10 +1816,10 @@
         <v>420</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>56800</v>
+        <v>92000</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0.023856</v>
+        <v>0.03864</v>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
@@ -1827,10 +1827,10 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>16.04</v>
+        <v>15.88</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>17.07</v>
+        <v>17.1</v>
       </c>
       <c r="I38" s="2" t="n">
         <v>63</v>
@@ -1845,17 +1845,17 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>+4.41%</t>
+          <t>+2.94%</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>1400</v>
+        <v>45400</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0.0009940000000000001</v>
+        <v>0.03178</v>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
@@ -1863,10 +1863,10 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>21.48</v>
+        <v>21.17</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>10.1</v>
+        <v>10.26</v>
       </c>
       <c r="I39" s="2" t="n">
         <v>131</v>
@@ -1881,17 +1881,17 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>+0.95%</t>
+          <t>+2.86%</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>1060</v>
+        <v>1080</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>18900</v>
+        <v>30600</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0.020034</v>
+        <v>0.033048</v>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>17.76</v>
+        <v>17.87</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>6.86</v>
+        <v>6.74</v>
       </c>
       <c r="I40" s="2" t="n">
         <v>163</v>
@@ -1915,19 +1915,15 @@
           <t>CFPT2616</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>-2.17%</t>
-        </is>
-      </c>
+      <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>4.5e-05</v>
+        <v>9.2e-05</v>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
@@ -1935,10 +1931,10 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>25.04</v>
+        <v>25.09</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>9.960000000000001</v>
+        <v>9.76</v>
       </c>
       <c r="I41" s="2" t="n">
         <v>55</v>
@@ -1951,15 +1947,19 @@
           <t>CFPT2617</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>+6.52%</t>
+        </is>
+      </c>
       <c r="C42" s="2" t="n">
-        <v>460</v>
+        <v>490</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>4.6e-05</v>
+        <v>9.8e-05</v>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>29.76</v>
+        <v>30.25</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>9.74</v>
+        <v>9.16</v>
       </c>
       <c r="I42" s="2" t="n">
         <v>98</v>
@@ -1985,17 +1985,17 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>+7.96%</t>
+          <t>+3.54%</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>1220</v>
+        <v>1170</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>47100</v>
+        <v>83800</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.057462</v>
+        <v>0.09804599999999999</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>3.04</v>
+        <v>2.62</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>14.69</v>
+        <v>15.34</v>
       </c>
       <c r="I43" s="2" t="n">
         <v>16</v>
@@ -2021,28 +2021,28 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>+8.14%</t>
+          <t>-6.98%</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>930</v>
+        <v>800</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>6100</v>
+        <v>97400</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.005673</v>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>ATM</t>
+        <v>0.07792</v>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>ITM</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>4.21</v>
+        <v>3.34</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>19.27</v>
+        <v>22.44</v>
       </c>
       <c r="I44" s="2" t="n">
         <v>16</v>
@@ -2057,17 +2057,17 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>+7.81%</t>
+          <t>+3.13%</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>690</v>
+        <v>660</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>51800</v>
+        <v>64100</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>0.035742</v>
+        <v>0.042306</v>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
@@ -2075,10 +2075,10 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>5.66</v>
+        <v>5.35</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>25.98</v>
+        <v>27.2</v>
       </c>
       <c r="I45" s="2" t="n">
         <v>16</v>
@@ -2093,17 +2093,17 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>+5.44%</t>
+          <t>+2.04%</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>1550</v>
+        <v>1500</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>12800</v>
+        <v>18400</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>0.01984</v>
+        <v>0.0276</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>11.3</v>
+        <v>10.72</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>7.71</v>
+        <v>7.98</v>
       </c>
       <c r="I46" s="2" t="n">
         <v>90</v>
@@ -2147,10 +2147,10 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>16.15</v>
+        <v>15.99</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>6.36</v>
+        <v>6.37</v>
       </c>
       <c r="I47" s="2" t="n">
         <v>154</v>
@@ -2165,17 +2165,17 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>+4.71%</t>
+          <t>+3.53%</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>890</v>
+        <v>880</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>221500</v>
+        <v>507000</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>0.197135</v>
+        <v>0.44616</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>12.66</v>
+        <v>12.34</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>6.71</v>
+        <v>6.8</v>
       </c>
       <c r="I48" s="2" t="n">
         <v>100</v>
@@ -2201,17 +2201,17 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>+3.36%</t>
+          <t>+2.52%</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>1230</v>
+        <v>1220</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>148700</v>
+        <v>148800</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>0.182901</v>
+        <v>0.181536</v>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>27.98</v>
+        <v>27.63</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>4.86</v>
+        <v>4.9</v>
       </c>
       <c r="I49" s="2" t="n">
         <v>230</v>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>14.09</v>
+        <v>13.93</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>9.19</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="I50" s="2" t="n">
         <v>103</v>
@@ -2291,10 +2291,10 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>18.27</v>
+        <v>18.11</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>6.96</v>
+        <v>6.97</v>
       </c>
       <c r="I51" s="2" t="n">
         <v>167</v>
@@ -2309,28 +2309,28 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>-1.69%</t>
+          <t>+5.08%</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>580</v>
+        <v>620</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>30300</v>
+        <v>306000</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>0.017574</v>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>OTM</t>
+        <v>0.18972</v>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>ATM</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>6.29</v>
+        <v>5.45</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>19.86</v>
+        <v>18.79</v>
       </c>
       <c r="I52" s="2" t="n">
         <v>19</v>
@@ -2345,17 +2345,17 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>1750</v>
+        <v>1810</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>197000</v>
+        <v>352800</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>0.34475</v>
+        <v>0.638568</v>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
@@ -2363,10 +2363,10 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>22.81</v>
+        <v>21.96</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>6.58</v>
+        <v>6.44</v>
       </c>
       <c r="I53" s="2" t="n">
         <v>148</v>
@@ -2381,17 +2381,17 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>-6.67%</t>
+          <t>+2.22%</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>420</v>
+        <v>460</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>24500</v>
+        <v>26100</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>0.01029</v>
+        <v>0.012006</v>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
@@ -2399,10 +2399,10 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>9.789999999999999</v>
+        <v>9.02</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>21.15</v>
+        <v>19.53</v>
       </c>
       <c r="I54" s="2" t="n">
         <v>35</v>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>28.18</v>
+        <v>26.75</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>5.16</v>
+        <v>5.22</v>
       </c>
       <c r="I55" s="2" t="n">
         <v>193</v>
@@ -2449,17 +2449,17 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>+6.25%</t>
+          <t>+17.19%</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>680</v>
+        <v>750</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>100</v>
+        <v>56000</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>6.8e-05</v>
+        <v>0.042</v>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
@@ -2467,10 +2467,10 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>10.09</v>
+        <v>9.65</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>13.06</v>
+        <v>11.98</v>
       </c>
       <c r="I56" s="2" t="n">
         <v>63</v>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>15.35</v>
+        <v>14.06</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>9.06</v>
+        <v>9.17</v>
       </c>
       <c r="I57" s="2" t="n">
         <v>131</v>
@@ -2517,17 +2517,17 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>-12.12%</t>
+          <t>+9.09%</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>290</v>
+        <v>360</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>11900</v>
+        <v>15200</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>0.003451</v>
+        <v>0.005472</v>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
@@ -2535,10 +2535,10 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>18.01</v>
+        <v>17.99</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>18.38</v>
+        <v>14.97</v>
       </c>
       <c r="I58" s="2" t="n">
         <v>55</v>
@@ -2551,19 +2551,15 @@
           <t>CHDB2607</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>-13.16%</t>
-        </is>
-      </c>
+      <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="n">
-        <v>330</v>
+        <v>380</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>53800</v>
+        <v>60200</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>0.017754</v>
+        <v>0.022876</v>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
@@ -2571,10 +2567,10 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>29.98</v>
+        <v>30.01</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>10.09</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="I59" s="2" t="n">
         <v>98</v>
@@ -2587,15 +2583,19 @@
           <t>CHDB2608</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>+3.60%</t>
+        </is>
+      </c>
       <c r="C60" s="2" t="n">
-        <v>1390</v>
+        <v>1440</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>84500</v>
+        <v>424900</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>0.117455</v>
+        <v>0.611856</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
@@ -2603,10 +2603,10 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>10.17</v>
+        <v>9.68</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>4.79</v>
+        <v>4.68</v>
       </c>
       <c r="I60" s="2" t="n">
         <v>100</v>
@@ -2621,17 +2621,17 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>-2.02%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>1940</v>
+        <v>1990</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>2000</v>
+        <v>9000</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>0.00388</v>
+        <v>0.01791</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>27.8</v>
+        <v>27.12</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>3.43</v>
+        <v>3.39</v>
       </c>
       <c r="I61" s="2" t="n">
         <v>230</v>
@@ -2655,15 +2655,19 @@
           <t>CHDB2610</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>+3.80%</t>
+        </is>
+      </c>
       <c r="C62" s="2" t="n">
-        <v>790</v>
+        <v>820</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>294200</v>
+        <v>714000</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>0.232418</v>
+        <v>0.58548</v>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
@@ -2671,10 +2675,10 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>13.96</v>
+        <v>13.02</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>11.24</v>
+        <v>10.96</v>
       </c>
       <c r="I62" s="2" t="n">
         <v>103</v>
@@ -2689,28 +2693,28 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>+1.92%</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>1010</v>
+        <v>1060</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>600</v>
+        <v>42800</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>0.000606</v>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>OTM</t>
+        <v>0.045368</v>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>ATM</t>
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>12.68</v>
+        <v>11.99</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I63" s="2" t="n">
         <v>103</v>
@@ -2725,17 +2729,17 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>+2.50%</t>
+          <t>+4.38%</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>1640</v>
+        <v>1670</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>15300</v>
+        <v>135000</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>0.025092</v>
+        <v>0.22545</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
@@ -2743,10 +2747,10 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>8.56</v>
+        <v>8.77</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>9.07</v>
+        <v>8.9</v>
       </c>
       <c r="I64" s="2" t="n">
         <v>30</v>
@@ -2761,17 +2765,17 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>-28.57%</t>
+          <t>-14.29%</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D65" s="2" t="n">
-        <v>204300</v>
+        <v>440800</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>0.010215</v>
+        <v>0.026448</v>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
@@ -2779,10 +2783,10 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>21.97</v>
+        <v>22.05</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>247.59</v>
+        <v>206.33</v>
       </c>
       <c r="I65" s="2" t="n">
         <v>19</v>
@@ -2795,15 +2799,19 @@
           <t>CHPG2539</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>+1.25%</t>
+        </is>
+      </c>
       <c r="C66" s="2" t="n">
-        <v>800</v>
+        <v>810</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>427700</v>
+        <v>537500</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>0.34216</v>
+        <v>0.435375</v>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
@@ -2811,10 +2819,10 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>45</v>
+        <v>45.08</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>15.47</v>
+        <v>15.28</v>
       </c>
       <c r="I66" s="2" t="n">
         <v>148</v>
@@ -2836,10 +2844,10 @@
         <v>90</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>136200</v>
+        <v>146800</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>0.012258</v>
+        <v>0.013212</v>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
@@ -2863,15 +2871,19 @@
           <t>CHPG2541</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>-16.28%</t>
+        </is>
+      </c>
       <c r="C68" s="2" t="n">
-        <v>430</v>
+        <v>360</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>20500</v>
+        <v>32400</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>0.008815</v>
+        <v>0.011664</v>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
@@ -2879,10 +2891,10 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>40.23</v>
+        <v>39.1</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>14.39</v>
+        <v>17.19</v>
       </c>
       <c r="I68" s="2" t="n">
         <v>113</v>
@@ -2895,19 +2907,15 @@
           <t>CHPG2602</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>-22.22%</t>
-        </is>
-      </c>
+      <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>44400</v>
+        <v>363800</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>0.003108</v>
+        <v>0.032742</v>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
@@ -2915,10 +2923,10 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>18.26</v>
+        <v>18.58</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>88.43000000000001</v>
+        <v>68.78</v>
       </c>
       <c r="I69" s="2" t="n">
         <v>28</v>
@@ -2940,10 +2948,10 @@
         <v>340</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>50000</v>
+        <v>71000</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>0.017</v>
+        <v>0.02414</v>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
@@ -2976,10 +2984,10 @@
         <v>180</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>538700</v>
+        <v>948500</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>0.096966</v>
+        <v>0.17073</v>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
@@ -3012,10 +3020,10 @@
         <v>850</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>16300</v>
+        <v>17500</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>0.013855</v>
+        <v>0.014875</v>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
@@ -3039,15 +3047,19 @@
           <t>CHPG2606</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>+2.56%</t>
+        </is>
+      </c>
       <c r="C73" s="2" t="n">
-        <v>780</v>
+        <v>800</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>1200</v>
+        <v>11100</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>0.000936</v>
+        <v>0.008880000000000001</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -3055,10 +3067,10 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>14.46</v>
+        <v>14.71</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>10.58</v>
+        <v>10.32</v>
       </c>
       <c r="I73" s="2" t="n">
         <v>100</v>
@@ -3071,19 +3083,15 @@
           <t>CHPG2607</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>+4.17%</t>
-        </is>
-      </c>
+      <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>765700</v>
+        <v>887300</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>0.191425</v>
+        <v>0.212952</v>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
@@ -3091,10 +3099,10 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>15.11</v>
+        <v>15.03</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>49.52</v>
+        <v>51.58</v>
       </c>
       <c r="I74" s="2" t="n">
         <v>34</v>
@@ -3112,10 +3120,10 @@
         <v>740</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>1400</v>
+        <v>4100</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>0.001036</v>
+        <v>0.003034</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -3139,15 +3147,19 @@
           <t>CHPG2610</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>+75%</t>
+        </is>
+      </c>
       <c r="C76" s="2" t="n">
-        <v>480</v>
+        <v>840</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v/>
+        <v>600</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v/>
+        <v>0.000504</v>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
@@ -3155,10 +3167,10 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>26.9</v>
+        <v>32.72</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>12.9</v>
+        <v>7.37</v>
       </c>
       <c r="I76" s="2" t="n">
         <v>111</v>
@@ -3180,10 +3192,10 @@
         <v>20</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>6300</v>
+        <v>56400</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>0.000126</v>
+        <v>0.001128</v>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
@@ -3207,15 +3219,19 @@
           <t>CHPG2613</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>+2.17%</t>
+        </is>
+      </c>
       <c r="C78" s="2" t="n">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>4200</v>
+        <v>24300</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>0.001932</v>
+        <v>0.011421</v>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
@@ -3223,10 +3239,10 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>30.45</v>
+        <v>30.65</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>10.77</v>
+        <v>10.54</v>
       </c>
       <c r="I78" s="2" t="n">
         <v>148</v>
@@ -3241,17 +3257,17 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>-5.26%</t>
+          <t>-15.79%</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>170700</v>
+        <v>389600</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>0.030726</v>
+        <v>0.062336</v>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
@@ -3259,10 +3275,10 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>18.02</v>
+        <v>17.69</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>34.39</v>
+        <v>38.69</v>
       </c>
       <c r="I79" s="2" t="n">
         <v>63</v>
@@ -3277,17 +3293,17 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>-13.04%</t>
+          <t>-4.35%</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>400</v>
+        <v>440</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>16700</v>
+        <v>35900</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>0.00668</v>
+        <v>0.015796</v>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
@@ -3295,10 +3311,10 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>23.59</v>
+        <v>24.23</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>15.48</v>
+        <v>14.07</v>
       </c>
       <c r="I80" s="2" t="n">
         <v>131</v>
@@ -3311,19 +3327,15 @@
           <t>CHPG2616</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>-11.54%</t>
-        </is>
-      </c>
+      <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="n">
-        <v>460</v>
+        <v>520</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>62800</v>
+        <v>74700</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>0.028888</v>
+        <v>0.038844</v>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
@@ -3331,10 +3343,10 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>17.38</v>
+        <v>18.46</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>12.01</v>
+        <v>10.62</v>
       </c>
       <c r="I81" s="2" t="n">
         <v>99</v>
@@ -3349,17 +3361,17 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>-5.36%</t>
+          <t>+10.71%</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>530</v>
+        <v>620</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>104000</v>
+        <v>289400</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>0.05512</v>
+        <v>0.179428</v>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
@@ -3367,10 +3379,10 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>24.52</v>
+        <v>26.15</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>10.42</v>
+        <v>8.91</v>
       </c>
       <c r="I82" s="2" t="n">
         <v>163</v>
@@ -3464,10 +3476,10 @@
         <v>290</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>5100</v>
+        <v>30100</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>0.001479</v>
+        <v>0.008729000000000001</v>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
@@ -3527,19 +3539,15 @@
           <t>CHPG2622</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>-3.70%</t>
-        </is>
-      </c>
+      <c r="B87" s="2" t="inlineStr"/>
       <c r="C87" s="2" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>211900</v>
+        <v>685600</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>0.055094</v>
+        <v>0.185112</v>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
@@ -3547,10 +3555,10 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>6.43</v>
+        <v>6.52</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>42.5</v>
+        <v>40.93</v>
       </c>
       <c r="I87" s="2" t="n">
         <v>16</v>
@@ -3568,10 +3576,10 @@
         <v>130</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>37700</v>
+        <v>89400</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>0.004901</v>
+        <v>0.011622</v>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
@@ -3595,15 +3603,19 @@
           <t>CHPG2624</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>-16.67%</t>
+        </is>
+      </c>
       <c r="C89" s="2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>324300</v>
+        <v>524700</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>0.019458</v>
+        <v>0.026235</v>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
@@ -3611,10 +3623,10 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>13.67</v>
+        <v>13.57</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>184.17</v>
+        <v>221</v>
       </c>
       <c r="I89" s="2" t="n">
         <v>16</v>
@@ -3627,15 +3639,19 @@
           <t>CHPG2625</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>+1.59%</t>
+        </is>
+      </c>
       <c r="C90" s="2" t="n">
-        <v>630</v>
+        <v>640</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>132200</v>
+        <v>254000</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>0.083286</v>
+        <v>0.16256</v>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
@@ -3643,10 +3659,10 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>18.82</v>
+        <v>18.91</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>17.54</v>
+        <v>17.27</v>
       </c>
       <c r="I90" s="2" t="n">
         <v>135</v>
@@ -3659,15 +3675,19 @@
           <t>CHPG2626</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>+2%</t>
+        </is>
+      </c>
       <c r="C91" s="2" t="n">
-        <v>1000</v>
+        <v>1020</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>79500</v>
+        <v>133000</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>0.0795</v>
+        <v>0.13566</v>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
@@ -3675,10 +3695,10 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>13.12</v>
+        <v>13.3</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>11.05</v>
+        <v>10.83</v>
       </c>
       <c r="I91" s="2" t="n">
         <v>90</v>
@@ -3693,17 +3713,17 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>+1.55%</t>
+          <t>+2.33%</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>1310</v>
+        <v>1320</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>12200</v>
+        <v>137500</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>0.015982</v>
+        <v>0.1815</v>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
@@ -3711,10 +3731,10 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>18.19</v>
+        <v>18.28</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>8.44</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="I92" s="2" t="n">
         <v>154</v>
@@ -3727,19 +3747,15 @@
           <t>CHPG2628</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>-0.55%</t>
-        </is>
-      </c>
+      <c r="B93" s="2" t="inlineStr"/>
       <c r="C93" s="2" t="n">
-        <v>1810</v>
+        <v>1820</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>421700</v>
+        <v>531300</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>0.763277</v>
+        <v>0.966966</v>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
@@ -3747,10 +3763,10 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>27.69</v>
+        <v>27.78</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>6.1</v>
+        <v>6.07</v>
       </c>
       <c r="I93" s="2" t="n">
         <v>230</v>
@@ -3844,10 +3860,10 @@
         <v>400</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>17200</v>
+        <v>21300</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>0.00688</v>
+        <v>0.00852</v>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
@@ -3907,19 +3923,15 @@
           <t>CLPB2602</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>+1.08%</t>
-        </is>
-      </c>
+      <c r="B98" s="2" t="inlineStr"/>
       <c r="C98" s="2" t="n">
-        <v>2810</v>
+        <v>2780</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>2500</v>
+        <v>23200</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>0.007025</v>
+        <v>0.064496</v>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
@@ -3927,7 +3939,7 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.46</v>
+        <v>1.4</v>
       </c>
       <c r="H98" s="2" t="n">
         <v>4.98</v>
@@ -3945,28 +3957,28 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>-2.75%</t>
+          <t>-4.59%</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>1060</v>
+        <v>1040</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>92800</v>
+        <v>181300</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>0.098368</v>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>ATM</t>
+        <v>0.188552</v>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>OTM</t>
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>12.97</v>
+        <v>14.03</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>8.32</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="I99" s="2" t="n">
         <v>99</v>
@@ -3979,15 +3991,19 @@
           <t>CLPB2604</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>+21.49%</t>
+        </is>
+      </c>
       <c r="C100" s="2" t="n">
-        <v>1210</v>
+        <v>1470</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>33500</v>
+        <v>79200</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>0.040535</v>
+        <v>0.116424</v>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
@@ -3995,10 +4011,10 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>19.96</v>
+        <v>24.32</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>7.29</v>
+        <v>5.93</v>
       </c>
       <c r="I100" s="2" t="n">
         <v>163</v>
@@ -4013,17 +4029,17 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>-6.25%</t>
+          <t>-4.69%</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>600</v>
+        <v>610</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>2000</v>
+        <v>22800</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>0.0012</v>
+        <v>0.013908</v>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
@@ -4031,10 +4047,10 @@
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>22.87</v>
+        <v>24.38</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>17.63</v>
+        <v>17.15</v>
       </c>
       <c r="I101" s="2" t="n">
         <v>78</v>
@@ -4056,10 +4072,10 @@
         <v>490</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>3400</v>
+        <v>14800</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>0.001666</v>
+        <v>0.007252</v>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
@@ -4067,10 +4083,10 @@
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>28.35</v>
+        <v>29.83</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>13.49</v>
+        <v>13.34</v>
       </c>
       <c r="I102" s="2" t="n">
         <v>98</v>
@@ -4085,17 +4101,17 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>-4.58%</t>
+          <t>-6.11%</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>1250</v>
+        <v>1230</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>100</v>
+        <v>20100</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>0.000125</v>
+        <v>0.024723</v>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
@@ -4103,10 +4119,10 @@
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>15.78</v>
+        <v>16.92</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="I103" s="2" t="n">
         <v>103</v>
@@ -4119,15 +4135,19 @@
           <t>CLPB2608</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
       <c r="C104" s="2" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v/>
+        <v>500</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v/>
+        <v>0.00049</v>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
@@ -4135,10 +4155,10 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>20.98</v>
+        <v>22.22</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>13.22</v>
+        <v>13.34</v>
       </c>
       <c r="I104" s="2" t="n">
         <v>103</v>
@@ -4153,17 +4173,17 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>+4.64%</t>
+          <t>+1.74%</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>3610</v>
+        <v>3510</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>12800</v>
+        <v>26200</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>0.046208</v>
+        <v>0.091962</v>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
@@ -4171,10 +4191,10 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>5.84</v>
+        <v>5.22</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>4.48</v>
+        <v>4.61</v>
       </c>
       <c r="I105" s="2" t="n">
         <v>30</v>
@@ -4189,17 +4209,17 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>45200</v>
+        <v>196000</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>0.007684</v>
+        <v>0.03724</v>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
@@ -4207,10 +4227,10 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>15.15</v>
+        <v>15.3</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>74.18000000000001</v>
+        <v>66.37</v>
       </c>
       <c r="I106" s="2" t="n">
         <v>19</v>
@@ -4228,10 +4248,10 @@
         <v>960</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>155600</v>
+        <v>195200</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>0.149376</v>
+        <v>0.187392</v>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
@@ -4260,10 +4280,10 @@
         <v>220</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>222400</v>
+        <v>580800</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>0.048928</v>
+        <v>0.127776</v>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
@@ -4321,17 +4341,17 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>-8.77%</t>
+          <t>+1.75%</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
-        <v>520</v>
+        <v>580</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>7000</v>
+        <v>27800</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>0.00364</v>
+        <v>0.016124</v>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
@@ -4339,10 +4359,10 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>7.22</v>
+        <v>7.69</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>24.25</v>
+        <v>21.74</v>
       </c>
       <c r="I110" s="2" t="n">
         <v>28</v>
@@ -4357,17 +4377,17 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>-3.13%</t>
+          <t>+3.13%</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>930</v>
+        <v>990</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>29000</v>
+        <v>59000</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>0.02697</v>
+        <v>0.05841</v>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
@@ -4375,10 +4395,10 @@
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>14.43</v>
+        <v>14.91</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>13.56</v>
+        <v>12.74</v>
       </c>
       <c r="I111" s="2" t="n">
         <v>93</v>
@@ -4391,15 +4411,19 @@
           <t>CMBB2604</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr"/>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>+2.33%</t>
+        </is>
+      </c>
       <c r="C112" s="2" t="n">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>41200</v>
+        <v>352500</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>0.017716</v>
+        <v>0.1551</v>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
@@ -4407,10 +4431,10 @@
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>12.17</v>
+        <v>12.29</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>19.55</v>
+        <v>19.11</v>
       </c>
       <c r="I112" s="2" t="n">
         <v>53</v>
@@ -4425,17 +4449,17 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>-6.17%</t>
+          <t>+2.47%</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>760</v>
+        <v>830</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>700</v>
+        <v>26900</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>0.000532</v>
+        <v>0.022327</v>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
@@ -4443,10 +4467,10 @@
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>13.09</v>
+        <v>13.64</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>16.59</v>
+        <v>15.19</v>
       </c>
       <c r="I113" s="2" t="n">
         <v>98</v>
@@ -4459,15 +4483,19 @@
           <t>CMBB2606</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr"/>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>+2.22%</t>
+        </is>
+      </c>
       <c r="C114" s="2" t="n">
-        <v>900</v>
+        <v>920</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>163200</v>
+        <v>628400</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>0.14688</v>
+        <v>0.578128</v>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
@@ -4475,10 +4503,10 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>1.9</v>
+        <v>2.14</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>9.34</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="I114" s="2" t="n">
         <v>35</v>
@@ -4491,19 +4519,15 @@
           <t>CMBB2607</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>-3.85%</t>
-        </is>
-      </c>
+      <c r="B115" s="2" t="inlineStr"/>
       <c r="C115" s="2" t="n">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>129000</v>
+        <v>322300</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>0.0645</v>
+        <v>0.167596</v>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
@@ -4511,10 +4535,10 @@
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>7.06</v>
+        <v>7.22</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>25.22</v>
+        <v>24.25</v>
       </c>
       <c r="I115" s="2" t="n">
         <v>34</v>
@@ -4527,19 +4551,15 @@
           <t>CMBB2609</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>+2.78%</t>
-        </is>
-      </c>
+      <c r="B116" s="2" t="inlineStr"/>
       <c r="C116" s="2" t="n">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>15000</v>
+        <v>90500</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>0.00555</v>
+        <v>0.03258</v>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
@@ -4547,10 +4567,10 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>22.84</v>
+        <v>22.68</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>17.04</v>
+        <v>17.51</v>
       </c>
       <c r="I116" s="2" t="n">
         <v>107</v>
@@ -4563,15 +4583,19 @@
           <t>CMBB2610</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr"/>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>-2.86%</t>
+        </is>
+      </c>
       <c r="C117" s="2" t="n">
-        <v>1050</v>
+        <v>1020</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v/>
+        <v>500</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v/>
+        <v>0.00051</v>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
@@ -4579,10 +4603,10 @@
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>35.41</v>
+        <v>35.05</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>8.01</v>
+        <v>8.24</v>
       </c>
       <c r="I117" s="2" t="n">
         <v>148</v>
@@ -4604,10 +4628,10 @@
         <v>860</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>14200</v>
+        <v>37200</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>0.012212</v>
+        <v>0.031992</v>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
@@ -4633,17 +4657,17 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>-3.70%</t>
+          <t>+1.85%</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>520</v>
+        <v>550</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>47900</v>
+        <v>59200</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>0.024908</v>
+        <v>0.03256</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -4651,10 +4675,10 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>3.25</v>
+        <v>3.49</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>24.25</v>
+        <v>22.93</v>
       </c>
       <c r="I119" s="2" t="n">
         <v>16</v>
@@ -4669,17 +4693,17 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>-3.23%</t>
+          <t>-6.45%</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>147900</v>
+        <v>342200</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>0.04437</v>
+        <v>0.09923800000000001</v>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
@@ -4687,10 +4711,10 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>5.47</v>
+        <v>5.39</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>42.03</v>
+        <v>43.48</v>
       </c>
       <c r="I120" s="2" t="n">
         <v>16</v>
@@ -4703,19 +4727,15 @@
           <t>CMBB2614</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>+1.32%</t>
-        </is>
-      </c>
+      <c r="B121" s="2" t="inlineStr"/>
       <c r="C121" s="2" t="n">
-        <v>770</v>
+        <v>760</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>617400</v>
+        <v>1005600</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>0.475398</v>
+        <v>0.764256</v>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
@@ -4723,10 +4743,10 @@
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>16.38</v>
+        <v>16.59</v>
       </c>
       <c r="I121" s="2" t="n">
         <v>135</v>
@@ -4739,19 +4759,15 @@
           <t>CMBB2615</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>-3.53%</t>
-        </is>
-      </c>
+      <c r="B122" s="2" t="inlineStr"/>
       <c r="C122" s="2" t="n">
-        <v>1640</v>
+        <v>1700</v>
       </c>
       <c r="D122" s="2" t="n">
-        <v>50100</v>
+        <v>51200</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>0.082164</v>
+        <v>0.08704000000000001</v>
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
@@ -4759,10 +4775,10 @@
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>8.15</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>7.7</v>
+        <v>7.43</v>
       </c>
       <c r="I122" s="2" t="n">
         <v>90</v>
@@ -4777,17 +4793,17 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>+0.50%</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>1990</v>
+        <v>2020</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>3100</v>
+        <v>39100</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>0.006169</v>
+        <v>0.078982</v>
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
@@ -4795,10 +4811,10 @@
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>12.9</v>
+        <v>13.14</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>6.35</v>
+        <v>6.25</v>
       </c>
       <c r="I123" s="2" t="n">
         <v>154</v>
@@ -4816,10 +4832,10 @@
         <v>1190</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>122300</v>
+        <v>139900</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>0.145537</v>
+        <v>0.166481</v>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
@@ -4852,10 +4868,10 @@
         <v>1930</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>78200</v>
+        <v>123800</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>0.150926</v>
+        <v>0.238934</v>
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
@@ -4879,19 +4895,15 @@
           <t>CMSN2522</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>-26.67%</t>
-        </is>
-      </c>
+      <c r="B126" s="2" t="inlineStr"/>
       <c r="C126" s="2" t="n">
-        <v>220</v>
+        <v>300</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>14800</v>
+        <v>14900</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>0.003256</v>
+        <v>0.00447</v>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
@@ -4899,10 +4911,10 @@
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>43.15</v>
+        <v>45.35</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>20.58</v>
+        <v>15.04</v>
       </c>
       <c r="I126" s="2" t="n">
         <v>84</v>
@@ -4924,10 +4936,10 @@
         <v>690</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>2600</v>
+        <v>29700</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>0.001794</v>
+        <v>0.020493</v>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
@@ -4935,10 +4947,10 @@
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>22.9</v>
+        <v>23.26</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>19.68</v>
+        <v>19.62</v>
       </c>
       <c r="I127" s="2" t="n">
         <v>98</v>
@@ -4956,10 +4968,10 @@
         <v>110</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>500</v>
+        <v>85200</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>5.5e-05</v>
+        <v>0.009372</v>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
@@ -4967,10 +4979,10 @@
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>19.12</v>
+        <v>19.47</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>77.16</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="I128" s="2" t="n">
         <v>16</v>
@@ -4983,19 +4995,15 @@
           <t>CMSN2605</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>+6.25%</t>
-        </is>
-      </c>
+      <c r="B129" s="2" t="inlineStr"/>
       <c r="C129" s="2" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>16300</v>
+        <v>61400</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>0.002771</v>
+        <v>0.009823999999999999</v>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
@@ -5003,10 +5011,10 @@
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>17.6</v>
+        <v>17.87</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>79.88</v>
+        <v>84.62</v>
       </c>
       <c r="I129" s="2" t="n">
         <v>34</v>
@@ -5024,10 +5032,10 @@
         <v>10</v>
       </c>
       <c r="D130" s="2" t="n">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>3e-06</v>
+        <v>7e-06</v>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
@@ -5035,10 +5043,10 @@
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>41.53</v>
+        <v>41.95</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I130" s="2" t="n">
         <v>6</v>
@@ -5060,10 +5068,10 @@
         <v>550</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>34000</v>
+        <v>51100</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>0.0187</v>
+        <v>0.028105</v>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
@@ -5071,10 +5079,10 @@
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>31.66</v>
+        <v>32.05</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>15.43</v>
+        <v>15.39</v>
       </c>
       <c r="I131" s="2" t="n">
         <v>133</v>
@@ -5089,17 +5097,17 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>+5.88%</t>
+          <t>+11.76%</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="D132" s="2" t="n">
-        <v>500</v>
+        <v>20300</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>9.000000000000001e-05</v>
+        <v>0.003857</v>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
@@ -5107,10 +5115,10 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>20.47</v>
+        <v>20.97</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>37.72</v>
+        <v>35.63</v>
       </c>
       <c r="I132" s="2" t="n">
         <v>63</v>
@@ -5132,10 +5140,10 @@
         <v>840</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>4900</v>
+        <v>55200</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>0.004116</v>
+        <v>0.046368</v>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
@@ -5143,10 +5151,10 @@
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>28.01</v>
+        <v>28.39</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>10.1</v>
+        <v>10.07</v>
       </c>
       <c r="I133" s="2" t="n">
         <v>163</v>
@@ -5161,17 +5169,17 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>-6.85%</t>
+          <t>+21.92%</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>680</v>
+        <v>890</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>3800</v>
+        <v>6700</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>0.002584</v>
+        <v>0.005963</v>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
@@ -5179,10 +5187,10 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>20.24</v>
+        <v>23.07</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>12.48</v>
+        <v>9.51</v>
       </c>
       <c r="I134" s="2" t="n">
         <v>99</v>
@@ -5195,15 +5203,19 @@
           <t>CMSN2613</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr"/>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>-2.56%</t>
+        </is>
+      </c>
       <c r="C135" s="2" t="n">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v/>
+        <v>200</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v/>
+        <v>7.6e-05</v>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
@@ -5211,10 +5223,10 @@
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>33.56</v>
+        <v>33.81</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>17.41</v>
+        <v>17.82</v>
       </c>
       <c r="I135" s="2" t="n">
         <v>33</v>
@@ -5232,10 +5244,10 @@
         <v>490</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v/>
+        <v>100</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v/>
+        <v>4.9e-05</v>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
@@ -5243,10 +5255,10 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>39.76</v>
+        <v>40.18</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>13.86</v>
+        <v>13.82</v>
       </c>
       <c r="I136" s="2" t="n">
         <v>78</v>
@@ -5264,10 +5276,10 @@
         <v>530</v>
       </c>
       <c r="D137" s="2" t="n">
-        <v/>
+        <v>9200</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v/>
+        <v>0.004876</v>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
@@ -5275,10 +5287,10 @@
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>42.99</v>
+        <v>43.41</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>12.81</v>
+        <v>12.77</v>
       </c>
       <c r="I137" s="2" t="n">
         <v>98</v>
@@ -5296,10 +5308,10 @@
         <v>210</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>691800</v>
+        <v>1020400</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>0.145278</v>
+        <v>0.214284</v>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
@@ -5307,10 +5319,10 @@
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>10.22</v>
+        <v>10.55</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>80.83</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I138" s="2" t="n">
         <v>16</v>
@@ -5323,15 +5335,19 @@
           <t>CMSN2617</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr"/>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>-5.88%</t>
+        </is>
+      </c>
       <c r="C139" s="2" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>84600</v>
+        <v>193400</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>0.014382</v>
+        <v>0.030944</v>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
@@ -5339,10 +5355,10 @@
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>11.46</v>
+        <v>11.73</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>105.78</v>
       </c>
       <c r="I139" s="2" t="n">
         <v>16</v>
@@ -5357,17 +5373,17 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>+16.67%</t>
+          <t>-8.33%</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="D140" s="2" t="n">
-        <v>323800</v>
+        <v>546500</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>0.045332</v>
+        <v>0.060115</v>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
@@ -5375,10 +5391,10 @@
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>12.75</v>
+        <v>12.91</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>121.25</v>
+        <v>153.86</v>
       </c>
       <c r="I140" s="2" t="n">
         <v>16</v>
@@ -5393,17 +5409,17 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>+3.87%</t>
+          <t>+4.52%</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>1610</v>
+        <v>1620</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>83400</v>
+        <v>202500</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>0.134274</v>
+        <v>0.32805</v>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
@@ -5411,10 +5427,10 @@
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>17.32</v>
+        <v>17.75</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>7.03</v>
+        <v>6.97</v>
       </c>
       <c r="I141" s="2" t="n">
         <v>154</v>
@@ -5436,10 +5452,10 @@
         <v>1550</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>115200</v>
+        <v>125200</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>0.17856</v>
+        <v>0.19406</v>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
@@ -5447,10 +5463,10 @@
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>27.84</v>
+        <v>28.21</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>5.48</v>
+        <v>5.46</v>
       </c>
       <c r="I142" s="2" t="n">
         <v>186</v>
@@ -5468,10 +5484,10 @@
         <v>450</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>11100</v>
+        <v>36700</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>0.004995</v>
+        <v>0.016515</v>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
@@ -5479,10 +5495,10 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>18.56</v>
+        <v>18.91</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>15.09</v>
+        <v>15.04</v>
       </c>
       <c r="I143" s="2" t="n">
         <v>103</v>
@@ -5500,10 +5516,10 @@
         <v>40</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>2800</v>
+        <v>25800</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>0.000112</v>
+        <v>0.001032</v>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
@@ -5511,10 +5527,10 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>21.67</v>
+        <v>20.67</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>459.54</v>
+        <v>463.35</v>
       </c>
       <c r="I144" s="2" t="n">
         <v>19</v>
@@ -5529,17 +5545,17 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>+4.71%</t>
+          <t>+9.42%</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
-        <v>2000</v>
+        <v>2090</v>
       </c>
       <c r="D145" s="2" t="n">
-        <v>188700</v>
+        <v>241400</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>0.3774</v>
+        <v>0.504526</v>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
@@ -5547,10 +5563,10 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>22.4</v>
+        <v>21.88</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>9.19</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="I145" s="2" t="n">
         <v>148</v>
@@ -5563,15 +5579,19 @@
           <t>CMWG2526</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr"/>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>+21.05%</t>
+        </is>
+      </c>
       <c r="C146" s="2" t="n">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v/>
+        <v>50400</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v/>
+        <v>0.011592</v>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
@@ -5579,10 +5599,10 @@
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>25.83</v>
+        <v>25.23</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>48.37</v>
+        <v>40.29</v>
       </c>
       <c r="I146" s="2" t="n">
         <v>47</v>
@@ -5597,17 +5617,17 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>+5.88%</t>
+          <t>+17.65%</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
-        <v>540</v>
+        <v>600</v>
       </c>
       <c r="D147" s="2" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>5.4e-05</v>
+        <v>0.00018</v>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
@@ -5615,10 +5635,10 @@
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>35.08</v>
+        <v>34.62</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>17.02</v>
+        <v>15.45</v>
       </c>
       <c r="I147" s="2" t="n">
         <v>113</v>
@@ -5636,10 +5656,10 @@
         <v>190</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v/>
+        <v>53700</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v/>
+        <v>0.010203</v>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
@@ -5647,10 +5667,10 @@
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>19.62</v>
+        <v>18.63</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>77.40000000000001</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="I148" s="2" t="n">
         <v>28</v>
@@ -5665,17 +5685,17 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>+12.73%</t>
+          <t>+23.64%</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>620</v>
+        <v>680</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>13500</v>
+        <v>38300</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>0.008370000000000001</v>
+        <v>0.026044</v>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
@@ -5683,10 +5703,10 @@
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>23.9</v>
+        <v>23.28</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>23.72</v>
+        <v>21.81</v>
       </c>
       <c r="I149" s="2" t="n">
         <v>93</v>
@@ -5701,17 +5721,17 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>+3.70%</t>
+          <t>+11.11%</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>619500</v>
+        <v>1273200</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>0.17346</v>
+        <v>0.38196</v>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
@@ -5719,10 +5739,10 @@
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>18.27</v>
+        <v>17.48</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>37.51</v>
+        <v>35.3</v>
       </c>
       <c r="I150" s="2" t="n">
         <v>53</v>
@@ -5735,15 +5755,19 @@
           <t>CMWG2607</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr"/>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>-83.33%</t>
+        </is>
+      </c>
       <c r="C151" s="2" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v/>
+        <v>100</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v/>
+        <v>1e-06</v>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
@@ -5751,10 +5775,10 @@
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>36.66</v>
+        <v>34.99</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>153.18</v>
+        <v>926.71</v>
       </c>
       <c r="I151" s="2" t="n">
         <v>16</v>
@@ -5769,17 +5793,17 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>+20%</t>
+          <t>-6.67%</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="D152" s="2" t="n">
-        <v>95800</v>
+        <v>173900</v>
       </c>
       <c r="E152" s="2" t="n">
-        <v>0.017244</v>
+        <v>0.024346</v>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
@@ -5787,10 +5811,10 @@
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>23.63</v>
+        <v>22.34</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>81.7</v>
+        <v>105.91</v>
       </c>
       <c r="I152" s="2" t="n">
         <v>34</v>
@@ -5812,10 +5836,10 @@
         <v>360</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>2000</v>
+        <v>16200</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>0.00072</v>
+        <v>0.005832</v>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
@@ -5823,10 +5847,10 @@
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>42.64</v>
+        <v>41.47</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>25.53</v>
+        <v>25.74</v>
       </c>
       <c r="I153" s="2" t="n">
         <v>107</v>
@@ -5859,10 +5883,10 @@
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>45.12</v>
+        <v>43.92</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>12.9</v>
+        <v>13.01</v>
       </c>
       <c r="I154" s="2" t="n">
         <v>148</v>
@@ -5877,17 +5901,17 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>+13.64%</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>1120</v>
+        <v>1250</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>100</v>
+        <v>169400</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>0.000112</v>
+        <v>0.21175</v>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
@@ -5895,10 +5919,10 @@
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>26.7</v>
+        <v>27.06</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>8.210000000000001</v>
+        <v>7.41</v>
       </c>
       <c r="I155" s="2" t="n">
         <v>163</v>
@@ -5913,17 +5937,17 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>+22.41%</t>
+          <t>+37.93%</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
-        <v>710</v>
+        <v>800</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>18500</v>
+        <v>75300</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>0.013135</v>
+        <v>0.06024</v>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
@@ -5931,10 +5955,10 @@
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>5.87</v>
+        <v>5.48</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>25.89</v>
+        <v>23.17</v>
       </c>
       <c r="I156" s="2" t="n">
         <v>16</v>
@@ -5949,17 +5973,17 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>+23.81%</t>
+          <t>+42.86%</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>520</v>
+        <v>600</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>6700</v>
+        <v>12900</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>0.003484</v>
+        <v>0.00774</v>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
@@ -5967,10 +5991,10 @@
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>7.55</v>
+        <v>7.1</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>35.35</v>
+        <v>30.89</v>
       </c>
       <c r="I157" s="2" t="n">
         <v>16</v>
@@ -5985,17 +6009,17 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>+23.33%</t>
+          <t>+30%</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
-        <v>370</v>
+        <v>390</v>
       </c>
       <c r="D158" s="2" t="n">
-        <v>106300</v>
+        <v>318800</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>0.039331</v>
+        <v>0.124332</v>
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
@@ -6003,10 +6027,10 @@
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>9.449999999999999</v>
+        <v>8.66</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>49.68</v>
+        <v>47.52</v>
       </c>
       <c r="I158" s="2" t="n">
         <v>16</v>
@@ -6021,17 +6045,17 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>+11.86%</t>
+          <t>+15.25%</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>660</v>
+        <v>680</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>1111000</v>
+        <v>1518400</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>0.73326</v>
+        <v>1.032512</v>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
@@ -6039,10 +6063,10 @@
         </is>
       </c>
       <c r="G159" s="2" t="n">
-        <v>17.81</v>
+        <v>17.03</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>15.92</v>
+        <v>15.58</v>
       </c>
       <c r="I159" s="2" t="n">
         <v>135</v>
@@ -6057,17 +6081,17 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>+4.44%</t>
+          <t>+8.89%</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
-        <v>1410</v>
+        <v>1470</v>
       </c>
       <c r="D160" s="2" t="n">
-        <v>109100</v>
+        <v>209500</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>0.153831</v>
+        <v>0.307965</v>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
@@ -6075,10 +6099,10 @@
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>12.27</v>
+        <v>11.75</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>10.43</v>
+        <v>10.09</v>
       </c>
       <c r="I160" s="2" t="n">
         <v>90</v>
@@ -6093,17 +6117,17 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>+10.07%</t>
+          <t>+14.39%</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>1530</v>
+        <v>1590</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>563000</v>
+        <v>849100</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>0.86139</v>
+        <v>1.350069</v>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
@@ -6111,10 +6135,10 @@
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>17.21</v>
+        <v>16.73</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>8.01</v>
+        <v>7.77</v>
       </c>
       <c r="I161" s="2" t="n">
         <v>154</v>
@@ -6129,17 +6153,17 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>+6.43%</t>
+          <t>+8.57%</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>1490</v>
+        <v>1520</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>157100</v>
+        <v>206900</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>0.234079</v>
+        <v>0.314488</v>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
@@ -6147,10 +6171,10 @@
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>14.41</v>
+        <v>13.79</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>6.17</v>
+        <v>6.1</v>
       </c>
       <c r="I162" s="2" t="n">
         <v>100</v>
@@ -6165,17 +6189,17 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>+1.67%</t>
+          <t>+5%</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>2440</v>
+        <v>2520</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>9000</v>
+        <v>27600</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>0.02196</v>
+        <v>0.069552</v>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
@@ -6183,10 +6207,10 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>27.19</v>
+        <v>27.01</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>3.77</v>
+        <v>3.68</v>
       </c>
       <c r="I163" s="2" t="n">
         <v>230</v>
@@ -6201,17 +6225,17 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>+10.13%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>870</v>
+        <v>820</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>400</v>
+        <v>103900</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>0.000348</v>
+        <v>0.085198</v>
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
@@ -6219,10 +6243,10 @@
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>29.15</v>
+        <v>27.55</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>10.56</v>
+        <v>11.3</v>
       </c>
       <c r="I164" s="2" t="n">
         <v>168</v>
@@ -6244,10 +6268,10 @@
         <v>20</v>
       </c>
       <c r="D165" s="2" t="n">
-        <v>22900</v>
+        <v>79800</v>
       </c>
       <c r="E165" s="2" t="n">
-        <v>0.000458</v>
+        <v>0.001596</v>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
@@ -6255,10 +6279,10 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>47.89</v>
+        <v>44.2</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>296.49</v>
+        <v>304.09</v>
       </c>
       <c r="I165" s="2" t="n">
         <v>16</v>
@@ -6271,15 +6295,19 @@
           <t>CSHB2605</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr"/>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>-66.67%</t>
+        </is>
+      </c>
       <c r="C166" s="2" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v/>
+        <v>33900</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v/>
+        <v>0.000339</v>
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
@@ -6287,10 +6315,10 @@
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>67.45</v>
+        <v>62.93</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>197.66</v>
+        <v>608.1799999999999</v>
       </c>
       <c r="I166" s="2" t="n">
         <v>6</v>
@@ -6319,10 +6347,10 @@
         </is>
       </c>
       <c r="G167" s="2" t="n">
-        <v>57.44</v>
+        <v>53.5</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>8.24</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="I167" s="2" t="n">
         <v>148</v>
@@ -6335,15 +6363,19 @@
           <t>CSHB2607</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr"/>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>+15%</t>
+        </is>
+      </c>
       <c r="C168" s="2" t="n">
-        <v>400</v>
+        <v>460</v>
       </c>
       <c r="D168" s="2" t="n">
-        <v>21900</v>
+        <v>97100</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>0.00876</v>
+        <v>0.044666</v>
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
@@ -6351,10 +6383,10 @@
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>39.32</v>
+        <v>36.83</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>14.62</v>
+        <v>13.04</v>
       </c>
       <c r="I168" s="2" t="n">
         <v>131</v>
@@ -6369,17 +6401,17 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>-4.17%</t>
+          <t>+12.50%</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
-        <v>230</v>
+        <v>270</v>
       </c>
       <c r="D169" s="2" t="n">
-        <v>700</v>
+        <v>105400</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>0.000161</v>
+        <v>0.028458</v>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
@@ -6387,10 +6419,10 @@
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>34.7</v>
+        <v>32</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>25.43</v>
+        <v>22.22</v>
       </c>
       <c r="I169" s="2" t="n">
         <v>63</v>
@@ -6403,15 +6435,19 @@
           <t>CSHB2609</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr"/>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>+5.88%</t>
+        </is>
+      </c>
       <c r="C170" s="2" t="n">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="D170" s="2" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E170" s="2" t="n">
-        <v>3.4e-05</v>
+        <v>7.2e-05</v>
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
@@ -6419,10 +6455,10 @@
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>51.22</v>
+        <v>48.11</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>8.6</v>
+        <v>8.33</v>
       </c>
       <c r="I170" s="2" t="n">
         <v>78</v>
@@ -6437,17 +6473,17 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>-3.23%</t>
+          <t>+3.23%</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="D171" s="2" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E171" s="2" t="n">
-        <v>3e-05</v>
+        <v>6.4e-05</v>
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
@@ -6455,10 +6491,10 @@
         </is>
       </c>
       <c r="G171" s="2" t="n">
-        <v>47</v>
+        <v>43.99</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>9.75</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I171" s="2" t="n">
         <v>55</v>
@@ -6473,17 +6509,17 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>-4.17%</t>
+          <t>+12.50%</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
-        <v>230</v>
+        <v>270</v>
       </c>
       <c r="D172" s="2" t="n">
-        <v>4500</v>
+        <v>12900</v>
       </c>
       <c r="E172" s="2" t="n">
-        <v>0.001035</v>
+        <v>0.003483</v>
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
@@ -6491,10 +6527,10 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>36.06</v>
+        <v>33.99</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>12.72</v>
+        <v>11.11</v>
       </c>
       <c r="I172" s="2" t="n">
         <v>33</v>
@@ -6507,19 +6543,15 @@
           <t>CSHB2612</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>-11.36%</t>
-        </is>
-      </c>
+      <c r="B173" s="2" t="inlineStr"/>
       <c r="C173" s="2" t="n">
-        <v>390</v>
+        <v>440</v>
       </c>
       <c r="D173" s="2" t="n">
-        <v>1300</v>
+        <v>5900</v>
       </c>
       <c r="E173" s="2" t="n">
-        <v>0.000507</v>
+        <v>0.002596</v>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
@@ -6527,10 +6559,10 @@
         </is>
       </c>
       <c r="G173" s="2" t="n">
-        <v>56.83</v>
+        <v>54.57</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>7.5</v>
+        <v>6.82</v>
       </c>
       <c r="I173" s="2" t="n">
         <v>98</v>
@@ -6545,17 +6577,17 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>-2.70%</t>
+          <t>+10.81%</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
-        <v>360</v>
+        <v>410</v>
       </c>
       <c r="D174" s="2" t="n">
-        <v>267700</v>
+        <v>1337500</v>
       </c>
       <c r="E174" s="2" t="n">
-        <v>0.096372</v>
+        <v>0.5483749999999999</v>
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
@@ -6563,10 +6595,10 @@
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>24.27</v>
+        <v>22.83</v>
       </c>
       <c r="H174" s="2" t="n">
-        <v>8.119999999999999</v>
+        <v>7.32</v>
       </c>
       <c r="I174" s="2" t="n">
         <v>100</v>
@@ -6581,17 +6613,17 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>-1.69%</t>
+          <t>+5.08%</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
-        <v>580</v>
+        <v>620</v>
       </c>
       <c r="D175" s="2" t="n">
-        <v>232000</v>
+        <v>811500</v>
       </c>
       <c r="E175" s="2" t="n">
-        <v>0.13456</v>
+        <v>0.50313</v>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
@@ -6599,10 +6631,10 @@
         </is>
       </c>
       <c r="G175" s="2" t="n">
-        <v>39.49</v>
+        <v>37.33</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>5.04</v>
+        <v>4.84</v>
       </c>
       <c r="I175" s="2" t="n">
         <v>186</v>
@@ -6617,17 +6649,17 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>-20.59%</t>
+          <t>+2.94%</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
-        <v>270</v>
+        <v>350</v>
       </c>
       <c r="D176" s="2" t="n">
-        <v>268600</v>
+        <v>283000</v>
       </c>
       <c r="E176" s="2" t="n">
-        <v>0.072522</v>
+        <v>0.09905</v>
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
@@ -6635,10 +6667,10 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>32.82</v>
+        <v>30.83</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>21.67</v>
+        <v>17.14</v>
       </c>
       <c r="I176" s="2" t="n">
         <v>103</v>
@@ -6653,17 +6685,17 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>-5.41%</t>
+          <t>+8.11%</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="D177" s="2" t="n">
-        <v>5500</v>
+        <v>14900</v>
       </c>
       <c r="E177" s="2" t="n">
-        <v>0.001925</v>
+        <v>0.00596</v>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
@@ -6671,10 +6703,10 @@
         </is>
       </c>
       <c r="G177" s="2" t="n">
-        <v>34.19</v>
+        <v>31.67</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>16.71</v>
+        <v>15</v>
       </c>
       <c r="I177" s="2" t="n">
         <v>103</v>
@@ -6707,10 +6739,10 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>41.37</v>
+        <v>37.83</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>11.25</v>
+        <v>11.54</v>
       </c>
       <c r="I178" s="2" t="n">
         <v>167</v>
@@ -6791,15 +6823,19 @@
           <t>CSSB2604</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr"/>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>+14.29%</t>
+        </is>
+      </c>
       <c r="C181" s="2" t="n">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="D181" s="2" t="n">
-        <v/>
+        <v>222200</v>
       </c>
       <c r="E181" s="2" t="n">
-        <v/>
+        <v>0.053328</v>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
@@ -6807,10 +6843,10 @@
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>22.08</v>
+        <v>22.87</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>18.15</v>
+        <v>15.89</v>
       </c>
       <c r="I181" s="2" t="n">
         <v>98</v>
@@ -6864,10 +6900,10 @@
         <v>180</v>
       </c>
       <c r="D183" s="2" t="n">
-        <v>132800</v>
+        <v>212400</v>
       </c>
       <c r="E183" s="2" t="n">
-        <v>0.023904</v>
+        <v>0.038232</v>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
@@ -6929,17 +6965,17 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>+5.70%</t>
+          <t>+0.76%</t>
         </is>
       </c>
       <c r="C185" s="2" t="n">
-        <v>2780</v>
+        <v>2650</v>
       </c>
       <c r="D185" s="2" t="n">
-        <v>16300</v>
+        <v>30700</v>
       </c>
       <c r="E185" s="2" t="n">
-        <v>0.045314</v>
+        <v>0.081355</v>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
@@ -6947,10 +6983,10 @@
         </is>
       </c>
       <c r="G185" s="2" t="n">
-        <v>2.04</v>
+        <v>2.75</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>9.050000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I185" s="2" t="n">
         <v>19</v>
@@ -6965,17 +7001,17 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>+2.54%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="C186" s="2" t="n">
-        <v>4850</v>
+        <v>4720</v>
       </c>
       <c r="D186" s="2" t="n">
-        <v>24100</v>
+        <v>25700</v>
       </c>
       <c r="E186" s="2" t="n">
-        <v>0.116885</v>
+        <v>0.121304</v>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
@@ -6983,10 +7019,10 @@
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>13.31</v>
+        <v>14.16</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>5.19</v>
+        <v>5.27</v>
       </c>
       <c r="I186" s="2" t="n">
         <v>148</v>
@@ -7001,17 +7037,17 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+2.17%</t>
         </is>
       </c>
       <c r="C187" s="2" t="n">
-        <v>2310</v>
+        <v>2350</v>
       </c>
       <c r="D187" s="2" t="n">
-        <v>10200</v>
+        <v>10300</v>
       </c>
       <c r="E187" s="2" t="n">
-        <v>0.023562</v>
+        <v>0.024205</v>
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
@@ -7019,10 +7055,10 @@
         </is>
       </c>
       <c r="G187" s="2" t="n">
-        <v>3.13</v>
+        <v>4.69</v>
       </c>
       <c r="H187" s="2" t="n">
-        <v>5.45</v>
+        <v>5.29</v>
       </c>
       <c r="I187" s="2" t="n">
         <v>47</v>
@@ -7035,15 +7071,19 @@
           <t>CSTB2537</t>
         </is>
       </c>
-      <c r="B188" s="2" t="inlineStr"/>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>+1.82%</t>
+        </is>
+      </c>
       <c r="C188" s="2" t="n">
-        <v>2750</v>
+        <v>2800</v>
       </c>
       <c r="D188" s="2" t="n">
-        <v/>
+        <v>120100</v>
       </c>
       <c r="E188" s="2" t="n">
-        <v/>
+        <v>0.33628</v>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
@@ -7051,10 +7091,10 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>7.95</v>
+        <v>9.65</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>4.58</v>
+        <v>4.44</v>
       </c>
       <c r="I188" s="2" t="n">
         <v>113</v>
@@ -7067,15 +7107,19 @@
           <t>CSTB2602</t>
         </is>
       </c>
-      <c r="B189" s="2" t="inlineStr"/>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>-3.50%</t>
+        </is>
+      </c>
       <c r="C189" s="2" t="n">
-        <v>6580</v>
+        <v>6350</v>
       </c>
       <c r="D189" s="2" t="n">
-        <v/>
+        <v>5100</v>
       </c>
       <c r="E189" s="2" t="n">
-        <v/>
+        <v>0.032385</v>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
@@ -7083,10 +7127,10 @@
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="I189" s="2" t="n">
         <v>28</v>
@@ -7099,15 +7143,19 @@
           <t>CSTB2603</t>
         </is>
       </c>
-      <c r="B190" s="2" t="inlineStr"/>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>+0.15%</t>
+        </is>
+      </c>
       <c r="C190" s="2" t="n">
-        <v>6830</v>
+        <v>6840</v>
       </c>
       <c r="D190" s="2" t="n">
-        <v/>
+        <v>200</v>
       </c>
       <c r="E190" s="2" t="n">
-        <v/>
+        <v>0.001368</v>
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
@@ -7115,10 +7163,10 @@
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>3.74</v>
+        <v>5.04</v>
       </c>
       <c r="H190" s="2" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="I190" s="2" t="n">
         <v>93</v>
@@ -7133,17 +7181,17 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>+3.15%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="C191" s="2" t="n">
-        <v>3270</v>
+        <v>3160</v>
       </c>
       <c r="D191" s="2" t="n">
-        <v>35900</v>
+        <v>154600</v>
       </c>
       <c r="E191" s="2" t="n">
-        <v>0.117393</v>
+        <v>0.488536</v>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
@@ -7151,10 +7199,10 @@
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>1.13</v>
+        <v>1.61</v>
       </c>
       <c r="H191" s="2" t="n">
-        <v>4.62</v>
+        <v>4.72</v>
       </c>
       <c r="I191" s="2" t="n">
         <v>53</v>
@@ -7169,17 +7217,17 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>+2.37%</t>
+          <t>+1.02%</t>
         </is>
       </c>
       <c r="C192" s="2" t="n">
-        <v>3020</v>
+        <v>2980</v>
       </c>
       <c r="D192" s="2" t="n">
-        <v>155100</v>
+        <v>302400</v>
       </c>
       <c r="E192" s="2" t="n">
-        <v>0.468402</v>
+        <v>0.901152</v>
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
@@ -7187,10 +7235,10 @@
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>7.42</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="H192" s="2" t="n">
-        <v>5</v>
+        <v>5.01</v>
       </c>
       <c r="I192" s="2" t="n">
         <v>107</v>
@@ -7205,17 +7253,17 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>-3.08%</t>
+          <t>-13.85%</t>
         </is>
       </c>
       <c r="C193" s="2" t="n">
-        <v>630</v>
+        <v>560</v>
       </c>
       <c r="D193" s="2" t="n">
-        <v>1600</v>
+        <v>86700</v>
       </c>
       <c r="E193" s="2" t="n">
-        <v>0.001008</v>
+        <v>0.048552</v>
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
@@ -7223,10 +7271,10 @@
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>-0.76</v>
+        <v>-0.31</v>
       </c>
       <c r="H193" s="2" t="n">
-        <v>14.98</v>
+        <v>16.65</v>
       </c>
       <c r="I193" s="2" t="n">
         <v>6</v>
@@ -7255,10 +7303,10 @@
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>25.77</v>
+        <v>27.29</v>
       </c>
       <c r="H194" s="2" t="n">
-        <v>4.73</v>
+        <v>4.67</v>
       </c>
       <c r="I194" s="2" t="n">
         <v>171</v>
@@ -7273,17 +7321,17 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>-4.65%</t>
+          <t>+4.65%</t>
         </is>
       </c>
       <c r="C195" s="2" t="n">
-        <v>2870</v>
+        <v>3150</v>
       </c>
       <c r="D195" s="2" t="n">
-        <v>600</v>
+        <v>3900</v>
       </c>
       <c r="E195" s="2" t="n">
-        <v>0.001722</v>
+        <v>0.012285</v>
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
@@ -7291,10 +7339,10 @@
         </is>
       </c>
       <c r="G195" s="2" t="n">
-        <v>2.62</v>
+        <v>5.36</v>
       </c>
       <c r="H195" s="2" t="n">
-        <v>6.58</v>
+        <v>5.92</v>
       </c>
       <c r="I195" s="2" t="n">
         <v>63</v>
@@ -7309,28 +7357,28 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>+1.07%</t>
+          <t>+4.28%</t>
         </is>
       </c>
       <c r="C196" s="2" t="n">
-        <v>1890</v>
+        <v>1950</v>
       </c>
       <c r="D196" s="2" t="n">
-        <v>4100</v>
+        <v>7100</v>
       </c>
       <c r="E196" s="2" t="n">
-        <v>0.007749</v>
-      </c>
-      <c r="F196" s="3" t="inlineStr">
-        <is>
-          <t>ITM</t>
+        <v>0.013845</v>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>ATM</t>
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>13.96</v>
+        <v>15.82</v>
       </c>
       <c r="H196" s="2" t="n">
-        <v>6.66</v>
+        <v>6.38</v>
       </c>
       <c r="I196" s="2" t="n">
         <v>163</v>
@@ -7363,10 +7411,10 @@
         </is>
       </c>
       <c r="G197" s="2" t="n">
-        <v>8.19</v>
+        <v>9.49</v>
       </c>
       <c r="H197" s="2" t="n">
-        <v>7.07</v>
+        <v>6.99</v>
       </c>
       <c r="I197" s="2" t="n">
         <v>99</v>
@@ -7379,15 +7427,19 @@
           <t>CSTB2612</t>
         </is>
       </c>
-      <c r="B198" s="2" t="inlineStr"/>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>+1.43%</t>
+        </is>
+      </c>
       <c r="C198" s="2" t="n">
-        <v>700</v>
+        <v>710</v>
       </c>
       <c r="D198" s="2" t="n">
-        <v/>
+        <v>200</v>
       </c>
       <c r="E198" s="2" t="n">
-        <v/>
+        <v>0.000142</v>
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
@@ -7395,10 +7447,10 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>14.55</v>
+        <v>16.04</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>13.48</v>
+        <v>13.13</v>
       </c>
       <c r="I198" s="2" t="n">
         <v>78</v>
@@ -7413,17 +7465,17 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>-11.36%</t>
+          <t>-6.82%</t>
         </is>
       </c>
       <c r="C199" s="2" t="n">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="D199" s="2" t="n">
-        <v>40000</v>
+        <v>191500</v>
       </c>
       <c r="E199" s="2" t="n">
-        <v>0.0156</v>
+        <v>0.078515</v>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
@@ -7431,10 +7483,10 @@
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>7.15</v>
+        <v>8.66</v>
       </c>
       <c r="H199" s="2" t="n">
-        <v>24.2</v>
+        <v>22.74</v>
       </c>
       <c r="I199" s="2" t="n">
         <v>33</v>
@@ -7449,17 +7501,17 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>+3.70%</t>
+          <t>+1.85%</t>
         </is>
       </c>
       <c r="C200" s="2" t="n">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="D200" s="2" t="n">
-        <v>3200</v>
+        <v>12900</v>
       </c>
       <c r="E200" s="2" t="n">
-        <v>0.001792</v>
+        <v>0.007095</v>
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
@@ -7467,10 +7519,10 @@
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>10.42</v>
+        <v>11.65</v>
       </c>
       <c r="H200" s="2" t="n">
-        <v>16.85</v>
+        <v>16.95</v>
       </c>
       <c r="I200" s="2" t="n">
         <v>55</v>
@@ -7485,17 +7537,17 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>+1.56%</t>
+          <t>+6.25%</t>
         </is>
       </c>
       <c r="C201" s="2" t="n">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="D201" s="2" t="n">
-        <v>100</v>
+        <v>3200</v>
       </c>
       <c r="E201" s="2" t="n">
-        <v>6.499999999999999e-05</v>
+        <v>0.002176</v>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
@@ -7503,10 +7555,10 @@
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>17.07</v>
+        <v>18.88</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>11.62</v>
+        <v>10.97</v>
       </c>
       <c r="I201" s="2" t="n">
         <v>98</v>
@@ -7521,17 +7573,17 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>+3.54%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="C202" s="2" t="n">
-        <v>2340</v>
+        <v>2240</v>
       </c>
       <c r="D202" s="2" t="n">
-        <v>2600</v>
+        <v>5400</v>
       </c>
       <c r="E202" s="2" t="n">
-        <v>0.006084</v>
+        <v>0.012096</v>
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
@@ -7539,10 +7591,10 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>1.14</v>
+        <v>1.82</v>
       </c>
       <c r="H202" s="2" t="n">
-        <v>8.07</v>
+        <v>8.33</v>
       </c>
       <c r="I202" s="2" t="n">
         <v>16</v>
@@ -7555,19 +7607,15 @@
           <t>CSTB2617</t>
         </is>
       </c>
-      <c r="B203" s="2" t="inlineStr">
-        <is>
-          <t>+4.41%</t>
-        </is>
-      </c>
+      <c r="B203" s="2" t="inlineStr"/>
       <c r="C203" s="2" t="n">
-        <v>2130</v>
+        <v>2040</v>
       </c>
       <c r="D203" s="2" t="n">
-        <v>2600</v>
+        <v>6500</v>
       </c>
       <c r="E203" s="2" t="n">
-        <v>0.005538</v>
+        <v>0.01326</v>
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
@@ -7575,10 +7623,10 @@
         </is>
       </c>
       <c r="G203" s="2" t="n">
-        <v>1.35</v>
+        <v>2.09</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>8.859999999999999</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="I203" s="2" t="n">
         <v>16</v>
@@ -7593,17 +7641,17 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>+4.86%</t>
+          <t>-5.41%</t>
         </is>
       </c>
       <c r="C204" s="2" t="n">
-        <v>1940</v>
+        <v>1750</v>
       </c>
       <c r="D204" s="2" t="n">
-        <v>3000</v>
+        <v>10500</v>
       </c>
       <c r="E204" s="2" t="n">
-        <v>0.00582</v>
+        <v>0.018375</v>
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
@@ -7611,10 +7659,10 @@
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="H204" s="2" t="n">
-        <v>9.73</v>
+        <v>10.66</v>
       </c>
       <c r="I204" s="2" t="n">
         <v>16</v>
@@ -7629,17 +7677,17 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>+5.49%</t>
+          <t>-3.30%</t>
         </is>
       </c>
       <c r="C205" s="2" t="n">
-        <v>960</v>
+        <v>880</v>
       </c>
       <c r="D205" s="2" t="n">
-        <v>20700</v>
+        <v>249700</v>
       </c>
       <c r="E205" s="2" t="n">
-        <v>0.019872</v>
+        <v>0.219736</v>
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
@@ -7647,10 +7695,10 @@
         </is>
       </c>
       <c r="G205" s="2" t="n">
-        <v>10.99</v>
+        <v>11.8</v>
       </c>
       <c r="H205" s="2" t="n">
-        <v>15.73</v>
+        <v>16.95</v>
       </c>
       <c r="I205" s="2" t="n">
         <v>135</v>
@@ -7679,10 +7727,10 @@
         </is>
       </c>
       <c r="G206" s="2" t="n">
-        <v>7.55</v>
+        <v>8.85</v>
       </c>
       <c r="H206" s="2" t="n">
-        <v>6.74</v>
+        <v>6.66</v>
       </c>
       <c r="I206" s="2" t="n">
         <v>99</v>
@@ -7695,15 +7743,19 @@
           <t>CSTB2621</t>
         </is>
       </c>
-      <c r="B207" s="2" t="inlineStr"/>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>+8.88%</t>
+        </is>
+      </c>
       <c r="C207" s="2" t="n">
-        <v>2590</v>
+        <v>2820</v>
       </c>
       <c r="D207" s="2" t="n">
-        <v/>
+        <v>17300</v>
       </c>
       <c r="E207" s="2" t="n">
-        <v/>
+        <v>0.048786</v>
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
@@ -7711,10 +7763,10 @@
         </is>
       </c>
       <c r="G207" s="2" t="n">
-        <v>11.85</v>
+        <v>14.75</v>
       </c>
       <c r="H207" s="2" t="n">
-        <v>5.83</v>
+        <v>5.29</v>
       </c>
       <c r="I207" s="2" t="n">
         <v>163</v>
@@ -7727,19 +7779,15 @@
           <t>CSTB2622</t>
         </is>
       </c>
-      <c r="B208" s="2" t="inlineStr">
-        <is>
-          <t>+3.86%</t>
-        </is>
-      </c>
+      <c r="B208" s="2" t="inlineStr"/>
       <c r="C208" s="2" t="n">
-        <v>2150</v>
+        <v>2070</v>
       </c>
       <c r="D208" s="2" t="n">
-        <v>109100</v>
+        <v>110800</v>
       </c>
       <c r="E208" s="2" t="n">
-        <v>0.234565</v>
+        <v>0.229356</v>
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
@@ -7747,10 +7795,10 @@
         </is>
       </c>
       <c r="G208" s="2" t="n">
-        <v>9.4</v>
+        <v>10.08</v>
       </c>
       <c r="H208" s="2" t="n">
-        <v>5.85</v>
+        <v>6.01</v>
       </c>
       <c r="I208" s="2" t="n">
         <v>100</v>
@@ -7765,17 +7813,17 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>+3.49%</t>
+          <t>+1.31%</t>
         </is>
       </c>
       <c r="C209" s="2" t="n">
-        <v>2370</v>
+        <v>2320</v>
       </c>
       <c r="D209" s="2" t="n">
-        <v>16700</v>
+        <v>20000</v>
       </c>
       <c r="E209" s="2" t="n">
-        <v>0.039579</v>
+        <v>0.0464</v>
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
@@ -7783,10 +7831,10 @@
         </is>
       </c>
       <c r="G209" s="2" t="n">
-        <v>26.12</v>
+        <v>27.24</v>
       </c>
       <c r="H209" s="2" t="n">
-        <v>5.31</v>
+        <v>5.36</v>
       </c>
       <c r="I209" s="2" t="n">
         <v>230</v>
@@ -7801,17 +7849,17 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>+12.67%</t>
+          <t>+18.67%</t>
         </is>
       </c>
       <c r="C210" s="2" t="n">
-        <v>1690</v>
+        <v>1780</v>
       </c>
       <c r="D210" s="2" t="n">
-        <v>2000</v>
+        <v>4100</v>
       </c>
       <c r="E210" s="2" t="n">
-        <v>0.00338</v>
+        <v>0.007298</v>
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
@@ -7819,10 +7867,10 @@
         </is>
       </c>
       <c r="G210" s="2" t="n">
-        <v>17.15</v>
+        <v>19.17</v>
       </c>
       <c r="H210" s="2" t="n">
-        <v>8.93</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="I210" s="2" t="n">
         <v>103</v>
@@ -7835,15 +7883,19 @@
           <t>CSTB2625</t>
         </is>
       </c>
-      <c r="B211" s="2" t="inlineStr"/>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>+28%</t>
+        </is>
+      </c>
       <c r="C211" s="2" t="n">
-        <v>1250</v>
+        <v>1600</v>
       </c>
       <c r="D211" s="2" t="n">
-        <v/>
+        <v>5000</v>
       </c>
       <c r="E211" s="2" t="n">
-        <v/>
+        <v>0.008</v>
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
@@ -7851,10 +7903,10 @@
         </is>
       </c>
       <c r="G211" s="2" t="n">
-        <v>12.58</v>
+        <v>15.82</v>
       </c>
       <c r="H211" s="2" t="n">
-        <v>15.1</v>
+        <v>11.66</v>
       </c>
       <c r="I211" s="2" t="n">
         <v>103</v>
@@ -7876,10 +7928,10 @@
         <v>20</v>
       </c>
       <c r="D212" s="2" t="n">
-        <v>98000</v>
+        <v>307800</v>
       </c>
       <c r="E212" s="2" t="n">
-        <v>0.00196</v>
+        <v>0.006156</v>
       </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
@@ -7887,10 +7939,10 @@
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>46.39</v>
+        <v>41.02</v>
       </c>
       <c r="H212" s="2" t="n">
-        <v>770.88</v>
+        <v>800.23</v>
       </c>
       <c r="I212" s="2" t="n">
         <v>19</v>
@@ -7905,17 +7957,17 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>+9%</t>
+          <t>+30%</t>
         </is>
       </c>
       <c r="C213" s="2" t="n">
-        <v>1090</v>
+        <v>1300</v>
       </c>
       <c r="D213" s="2" t="n">
-        <v>356500</v>
+        <v>387200</v>
       </c>
       <c r="E213" s="2" t="n">
-        <v>0.388585</v>
+        <v>0.50336</v>
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
@@ -7923,10 +7975,10 @@
         </is>
       </c>
       <c r="G213" s="2" t="n">
-        <v>45.23</v>
+        <v>41.21</v>
       </c>
       <c r="H213" s="2" t="n">
-        <v>14.14</v>
+        <v>12.31</v>
       </c>
       <c r="I213" s="2" t="n">
         <v>148</v>
@@ -7939,15 +7991,19 @@
           <t>CTCB2522</t>
         </is>
       </c>
-      <c r="B214" s="2" t="inlineStr"/>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>+7.14%</t>
+        </is>
+      </c>
       <c r="C214" s="2" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="D214" s="2" t="n">
-        <v/>
+        <v>201300</v>
       </c>
       <c r="E214" s="2" t="n">
-        <v/>
+        <v>0.030195</v>
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
@@ -7955,10 +8011,10 @@
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>46.13</v>
+        <v>40.9</v>
       </c>
       <c r="H214" s="2" t="n">
-        <v>55.06</v>
+        <v>53.35</v>
       </c>
       <c r="I214" s="2" t="n">
         <v>47</v>
@@ -7973,17 +8029,17 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>+22.22%</t>
+          <t>+11.11%</t>
         </is>
       </c>
       <c r="C215" s="2" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="D215" s="2" t="n">
-        <v>1500</v>
+        <v>16500</v>
       </c>
       <c r="E215" s="2" t="n">
-        <v>0.00033</v>
+        <v>0.0033</v>
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
@@ -7991,10 +8047,10 @@
         </is>
       </c>
       <c r="G215" s="2" t="n">
-        <v>50.41</v>
+        <v>44.65</v>
       </c>
       <c r="H215" s="2" t="n">
-        <v>35.04</v>
+        <v>40.01</v>
       </c>
       <c r="I215" s="2" t="n">
         <v>113</v>
@@ -8009,17 +8065,17 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>+12.50%</t>
+          <t>+4.17%</t>
         </is>
       </c>
       <c r="C216" s="2" t="n">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="D216" s="2" t="n">
-        <v>157400</v>
+        <v>403100</v>
       </c>
       <c r="E216" s="2" t="n">
-        <v>0.042498</v>
+        <v>0.100775</v>
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
@@ -8027,10 +8083,10 @@
         </is>
       </c>
       <c r="G216" s="2" t="n">
-        <v>23.5</v>
+        <v>18.72</v>
       </c>
       <c r="H216" s="2" t="n">
-        <v>28.55</v>
+        <v>32.01</v>
       </c>
       <c r="I216" s="2" t="n">
         <v>53</v>
@@ -8045,17 +8101,17 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>+4.55%</t>
+          <t>+22.73%</t>
         </is>
       </c>
       <c r="C217" s="2" t="n">
-        <v>230</v>
+        <v>270</v>
       </c>
       <c r="D217" s="2" t="n">
-        <v>103200</v>
+        <v>270500</v>
       </c>
       <c r="E217" s="2" t="n">
-        <v>0.023736</v>
+        <v>0.073035</v>
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
@@ -8063,10 +8119,10 @@
         </is>
       </c>
       <c r="G217" s="2" t="n">
-        <v>18.99</v>
+        <v>15</v>
       </c>
       <c r="H217" s="2" t="n">
-        <v>44.69</v>
+        <v>39.52</v>
       </c>
       <c r="I217" s="2" t="n">
         <v>35</v>
@@ -8081,17 +8137,17 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>+10.71%</t>
+          <t>+28.57%</t>
         </is>
       </c>
       <c r="C218" s="2" t="n">
-        <v>310</v>
+        <v>360</v>
       </c>
       <c r="D218" s="2" t="n">
-        <v>19200</v>
+        <v>156000</v>
       </c>
       <c r="E218" s="2" t="n">
-        <v>0.005952</v>
+        <v>0.05616</v>
       </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
@@ -8099,10 +8155,10 @@
         </is>
       </c>
       <c r="G218" s="2" t="n">
-        <v>15.52</v>
+        <v>11.59</v>
       </c>
       <c r="H218" s="2" t="n">
-        <v>49.73</v>
+        <v>44.46</v>
       </c>
       <c r="I218" s="2" t="n">
         <v>34</v>
@@ -8117,17 +8173,17 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>+5.13%</t>
+          <t>+2.56%</t>
         </is>
       </c>
       <c r="C219" s="2" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="D219" s="2" t="n">
-        <v>29100</v>
+        <v>63600</v>
       </c>
       <c r="E219" s="2" t="n">
-        <v>0.011931</v>
+        <v>0.02544</v>
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
@@ -8135,10 +8191,10 @@
         </is>
       </c>
       <c r="G219" s="2" t="n">
-        <v>33.42</v>
+        <v>28.4</v>
       </c>
       <c r="H219" s="2" t="n">
-        <v>18.8</v>
+        <v>20.01</v>
       </c>
       <c r="I219" s="2" t="n">
         <v>107</v>
@@ -8153,17 +8209,17 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>+6.67%</t>
+          <t>+21.11%</t>
         </is>
       </c>
       <c r="C220" s="2" t="n">
-        <v>960</v>
+        <v>1090</v>
       </c>
       <c r="D220" s="2" t="n">
-        <v>1400</v>
+        <v>2600</v>
       </c>
       <c r="E220" s="2" t="n">
-        <v>0.001344</v>
+        <v>0.002834</v>
       </c>
       <c r="F220" s="4" t="inlineStr">
         <is>
@@ -8171,10 +8227,10 @@
         </is>
       </c>
       <c r="G220" s="2" t="n">
-        <v>29.21</v>
+        <v>26.1</v>
       </c>
       <c r="H220" s="2" t="n">
-        <v>8.029999999999999</v>
+        <v>7.34</v>
       </c>
       <c r="I220" s="2" t="n">
         <v>171</v>
@@ -8189,17 +8245,17 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>+21.43%</t>
+          <t>+71.43%</t>
         </is>
       </c>
       <c r="C221" s="2" t="n">
-        <v>170</v>
+        <v>240</v>
       </c>
       <c r="D221" s="2" t="n">
-        <v>103700</v>
+        <v>1160500</v>
       </c>
       <c r="E221" s="2" t="n">
-        <v>0.017629</v>
+        <v>0.27852</v>
       </c>
       <c r="F221" s="4" t="inlineStr">
         <is>
@@ -8207,10 +8263,10 @@
         </is>
       </c>
       <c r="G221" s="2" t="n">
-        <v>10.4</v>
+        <v>6.79</v>
       </c>
       <c r="H221" s="2" t="n">
-        <v>88.81999999999999</v>
+        <v>65.31</v>
       </c>
       <c r="I221" s="2" t="n">
         <v>16</v>
@@ -8225,17 +8281,17 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>+33.33%</t>
+          <t>+116.67%</t>
         </is>
       </c>
       <c r="C222" s="2" t="n">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="D222" s="2" t="n">
-        <v>1176600</v>
+        <v>4632000</v>
       </c>
       <c r="E222" s="2" t="n">
-        <v>0.094128</v>
+        <v>0.60216</v>
       </c>
       <c r="F222" s="4" t="inlineStr">
         <is>
@@ -8243,10 +8299,10 @@
         </is>
       </c>
       <c r="G222" s="2" t="n">
-        <v>13.11</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="H222" s="2" t="n">
-        <v>188.75</v>
+        <v>120.58</v>
       </c>
       <c r="I222" s="2" t="n">
         <v>16</v>
@@ -8261,17 +8317,17 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>+25%</t>
+          <t>+50%</t>
         </is>
       </c>
       <c r="C223" s="2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D223" s="2" t="n">
-        <v>695500</v>
+        <v>3328400</v>
       </c>
       <c r="E223" s="2" t="n">
-        <v>0.034775</v>
+        <v>0.199704</v>
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
@@ -8279,10 +8335,10 @@
         </is>
       </c>
       <c r="G223" s="2" t="n">
-        <v>16.23</v>
+        <v>12.03</v>
       </c>
       <c r="H223" s="2" t="n">
-        <v>302</v>
+        <v>261.25</v>
       </c>
       <c r="I223" s="2" t="n">
         <v>16</v>
@@ -8297,17 +8353,17 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>+17.24%</t>
+          <t>+18.97%</t>
         </is>
       </c>
       <c r="C224" s="2" t="n">
-        <v>680</v>
+        <v>690</v>
       </c>
       <c r="D224" s="2" t="n">
-        <v>193100</v>
+        <v>882900</v>
       </c>
       <c r="E224" s="2" t="n">
-        <v>0.131308</v>
+        <v>0.609201</v>
       </c>
       <c r="F224" s="4" t="inlineStr">
         <is>
@@ -8315,10 +8371,10 @@
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>19.34</v>
+        <v>15.06</v>
       </c>
       <c r="H224" s="2" t="n">
-        <v>14.8</v>
+        <v>15.14</v>
       </c>
       <c r="I224" s="2" t="n">
         <v>135</v>
@@ -8333,28 +8389,28 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>+10.26%</t>
+          <t>+31.41%</t>
         </is>
       </c>
       <c r="C225" s="2" t="n">
-        <v>1720</v>
+        <v>2050</v>
       </c>
       <c r="D225" s="2" t="n">
-        <v>962100</v>
+        <v>1260700</v>
       </c>
       <c r="E225" s="2" t="n">
-        <v>1.654812</v>
-      </c>
-      <c r="F225" s="2" t="inlineStr">
-        <is>
-          <t>ATM</t>
+        <v>2.584435</v>
+      </c>
+      <c r="F225" s="3" t="inlineStr">
+        <is>
+          <t>ITM</t>
         </is>
       </c>
       <c r="G225" s="2" t="n">
-        <v>10.73</v>
+        <v>8.77</v>
       </c>
       <c r="H225" s="2" t="n">
-        <v>8.779999999999999</v>
+        <v>7.65</v>
       </c>
       <c r="I225" s="2" t="n">
         <v>90</v>
@@ -8369,28 +8425,28 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>+7.46%</t>
+          <t>+23.88%</t>
         </is>
       </c>
       <c r="C226" s="2" t="n">
-        <v>1440</v>
+        <v>1660</v>
       </c>
       <c r="D226" s="2" t="n">
-        <v>159300</v>
+        <v>447300</v>
       </c>
       <c r="E226" s="2" t="n">
-        <v>0.229392</v>
-      </c>
-      <c r="F226" s="2" t="inlineStr">
-        <is>
-          <t>ATM</t>
+        <v>0.742518</v>
+      </c>
+      <c r="F226" s="3" t="inlineStr">
+        <is>
+          <t>ITM</t>
         </is>
       </c>
       <c r="G226" s="2" t="n">
-        <v>15.3</v>
+        <v>13.17</v>
       </c>
       <c r="H226" s="2" t="n">
-        <v>6.99</v>
+        <v>6.3</v>
       </c>
       <c r="I226" s="2" t="n">
         <v>154</v>
@@ -8405,17 +8461,17 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>+9.18%</t>
+          <t>+19.39%</t>
         </is>
       </c>
       <c r="C227" s="2" t="n">
-        <v>1070</v>
+        <v>1170</v>
       </c>
       <c r="D227" s="2" t="n">
-        <v>58300</v>
+        <v>96400</v>
       </c>
       <c r="E227" s="2" t="n">
-        <v>0.062381</v>
+        <v>0.112788</v>
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
@@ -8423,10 +8479,10 @@
         </is>
       </c>
       <c r="G227" s="2" t="n">
-        <v>31.72</v>
+        <v>28.17</v>
       </c>
       <c r="H227" s="2" t="n">
-        <v>7.06</v>
+        <v>6.7</v>
       </c>
       <c r="I227" s="2" t="n">
         <v>186</v>
@@ -8441,17 +8497,17 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>+23.33%</t>
         </is>
       </c>
       <c r="C228" s="2" t="n">
-        <v>330</v>
+        <v>370</v>
       </c>
       <c r="D228" s="2" t="n">
-        <v>200</v>
+        <v>19200</v>
       </c>
       <c r="E228" s="2" t="n">
-        <v>6.600000000000001e-05</v>
+        <v>0.007104</v>
       </c>
       <c r="F228" s="4" t="inlineStr">
         <is>
@@ -8459,10 +8515,10 @@
         </is>
       </c>
       <c r="G228" s="2" t="n">
-        <v>24.67</v>
+        <v>20.73</v>
       </c>
       <c r="H228" s="2" t="n">
-        <v>18.3</v>
+        <v>16.95</v>
       </c>
       <c r="I228" s="2" t="n">
         <v>103</v>
@@ -8480,10 +8536,10 @@
         <v>20</v>
       </c>
       <c r="D229" s="2" t="n">
-        <v>100</v>
+        <v>102800</v>
       </c>
       <c r="E229" s="2" t="n">
-        <v>2e-06</v>
+        <v>0.002056</v>
       </c>
       <c r="F229" s="4" t="inlineStr">
         <is>
@@ -8491,10 +8547,10 @@
         </is>
       </c>
       <c r="G229" s="2" t="n">
-        <v>29.97</v>
+        <v>29.08</v>
       </c>
       <c r="H229" s="2" t="n">
-        <v>366.25</v>
+        <v>368.75</v>
       </c>
       <c r="I229" s="2" t="n">
         <v>16</v>
@@ -8507,16 +8563,12 @@
           <t>CTPB2604</t>
         </is>
       </c>
-      <c r="B230" s="2" t="inlineStr">
-        <is>
-          <t>+100%</t>
-        </is>
-      </c>
+      <c r="B230" s="2" t="inlineStr"/>
       <c r="C230" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D230" s="2" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E230" s="2" t="n">
         <v>2e-06</v>
@@ -8527,10 +8579,10 @@
         </is>
       </c>
       <c r="G230" s="2" t="n">
-        <v>41.49</v>
+        <v>40.39</v>
       </c>
       <c r="H230" s="2" t="n">
-        <v>366.25</v>
+        <v>737.5</v>
       </c>
       <c r="I230" s="2" t="n">
         <v>6</v>
@@ -8548,10 +8600,10 @@
         <v>500</v>
       </c>
       <c r="D231" s="2" t="n">
-        <v>23900</v>
+        <v>131100</v>
       </c>
       <c r="E231" s="2" t="n">
-        <v>0.01195</v>
+        <v>0.06555</v>
       </c>
       <c r="F231" s="4" t="inlineStr">
         <is>
@@ -8559,10 +8611,10 @@
         </is>
       </c>
       <c r="G231" s="2" t="n">
-        <v>29.69</v>
+        <v>28.81</v>
       </c>
       <c r="H231" s="2" t="n">
-        <v>14.65</v>
+        <v>14.75</v>
       </c>
       <c r="I231" s="2" t="n">
         <v>133</v>
@@ -8591,10 +8643,10 @@
         </is>
       </c>
       <c r="G232" s="2" t="n">
-        <v>35.77</v>
+        <v>34.85</v>
       </c>
       <c r="H232" s="2" t="n">
-        <v>7.75</v>
+        <v>7.8</v>
       </c>
       <c r="I232" s="2" t="n">
         <v>193</v>
@@ -8609,17 +8661,17 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>-28.89%</t>
+          <t>-24.44%</t>
         </is>
       </c>
       <c r="C233" s="2" t="n">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="D233" s="2" t="n">
-        <v>1100</v>
+        <v>11100</v>
       </c>
       <c r="E233" s="2" t="n">
-        <v>0.000352</v>
+        <v>0.003774</v>
       </c>
       <c r="F233" s="4" t="inlineStr">
         <is>
@@ -8627,10 +8679,10 @@
         </is>
       </c>
       <c r="G233" s="2" t="n">
-        <v>41.15</v>
+        <v>40.74</v>
       </c>
       <c r="H233" s="2" t="n">
-        <v>11.45</v>
+        <v>10.85</v>
       </c>
       <c r="I233" s="2" t="n">
         <v>98</v>
@@ -8648,10 +8700,10 @@
         <v>300</v>
       </c>
       <c r="D234" s="2" t="n">
-        <v/>
+        <v>700</v>
       </c>
       <c r="E234" s="2" t="n">
-        <v/>
+        <v>0.00021</v>
       </c>
       <c r="F234" s="4" t="inlineStr">
         <is>
@@ -8659,10 +8711,10 @@
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>37.12</v>
+        <v>36.19</v>
       </c>
       <c r="H234" s="2" t="n">
-        <v>12.21</v>
+        <v>12.29</v>
       </c>
       <c r="I234" s="2" t="n">
         <v>78</v>
@@ -8695,10 +8747,10 @@
         </is>
       </c>
       <c r="G235" s="2" t="n">
-        <v>28.33</v>
+        <v>27.46</v>
       </c>
       <c r="H235" s="2" t="n">
-        <v>18.31</v>
+        <v>18.44</v>
       </c>
       <c r="I235" s="2" t="n">
         <v>103</v>
@@ -8716,10 +8768,10 @@
         <v>320</v>
       </c>
       <c r="D236" s="2" t="n">
-        <v>100</v>
+        <v>4700</v>
       </c>
       <c r="E236" s="2" t="n">
-        <v>3.2e-05</v>
+        <v>0.001504</v>
       </c>
       <c r="F236" s="4" t="inlineStr">
         <is>
@@ -8727,10 +8779,10 @@
         </is>
       </c>
       <c r="G236" s="2" t="n">
-        <v>27.24</v>
+        <v>26.37</v>
       </c>
       <c r="H236" s="2" t="n">
-        <v>22.89</v>
+        <v>23.05</v>
       </c>
       <c r="I236" s="2" t="n">
         <v>103</v>
@@ -8745,17 +8797,17 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>-9.59%</t>
+          <t>-14.51%</t>
         </is>
       </c>
       <c r="C237" s="2" t="n">
-        <v>3490</v>
+        <v>3300</v>
       </c>
       <c r="D237" s="2" t="n">
-        <v>7000</v>
+        <v>281900</v>
       </c>
       <c r="E237" s="2" t="n">
-        <v>0.02443</v>
+        <v>0.93027</v>
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
@@ -8763,10 +8815,10 @@
         </is>
       </c>
       <c r="G237" s="2" t="n">
-        <v>11.83</v>
+        <v>11.9</v>
       </c>
       <c r="H237" s="2" t="n">
-        <v>5.38</v>
+        <v>5.63</v>
       </c>
       <c r="I237" s="2" t="n">
         <v>47</v>
@@ -8799,10 +8851,10 @@
         </is>
       </c>
       <c r="G238" s="2" t="n">
-        <v>23.15</v>
+        <v>24.35</v>
       </c>
       <c r="H238" s="2" t="n">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="I238" s="2" t="n">
         <v>113</v>
@@ -8817,17 +8869,17 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>-2.08%</t>
+          <t>-16.16%</t>
         </is>
       </c>
       <c r="C239" s="2" t="n">
-        <v>8000</v>
+        <v>6850</v>
       </c>
       <c r="D239" s="2" t="n">
-        <v>3900</v>
+        <v>12400</v>
       </c>
       <c r="E239" s="2" t="n">
-        <v>0.0312</v>
+        <v>0.08494</v>
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
@@ -8835,10 +8887,10 @@
         </is>
       </c>
       <c r="G239" s="2" t="n">
-        <v>9.220000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="H239" s="2" t="n">
-        <v>2.35</v>
+        <v>2.71</v>
       </c>
       <c r="I239" s="2" t="n">
         <v>28</v>
@@ -8853,17 +8905,17 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>+6.53%</t>
+          <t>-7.92%</t>
         </is>
       </c>
       <c r="C240" s="2" t="n">
-        <v>7670</v>
+        <v>6630</v>
       </c>
       <c r="D240" s="2" t="n">
-        <v>1700</v>
+        <v>189900</v>
       </c>
       <c r="E240" s="2" t="n">
-        <v>0.013039</v>
+        <v>1.259037</v>
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
@@ -8871,10 +8923,10 @@
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>8.789999999999999</v>
+        <v>4.26</v>
       </c>
       <c r="H240" s="2" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="I240" s="2" t="n">
         <v>93</v>
@@ -8889,17 +8941,17 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>-6.08%</t>
+          <t>-8.16%</t>
         </is>
       </c>
       <c r="C241" s="2" t="n">
-        <v>5410</v>
+        <v>5290</v>
       </c>
       <c r="D241" s="2" t="n">
-        <v>21100</v>
+        <v>75700</v>
       </c>
       <c r="E241" s="2" t="n">
-        <v>0.114151</v>
+        <v>0.400453</v>
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
@@ -8907,10 +8959,10 @@
         </is>
       </c>
       <c r="G241" s="2" t="n">
-        <v>6.62</v>
+        <v>6.85</v>
       </c>
       <c r="H241" s="2" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="I241" s="2" t="n">
         <v>98</v>
@@ -8925,17 +8977,17 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>+22.34%</t>
+          <t>+4.40%</t>
         </is>
       </c>
       <c r="C242" s="2" t="n">
-        <v>6680</v>
+        <v>5700</v>
       </c>
       <c r="D242" s="2" t="n">
-        <v>17400</v>
+        <v>26800</v>
       </c>
       <c r="E242" s="2" t="n">
-        <v>0.116232</v>
+        <v>0.15276</v>
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
@@ -8943,10 +8995,10 @@
         </is>
       </c>
       <c r="G242" s="2" t="n">
-        <v>12.15</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="H242" s="2" t="n">
-        <v>4.5</v>
+        <v>5.22</v>
       </c>
       <c r="I242" s="2" t="n">
         <v>34</v>
@@ -8961,17 +9013,17 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>-27.97%</t>
+          <t>-57.63%</t>
         </is>
       </c>
       <c r="C243" s="2" t="n">
-        <v>850</v>
+        <v>500</v>
       </c>
       <c r="D243" s="2" t="n">
-        <v>27500</v>
+        <v>61200</v>
       </c>
       <c r="E243" s="2" t="n">
-        <v>0.023375</v>
+        <v>0.0306</v>
       </c>
       <c r="F243" s="2" t="inlineStr">
         <is>
@@ -8979,10 +9031,10 @@
         </is>
       </c>
       <c r="G243" s="2" t="n">
-        <v>5.94</v>
+        <v>4.16</v>
       </c>
       <c r="H243" s="2" t="n">
-        <v>14.72</v>
+        <v>24.78</v>
       </c>
       <c r="I243" s="2" t="n">
         <v>6</v>
@@ -8997,17 +9049,17 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>-1.99%</t>
+          <t>-2.98%</t>
         </is>
       </c>
       <c r="C244" s="2" t="n">
-        <v>4930</v>
+        <v>4880</v>
       </c>
       <c r="D244" s="2" t="n">
-        <v>30300</v>
+        <v>66100</v>
       </c>
       <c r="E244" s="2" t="n">
-        <v>0.149379</v>
+        <v>0.322568</v>
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
@@ -9015,10 +9067,10 @@
         </is>
       </c>
       <c r="G244" s="2" t="n">
-        <v>16.12</v>
+        <v>16.95</v>
       </c>
       <c r="H244" s="2" t="n">
-        <v>3.38</v>
+        <v>3.39</v>
       </c>
       <c r="I244" s="2" t="n">
         <v>133</v>
@@ -9033,17 +9085,17 @@
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>-8.96%</t>
+          <t>-13.93%</t>
         </is>
       </c>
       <c r="C245" s="2" t="n">
-        <v>1830</v>
+        <v>1730</v>
       </c>
       <c r="D245" s="2" t="n">
-        <v>159800</v>
+        <v>384800</v>
       </c>
       <c r="E245" s="2" t="n">
-        <v>0.292434</v>
+        <v>0.665704</v>
       </c>
       <c r="F245" s="4" t="inlineStr">
         <is>
@@ -9051,10 +9103,10 @@
         </is>
       </c>
       <c r="G245" s="2" t="n">
-        <v>33.62</v>
+        <v>34.39</v>
       </c>
       <c r="H245" s="2" t="n">
-        <v>10.26</v>
+        <v>10.74</v>
       </c>
       <c r="I245" s="2" t="n">
         <v>99</v>
@@ -9069,17 +9121,17 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>-7.24%</t>
+          <t>-11.72%</t>
         </is>
       </c>
       <c r="C246" s="2" t="n">
-        <v>2690</v>
+        <v>2560</v>
       </c>
       <c r="D246" s="2" t="n">
-        <v>209500</v>
+        <v>211800</v>
       </c>
       <c r="E246" s="2" t="n">
-        <v>0.563555</v>
+        <v>0.542208</v>
       </c>
       <c r="F246" s="4" t="inlineStr">
         <is>
@@ -9087,10 +9139,10 @@
         </is>
       </c>
       <c r="G246" s="2" t="n">
-        <v>40.86</v>
+        <v>41.54</v>
       </c>
       <c r="H246" s="2" t="n">
-        <v>6.98</v>
+        <v>7.26</v>
       </c>
       <c r="I246" s="2" t="n">
         <v>163</v>
@@ -9105,17 +9157,17 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>-13.51%</t>
+          <t>+2.70%</t>
         </is>
       </c>
       <c r="C247" s="2" t="n">
-        <v>320</v>
+        <v>380</v>
       </c>
       <c r="D247" s="2" t="n">
-        <v>39100</v>
+        <v>130700</v>
       </c>
       <c r="E247" s="2" t="n">
-        <v>0.012512</v>
+        <v>0.049666</v>
       </c>
       <c r="F247" s="4" t="inlineStr">
         <is>
@@ -9123,10 +9175,10 @@
         </is>
       </c>
       <c r="G247" s="2" t="n">
-        <v>17.47</v>
+        <v>19.43</v>
       </c>
       <c r="H247" s="2" t="n">
-        <v>23.46</v>
+        <v>19.57</v>
       </c>
       <c r="I247" s="2" t="n">
         <v>33</v>
@@ -9141,17 +9193,17 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>+1.85%</t>
+          <t>-5.56%</t>
         </is>
       </c>
       <c r="C248" s="2" t="n">
-        <v>550</v>
+        <v>510</v>
       </c>
       <c r="D248" s="2" t="n">
-        <v>3500</v>
+        <v>74100</v>
       </c>
       <c r="E248" s="2" t="n">
-        <v>0.001925</v>
+        <v>0.037791</v>
       </c>
       <c r="F248" s="4" t="inlineStr">
         <is>
@@ -9159,10 +9211,10 @@
         </is>
       </c>
       <c r="G248" s="2" t="n">
-        <v>23.19</v>
+        <v>23.85</v>
       </c>
       <c r="H248" s="2" t="n">
-        <v>13.65</v>
+        <v>14.58</v>
       </c>
       <c r="I248" s="2" t="n">
         <v>78</v>
@@ -9177,17 +9229,17 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>-11.59%</t>
+          <t>-18.84%</t>
         </is>
       </c>
       <c r="C249" s="2" t="n">
-        <v>610</v>
+        <v>560</v>
       </c>
       <c r="D249" s="2" t="n">
-        <v>439200</v>
+        <v>624100</v>
       </c>
       <c r="E249" s="2" t="n">
-        <v>0.267912</v>
+        <v>0.349496</v>
       </c>
       <c r="F249" s="4" t="inlineStr">
         <is>
@@ -9195,10 +9247,10 @@
         </is>
       </c>
       <c r="G249" s="2" t="n">
-        <v>25.91</v>
+        <v>26.47</v>
       </c>
       <c r="H249" s="2" t="n">
-        <v>12.31</v>
+        <v>13.28</v>
       </c>
       <c r="I249" s="2" t="n">
         <v>98</v>
@@ -9213,17 +9265,17 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>-6.97%</t>
+          <t>-8.96%</t>
         </is>
       </c>
       <c r="C250" s="2" t="n">
-        <v>1870</v>
+        <v>1830</v>
       </c>
       <c r="D250" s="2" t="n">
-        <v>80200</v>
+        <v>339700</v>
       </c>
       <c r="E250" s="2" t="n">
-        <v>0.149974</v>
+        <v>0.621651</v>
       </c>
       <c r="F250" s="4" t="inlineStr">
         <is>
@@ -9231,10 +9283,10 @@
         </is>
       </c>
       <c r="G250" s="2" t="n">
-        <v>40</v>
+        <v>41.03</v>
       </c>
       <c r="H250" s="2" t="n">
-        <v>6.44</v>
+        <v>6.52</v>
       </c>
       <c r="I250" s="2" t="n">
         <v>168</v>
@@ -9247,15 +9299,19 @@
           <t>CVIB2513</t>
         </is>
       </c>
-      <c r="B251" s="2" t="inlineStr"/>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>+7.41%</t>
+        </is>
+      </c>
       <c r="C251" s="2" t="n">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="D251" s="2" t="n">
-        <v>61200</v>
+        <v>63200</v>
       </c>
       <c r="E251" s="2" t="n">
-        <v>0.016524</v>
+        <v>0.018328</v>
       </c>
       <c r="F251" s="4" t="inlineStr">
         <is>
@@ -9263,10 +9319,10 @@
         </is>
       </c>
       <c r="G251" s="2" t="n">
-        <v>37.99</v>
+        <v>37.78</v>
       </c>
       <c r="H251" s="2" t="n">
-        <v>28.91</v>
+        <v>27</v>
       </c>
       <c r="I251" s="2" t="n">
         <v>84</v>
@@ -9281,17 +9337,17 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>+3.92%</t>
+          <t>+5.88%</t>
         </is>
       </c>
       <c r="C252" s="2" t="n">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="D252" s="2" t="n">
-        <v>6700</v>
+        <v>23200</v>
       </c>
       <c r="E252" s="2" t="n">
-        <v>0.003551</v>
+        <v>0.012528</v>
       </c>
       <c r="F252" s="4" t="inlineStr">
         <is>
@@ -9299,10 +9355,10 @@
         </is>
       </c>
       <c r="G252" s="2" t="n">
-        <v>22.1</v>
+        <v>21.82</v>
       </c>
       <c r="H252" s="2" t="n">
-        <v>14.73</v>
+        <v>14.5</v>
       </c>
       <c r="I252" s="2" t="n">
         <v>98</v>
@@ -9315,15 +9371,19 @@
           <t>CVIB2603</t>
         </is>
       </c>
-      <c r="B253" s="2" t="inlineStr"/>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>+100%</t>
+        </is>
+      </c>
       <c r="C253" s="2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D253" s="2" t="n">
-        <v>3000</v>
+        <v>8100</v>
       </c>
       <c r="E253" s="2" t="n">
-        <v>3e-05</v>
+        <v>0.000162</v>
       </c>
       <c r="F253" s="4" t="inlineStr">
         <is>
@@ -9331,10 +9391,10 @@
         </is>
       </c>
       <c r="G253" s="2" t="n">
-        <v>28.32</v>
+        <v>28.08</v>
       </c>
       <c r="H253" s="2" t="n">
-        <v>520.3200000000001</v>
+        <v>261.04</v>
       </c>
       <c r="I253" s="2" t="n">
         <v>16</v>
@@ -9349,17 +9409,17 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>+1.96%</t>
+          <t>+5.88%</t>
         </is>
       </c>
       <c r="C254" s="2" t="n">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="D254" s="2" t="n">
-        <v>54300</v>
+        <v>141100</v>
       </c>
       <c r="E254" s="2" t="n">
-        <v>0.028236</v>
+        <v>0.076194</v>
       </c>
       <c r="F254" s="4" t="inlineStr">
         <is>
@@ -9367,10 +9427,10 @@
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>25.19</v>
+        <v>25.02</v>
       </c>
       <c r="H254" s="2" t="n">
-        <v>14.98</v>
+        <v>14.47</v>
       </c>
       <c r="I254" s="2" t="n">
         <v>133</v>
@@ -9383,15 +9443,19 @@
           <t>CVIB2605</t>
         </is>
       </c>
-      <c r="B255" s="2" t="inlineStr"/>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>+3.08%</t>
+        </is>
+      </c>
       <c r="C255" s="2" t="n">
-        <v>650</v>
+        <v>670</v>
       </c>
       <c r="D255" s="2" t="n">
-        <v>100</v>
+        <v>50200</v>
       </c>
       <c r="E255" s="2" t="n">
-        <v>6.499999999999999e-05</v>
+        <v>0.033634</v>
       </c>
       <c r="F255" s="4" t="inlineStr">
         <is>
@@ -9399,10 +9463,10 @@
         </is>
       </c>
       <c r="G255" s="2" t="n">
-        <v>37.16</v>
+        <v>36.97</v>
       </c>
       <c r="H255" s="2" t="n">
-        <v>11.38</v>
+        <v>11.08</v>
       </c>
       <c r="I255" s="2" t="n">
         <v>148</v>
@@ -9415,19 +9479,15 @@
           <t>CVIB2606</t>
         </is>
       </c>
-      <c r="B256" s="2" t="inlineStr">
-        <is>
-          <t>+2.63%</t>
-        </is>
-      </c>
+      <c r="B256" s="2" t="inlineStr"/>
       <c r="C256" s="2" t="n">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="D256" s="2" t="n">
-        <v>1000</v>
+        <v>55000</v>
       </c>
       <c r="E256" s="2" t="n">
-        <v>0.00039</v>
+        <v>0.0209</v>
       </c>
       <c r="F256" s="4" t="inlineStr">
         <is>
@@ -9435,10 +9495,10 @@
         </is>
       </c>
       <c r="G256" s="2" t="n">
-        <v>23.51</v>
+        <v>22.96</v>
       </c>
       <c r="H256" s="2" t="n">
-        <v>18.97</v>
+        <v>19.54</v>
       </c>
       <c r="I256" s="2" t="n">
         <v>103</v>
@@ -9451,15 +9511,19 @@
           <t>CVIC2515</t>
         </is>
       </c>
-      <c r="B257" s="2" t="inlineStr"/>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>-4.69%</t>
+        </is>
+      </c>
       <c r="C257" s="2" t="n">
-        <v>24750</v>
+        <v>23590</v>
       </c>
       <c r="D257" s="2" t="n">
-        <v/>
+        <v>300</v>
       </c>
       <c r="E257" s="2" t="n">
-        <v/>
+        <v>0.007077</v>
       </c>
       <c r="F257" s="3" t="inlineStr">
         <is>
@@ -9467,10 +9531,10 @@
         </is>
       </c>
       <c r="G257" s="2" t="n">
-        <v>3.12</v>
+        <v>4.01</v>
       </c>
       <c r="H257" s="2" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="I257" s="2" t="n">
         <v>47</v>
@@ -9499,10 +9563,10 @@
         </is>
       </c>
       <c r="G258" s="2" t="n">
-        <v>4.75</v>
+        <v>7.91</v>
       </c>
       <c r="H258" s="2" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="I258" s="2" t="n">
         <v>113</v>
@@ -9517,17 +9581,17 @@
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>-3.31%</t>
+          <t>-11.57%</t>
         </is>
       </c>
       <c r="C259" s="2" t="n">
-        <v>1170</v>
+        <v>1070</v>
       </c>
       <c r="D259" s="2" t="n">
-        <v>41000</v>
+        <v>107200</v>
       </c>
       <c r="E259" s="2" t="n">
-        <v>0.04797</v>
+        <v>0.114704</v>
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
@@ -9535,10 +9599,10 @@
         </is>
       </c>
       <c r="G259" s="2" t="n">
-        <v>0.19</v>
+        <v>2.26</v>
       </c>
       <c r="H259" s="2" t="n">
-        <v>9.18</v>
+        <v>9.74</v>
       </c>
       <c r="I259" s="2" t="n">
         <v>6</v>
@@ -9553,17 +9617,17 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>-14.68%</t>
+          <t>-11.93%</t>
         </is>
       </c>
       <c r="C260" s="2" t="n">
-        <v>930</v>
+        <v>960</v>
       </c>
       <c r="D260" s="2" t="n">
-        <v>24300</v>
+        <v>35100</v>
       </c>
       <c r="E260" s="2" t="n">
-        <v>0.022599</v>
+        <v>0.033696</v>
       </c>
       <c r="F260" s="4" t="inlineStr">
         <is>
@@ -9571,10 +9635,10 @@
         </is>
       </c>
       <c r="G260" s="2" t="n">
-        <v>24.53</v>
+        <v>28.58</v>
       </c>
       <c r="H260" s="2" t="n">
-        <v>11.55</v>
+        <v>10.86</v>
       </c>
       <c r="I260" s="2" t="n">
         <v>78</v>
@@ -9589,17 +9653,17 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>-3.15%</t>
         </is>
       </c>
       <c r="C261" s="2" t="n">
-        <v>1260</v>
+        <v>1230</v>
       </c>
       <c r="D261" s="2" t="n">
-        <v>21800</v>
+        <v>25600</v>
       </c>
       <c r="E261" s="2" t="n">
-        <v>0.027468</v>
+        <v>0.031488</v>
       </c>
       <c r="F261" s="4" t="inlineStr">
         <is>
@@ -9607,10 +9671,10 @@
         </is>
       </c>
       <c r="G261" s="2" t="n">
-        <v>28.49</v>
+        <v>32.08</v>
       </c>
       <c r="H261" s="2" t="n">
-        <v>8.52</v>
+        <v>8.48</v>
       </c>
       <c r="I261" s="2" t="n">
         <v>98</v>
@@ -9625,17 +9689,17 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-8.22%</t>
         </is>
       </c>
       <c r="C262" s="2" t="n">
-        <v>1450</v>
+        <v>1340</v>
       </c>
       <c r="D262" s="2" t="n">
-        <v>233200</v>
+        <v>260700</v>
       </c>
       <c r="E262" s="2" t="n">
-        <v>0.33814</v>
+        <v>0.349338</v>
       </c>
       <c r="F262" s="4" t="inlineStr">
         <is>
@@ -9643,10 +9707,10 @@
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>31.19</v>
+        <v>34.1</v>
       </c>
       <c r="H262" s="2" t="n">
-        <v>7.41</v>
+        <v>7.78</v>
       </c>
       <c r="I262" s="2" t="n">
         <v>121</v>
@@ -9661,17 +9725,17 @@
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>-18.52%</t>
+          <t>-5.56%</t>
         </is>
       </c>
       <c r="C263" s="2" t="n">
-        <v>440</v>
+        <v>510</v>
       </c>
       <c r="D263" s="2" t="n">
-        <v>129700</v>
+        <v>272500</v>
       </c>
       <c r="E263" s="2" t="n">
-        <v>0.057068</v>
+        <v>0.138975</v>
       </c>
       <c r="F263" s="4" t="inlineStr">
         <is>
@@ -9679,10 +9743,10 @@
         </is>
       </c>
       <c r="G263" s="2" t="n">
-        <v>17.95</v>
+        <v>22.19</v>
       </c>
       <c r="H263" s="2" t="n">
-        <v>24.41</v>
+        <v>20.44</v>
       </c>
       <c r="I263" s="2" t="n">
         <v>33</v>
@@ -9695,15 +9759,19 @@
           <t>CVIC2606</t>
         </is>
       </c>
-      <c r="B264" s="2" t="inlineStr"/>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>-3.33%</t>
+        </is>
+      </c>
       <c r="C264" s="2" t="n">
-        <v>900</v>
+        <v>870</v>
       </c>
       <c r="D264" s="2" t="n">
-        <v/>
+        <v>6400</v>
       </c>
       <c r="E264" s="2" t="n">
-        <v/>
+        <v>0.005568</v>
       </c>
       <c r="F264" s="4" t="inlineStr">
         <is>
@@ -9711,10 +9779,10 @@
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>23.27</v>
+        <v>26.71</v>
       </c>
       <c r="H264" s="2" t="n">
-        <v>11.93</v>
+        <v>11.98</v>
       </c>
       <c r="I264" s="2" t="n">
         <v>55</v>
@@ -9729,17 +9797,17 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>+0.65%</t>
+          <t>-5.81%</t>
         </is>
       </c>
       <c r="C265" s="2" t="n">
-        <v>3120</v>
+        <v>2920</v>
       </c>
       <c r="D265" s="2" t="n">
-        <v>34900</v>
+        <v>176100</v>
       </c>
       <c r="E265" s="2" t="n">
-        <v>0.108888</v>
+        <v>0.514212</v>
       </c>
       <c r="F265" s="4" t="inlineStr">
         <is>
@@ -9747,10 +9815,10 @@
         </is>
       </c>
       <c r="G265" s="2" t="n">
-        <v>33.82</v>
+        <v>36.71</v>
       </c>
       <c r="H265" s="2" t="n">
-        <v>5.74</v>
+        <v>5.95</v>
       </c>
       <c r="I265" s="2" t="n">
         <v>168</v>
@@ -9772,10 +9840,10 @@
         <v>10</v>
       </c>
       <c r="D266" s="2" t="n">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="E266" s="2" t="n">
-        <v>3.2e-05</v>
+        <v>3.3e-05</v>
       </c>
       <c r="F266" s="4" t="inlineStr">
         <is>
@@ -9783,10 +9851,10 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>34.11</v>
+        <v>34.96</v>
       </c>
       <c r="H266" s="2" t="n">
-        <v>820.99</v>
+        <v>815.79</v>
       </c>
       <c r="I266" s="2" t="n">
         <v>6</v>
@@ -9799,19 +9867,15 @@
           <t>CVJC2602</t>
         </is>
       </c>
-      <c r="B267" s="2" t="inlineStr">
-        <is>
-          <t>-14.29%</t>
-        </is>
-      </c>
+      <c r="B267" s="2" t="inlineStr"/>
       <c r="C267" s="2" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="D267" s="2" t="n">
-        <v>89000</v>
+        <v>89100</v>
       </c>
       <c r="E267" s="2" t="n">
-        <v>0.0267</v>
+        <v>0.031185</v>
       </c>
       <c r="F267" s="4" t="inlineStr">
         <is>
@@ -9819,10 +9883,10 @@
         </is>
       </c>
       <c r="G267" s="2" t="n">
-        <v>24.2</v>
+        <v>25.61</v>
       </c>
       <c r="H267" s="2" t="n">
-        <v>27.37</v>
+        <v>23.31</v>
       </c>
       <c r="I267" s="2" t="n">
         <v>55</v>
@@ -9835,19 +9899,15 @@
           <t>CVJC2603</t>
         </is>
       </c>
-      <c r="B268" s="2" t="inlineStr">
-        <is>
-          <t>+1.72%</t>
-        </is>
-      </c>
+      <c r="B268" s="2" t="inlineStr"/>
       <c r="C268" s="2" t="n">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="D268" s="2" t="n">
-        <v>110300</v>
+        <v>125500</v>
       </c>
       <c r="E268" s="2" t="n">
-        <v>0.065077</v>
+        <v>0.07278999999999999</v>
       </c>
       <c r="F268" s="4" t="inlineStr">
         <is>
@@ -9855,10 +9915,10 @@
         </is>
       </c>
       <c r="G268" s="2" t="n">
-        <v>32.45</v>
+        <v>33.17</v>
       </c>
       <c r="H268" s="2" t="n">
-        <v>13.92</v>
+        <v>14.07</v>
       </c>
       <c r="I268" s="2" t="n">
         <v>98</v>
@@ -9871,19 +9931,15 @@
           <t>CVJC2604</t>
         </is>
       </c>
-      <c r="B269" s="2" t="inlineStr">
-        <is>
-          <t>+2.27%</t>
-        </is>
-      </c>
+      <c r="B269" s="2" t="inlineStr"/>
       <c r="C269" s="2" t="n">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="D269" s="2" t="n">
-        <v>600</v>
+        <v>2100</v>
       </c>
       <c r="E269" s="2" t="n">
-        <v>0.00027</v>
+        <v>0.000924</v>
       </c>
       <c r="F269" s="4" t="inlineStr">
         <is>
@@ -9891,10 +9947,10 @@
         </is>
       </c>
       <c r="G269" s="2" t="n">
-        <v>27.89</v>
+        <v>28.58</v>
       </c>
       <c r="H269" s="2" t="n">
-        <v>18.25</v>
+        <v>18.55</v>
       </c>
       <c r="I269" s="2" t="n">
         <v>78</v>
@@ -9909,17 +9965,17 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>+5.26%</t>
+          <t>+3.16%</t>
         </is>
       </c>
       <c r="C270" s="2" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="D270" s="2" t="n">
-        <v>122100</v>
+        <v>611200</v>
       </c>
       <c r="E270" s="2" t="n">
-        <v>0.1221</v>
+        <v>0.598976</v>
       </c>
       <c r="F270" s="3" t="inlineStr">
         <is>
@@ -9927,10 +9983,10 @@
         </is>
       </c>
       <c r="G270" s="2" t="n">
-        <v>8.529999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="H270" s="2" t="n">
-        <v>6.74</v>
+        <v>6.84</v>
       </c>
       <c r="I270" s="2" t="n">
         <v>84</v>
@@ -9943,19 +9999,15 @@
           <t>CVNM2601</t>
         </is>
       </c>
-      <c r="B271" s="2" t="inlineStr">
-        <is>
-          <t>+7.27%</t>
-        </is>
-      </c>
+      <c r="B271" s="2" t="inlineStr"/>
       <c r="C271" s="2" t="n">
-        <v>1180</v>
+        <v>1100</v>
       </c>
       <c r="D271" s="2" t="n">
-        <v>3000</v>
+        <v>50100</v>
       </c>
       <c r="E271" s="2" t="n">
-        <v>0.00354</v>
+        <v>0.05511</v>
       </c>
       <c r="F271" s="2" t="inlineStr">
         <is>
@@ -9963,10 +10015,10 @@
         </is>
       </c>
       <c r="G271" s="2" t="n">
-        <v>8.56</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="H271" s="2" t="n">
-        <v>10.91</v>
+        <v>11.65</v>
       </c>
       <c r="I271" s="2" t="n">
         <v>98</v>
@@ -9988,10 +10040,10 @@
         <v>820</v>
       </c>
       <c r="D272" s="2" t="n">
-        <v>59300</v>
+        <v>80900</v>
       </c>
       <c r="E272" s="2" t="n">
-        <v>0.048626</v>
+        <v>0.06633799999999999</v>
       </c>
       <c r="F272" s="2" t="inlineStr">
         <is>
@@ -9999,10 +10051,10 @@
         </is>
       </c>
       <c r="G272" s="2" t="n">
-        <v>9.59</v>
+        <v>10.12</v>
       </c>
       <c r="H272" s="2" t="n">
-        <v>9.82</v>
+        <v>9.77</v>
       </c>
       <c r="I272" s="2" t="n">
         <v>107</v>
@@ -10020,10 +10072,10 @@
         <v>10</v>
       </c>
       <c r="D273" s="2" t="n">
-        <v>6100</v>
+        <v>6200</v>
       </c>
       <c r="E273" s="2" t="n">
-        <v>6.1e-05</v>
+        <v>6.2e-05</v>
       </c>
       <c r="F273" s="4" t="inlineStr">
         <is>
@@ -10031,10 +10083,10 @@
         </is>
       </c>
       <c r="G273" s="2" t="n">
-        <v>30.58</v>
+        <v>31.21</v>
       </c>
       <c r="H273" s="2" t="n">
-        <v>643.88</v>
+        <v>640.78</v>
       </c>
       <c r="I273" s="2" t="n">
         <v>6</v>
@@ -10047,26 +10099,30 @@
           <t>CVNM2605</t>
         </is>
       </c>
-      <c r="B274" s="2" t="inlineStr"/>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>-5.41%</t>
+        </is>
+      </c>
       <c r="C274" s="2" t="n">
-        <v>740</v>
+        <v>700</v>
       </c>
       <c r="D274" s="2" t="n">
-        <v>204100</v>
+        <v>743500</v>
       </c>
       <c r="E274" s="2" t="n">
-        <v>0.151034</v>
-      </c>
-      <c r="F274" s="2" t="inlineStr">
-        <is>
-          <t>ATM</t>
+        <v>0.52045</v>
+      </c>
+      <c r="F274" s="4" t="inlineStr">
+        <is>
+          <t>OTM</t>
         </is>
       </c>
       <c r="G274" s="2" t="n">
-        <v>7.85</v>
+        <v>7.99</v>
       </c>
       <c r="H274" s="2" t="n">
-        <v>14.5</v>
+        <v>15.26</v>
       </c>
       <c r="I274" s="2" t="n">
         <v>133</v>
@@ -10088,10 +10144,10 @@
         <v>1410</v>
       </c>
       <c r="D275" s="2" t="n">
-        <v>2200</v>
+        <v>2700</v>
       </c>
       <c r="E275" s="2" t="n">
-        <v>0.003102</v>
+        <v>0.003807</v>
       </c>
       <c r="F275" s="4" t="inlineStr">
         <is>
@@ -10099,10 +10155,10 @@
         </is>
       </c>
       <c r="G275" s="2" t="n">
-        <v>17.83</v>
+        <v>18.4</v>
       </c>
       <c r="H275" s="2" t="n">
-        <v>6.52</v>
+        <v>6.49</v>
       </c>
       <c r="I275" s="2" t="n">
         <v>171</v>
@@ -10115,15 +10171,19 @@
           <t>CVNM2607</t>
         </is>
       </c>
-      <c r="B276" s="2" t="inlineStr"/>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>-1.67%</t>
+        </is>
+      </c>
       <c r="C276" s="2" t="n">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="D276" s="2" t="n">
-        <v>220300</v>
+        <v>251700</v>
       </c>
       <c r="E276" s="2" t="n">
-        <v>0.13218</v>
+        <v>0.148503</v>
       </c>
       <c r="F276" s="3" t="inlineStr">
         <is>
@@ -10131,10 +10191,10 @@
         </is>
       </c>
       <c r="G276" s="2" t="n">
-        <v>5.61</v>
+        <v>5.96</v>
       </c>
       <c r="H276" s="2" t="n">
-        <v>10.73</v>
+        <v>10.86</v>
       </c>
       <c r="I276" s="2" t="n">
         <v>63</v>
@@ -10156,10 +10216,10 @@
         <v>390</v>
       </c>
       <c r="D277" s="2" t="n">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="E277" s="2" t="n">
-        <v>3.9e-05</v>
+        <v>0.000429</v>
       </c>
       <c r="F277" s="4" t="inlineStr">
         <is>
@@ -10167,10 +10227,10 @@
         </is>
       </c>
       <c r="G277" s="2" t="n">
-        <v>10.11</v>
+        <v>10.64</v>
       </c>
       <c r="H277" s="2" t="n">
-        <v>16.51</v>
+        <v>16.43</v>
       </c>
       <c r="I277" s="2" t="n">
         <v>33</v>
@@ -10203,10 +10263,10 @@
         </is>
       </c>
       <c r="G278" s="2" t="n">
-        <v>16.81</v>
+        <v>17.37</v>
       </c>
       <c r="H278" s="2" t="n">
-        <v>12.63</v>
+        <v>12.56</v>
       </c>
       <c r="I278" s="2" t="n">
         <v>78</v>
@@ -10221,17 +10281,17 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>+9.04%</t>
+          <t>-2.82%</t>
         </is>
       </c>
       <c r="C279" s="2" t="n">
-        <v>1930</v>
+        <v>1720</v>
       </c>
       <c r="D279" s="2" t="n">
-        <v>830300</v>
+        <v>1445900</v>
       </c>
       <c r="E279" s="2" t="n">
-        <v>1.602479</v>
+        <v>2.486948</v>
       </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
@@ -10239,10 +10299,10 @@
         </is>
       </c>
       <c r="G279" s="2" t="n">
-        <v>3.72</v>
+        <v>2.87</v>
       </c>
       <c r="H279" s="2" t="n">
-        <v>8.08</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="I279" s="2" t="n">
         <v>16</v>
@@ -10257,17 +10317,17 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>+8.63%</t>
+          <t>-9.35%</t>
         </is>
       </c>
       <c r="C280" s="2" t="n">
-        <v>1510</v>
+        <v>1260</v>
       </c>
       <c r="D280" s="2" t="n">
-        <v>256500</v>
+        <v>377900</v>
       </c>
       <c r="E280" s="2" t="n">
-        <v>0.387315</v>
+        <v>0.476154</v>
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
@@ -10275,10 +10335,10 @@
         </is>
       </c>
       <c r="G280" s="2" t="n">
-        <v>4.23</v>
+        <v>3.12</v>
       </c>
       <c r="H280" s="2" t="n">
-        <v>10.33</v>
+        <v>12.32</v>
       </c>
       <c r="I280" s="2" t="n">
         <v>16</v>
@@ -10293,17 +10353,17 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>+10.75%</t>
+          <t>-6.45%</t>
         </is>
       </c>
       <c r="C281" s="2" t="n">
-        <v>1030</v>
+        <v>870</v>
       </c>
       <c r="D281" s="2" t="n">
-        <v>236200</v>
+        <v>376700</v>
       </c>
       <c r="E281" s="2" t="n">
-        <v>0.243286</v>
+        <v>0.327729</v>
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
@@ -10311,10 +10371,10 @@
         </is>
       </c>
       <c r="G281" s="2" t="n">
-        <v>4.36</v>
+        <v>3.83</v>
       </c>
       <c r="H281" s="2" t="n">
-        <v>15.15</v>
+        <v>17.84</v>
       </c>
       <c r="I281" s="2" t="n">
         <v>16</v>
@@ -10329,17 +10389,17 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>-5.53%</t>
+          <t>-8.42%</t>
         </is>
       </c>
       <c r="C282" s="2" t="n">
-        <v>3590</v>
+        <v>3480</v>
       </c>
       <c r="D282" s="2" t="n">
-        <v>10100</v>
+        <v>370100</v>
       </c>
       <c r="E282" s="2" t="n">
-        <v>0.036259</v>
+        <v>1.287948</v>
       </c>
       <c r="F282" s="3" t="inlineStr">
         <is>
@@ -10350,7 +10410,7 @@
         <v>6.82</v>
       </c>
       <c r="H282" s="2" t="n">
-        <v>5.97</v>
+        <v>6.13</v>
       </c>
       <c r="I282" s="2" t="n">
         <v>90</v>
@@ -10365,17 +10425,17 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>+3.51%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="C283" s="2" t="n">
-        <v>3240</v>
+        <v>3150</v>
       </c>
       <c r="D283" s="2" t="n">
-        <v>30600</v>
+        <v>33800</v>
       </c>
       <c r="E283" s="2" t="n">
-        <v>0.099144</v>
+        <v>0.10647</v>
       </c>
       <c r="F283" s="3" t="inlineStr">
         <is>
@@ -10383,10 +10443,10 @@
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>10.22</v>
+        <v>10.19</v>
       </c>
       <c r="H283" s="2" t="n">
-        <v>4.96</v>
+        <v>5.08</v>
       </c>
       <c r="I283" s="2" t="n">
         <v>154</v>
@@ -10401,17 +10461,17 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>+4.36%</t>
+          <t>+2.49%</t>
         </is>
       </c>
       <c r="C284" s="2" t="n">
-        <v>3350</v>
+        <v>3290</v>
       </c>
       <c r="D284" s="2" t="n">
-        <v>8500</v>
+        <v>25700</v>
       </c>
       <c r="E284" s="2" t="n">
-        <v>0.028475</v>
+        <v>0.084553</v>
       </c>
       <c r="F284" s="3" t="inlineStr">
         <is>
@@ -10419,10 +10479,10 @@
         </is>
       </c>
       <c r="G284" s="2" t="n">
-        <v>14.18</v>
+        <v>14.25</v>
       </c>
       <c r="H284" s="2" t="n">
-        <v>3.73</v>
+        <v>3.78</v>
       </c>
       <c r="I284" s="2" t="n">
         <v>186</v>
@@ -10437,17 +10497,17 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>-3.85%</t>
         </is>
       </c>
       <c r="C285" s="2" t="n">
-        <v>770</v>
+        <v>750</v>
       </c>
       <c r="D285" s="2" t="n">
-        <v>10100</v>
+        <v>23200</v>
       </c>
       <c r="E285" s="2" t="n">
-        <v>0.007777</v>
+        <v>0.0174</v>
       </c>
       <c r="F285" s="3" t="inlineStr">
         <is>
@@ -10455,10 +10515,10 @@
         </is>
       </c>
       <c r="G285" s="2" t="n">
-        <v>8.49</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H285" s="2" t="n">
-        <v>8.1</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="I285" s="2" t="n">
         <v>103</v>
@@ -10473,17 +10533,17 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>+7.69%</t>
+          <t>+15.38%</t>
         </is>
       </c>
       <c r="C286" s="2" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="D286" s="2" t="n">
-        <v>66100</v>
+        <v>192300</v>
       </c>
       <c r="E286" s="2" t="n">
-        <v>0.018508</v>
+        <v>0.05769</v>
       </c>
       <c r="F286" s="4" t="inlineStr">
         <is>
@@ -10491,10 +10551,10 @@
         </is>
       </c>
       <c r="G286" s="2" t="n">
-        <v>47.54</v>
+        <v>45.2</v>
       </c>
       <c r="H286" s="2" t="n">
-        <v>30.78</v>
+        <v>29.23</v>
       </c>
       <c r="I286" s="2" t="n">
         <v>84</v>
@@ -10509,17 +10569,17 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>-23.81%</t>
+          <t>+4.76%</t>
         </is>
       </c>
       <c r="C287" s="2" t="n">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="D287" s="2" t="n">
-        <v>1100</v>
+        <v>8900</v>
       </c>
       <c r="E287" s="2" t="n">
-        <v>0.000176</v>
+        <v>0.001958</v>
       </c>
       <c r="F287" s="4" t="inlineStr">
         <is>
@@ -10527,10 +10587,10 @@
         </is>
       </c>
       <c r="G287" s="2" t="n">
-        <v>34</v>
+        <v>32.58</v>
       </c>
       <c r="H287" s="2" t="n">
-        <v>40.39</v>
+        <v>29.9</v>
       </c>
       <c r="I287" s="2" t="n">
         <v>47</v>
@@ -10545,17 +10605,17 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+9.09%</t>
         </is>
       </c>
       <c r="C288" s="2" t="n">
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="D288" s="2" t="n">
-        <v>200</v>
+        <v>8600</v>
       </c>
       <c r="E288" s="2" t="n">
-        <v>9.000000000000001e-05</v>
+        <v>0.004128</v>
       </c>
       <c r="F288" s="4" t="inlineStr">
         <is>
@@ -10563,10 +10623,10 @@
         </is>
       </c>
       <c r="G288" s="2" t="n">
-        <v>42.35</v>
+        <v>40.33</v>
       </c>
       <c r="H288" s="2" t="n">
-        <v>14.36</v>
+        <v>13.7</v>
       </c>
       <c r="I288" s="2" t="n">
         <v>113</v>
@@ -10581,17 +10641,17 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>-2.94%</t>
+          <t>-17.65%</t>
         </is>
       </c>
       <c r="C289" s="2" t="n">
-        <v>330</v>
+        <v>280</v>
       </c>
       <c r="D289" s="2" t="n">
-        <v>2400</v>
+        <v>14500</v>
       </c>
       <c r="E289" s="2" t="n">
-        <v>0.000792</v>
+        <v>0.00406</v>
       </c>
       <c r="F289" s="4" t="inlineStr">
         <is>
@@ -10599,10 +10659,10 @@
         </is>
       </c>
       <c r="G289" s="2" t="n">
-        <v>18.6</v>
+        <v>16.16</v>
       </c>
       <c r="H289" s="2" t="n">
-        <v>39.17</v>
+        <v>46.98</v>
       </c>
       <c r="I289" s="2" t="n">
         <v>28</v>
@@ -10617,17 +10677,17 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>+9.52%</t>
+          <t>+11.11%</t>
         </is>
       </c>
       <c r="C290" s="2" t="n">
-        <v>690</v>
+        <v>700</v>
       </c>
       <c r="D290" s="2" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="E290" s="2" t="n">
-        <v>0.001035</v>
+        <v>0.0014</v>
       </c>
       <c r="F290" s="4" t="inlineStr">
         <is>
@@ -10635,10 +10695,10 @@
         </is>
       </c>
       <c r="G290" s="2" t="n">
-        <v>25.26</v>
+        <v>23.15</v>
       </c>
       <c r="H290" s="2" t="n">
-        <v>18.73</v>
+        <v>18.79</v>
       </c>
       <c r="I290" s="2" t="n">
         <v>93</v>
@@ -10653,17 +10713,17 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>+16.67%</t>
+          <t>+12.50%</t>
         </is>
       </c>
       <c r="C291" s="2" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="D291" s="2" t="n">
-        <v>43100</v>
+        <v>204200</v>
       </c>
       <c r="E291" s="2" t="n">
-        <v>0.012068</v>
+        <v>0.055134</v>
       </c>
       <c r="F291" s="4" t="inlineStr">
         <is>
@@ -10671,10 +10731,10 @@
         </is>
       </c>
       <c r="G291" s="2" t="n">
-        <v>18.21</v>
+        <v>16.08</v>
       </c>
       <c r="H291" s="2" t="n">
-        <v>46.16</v>
+        <v>48.72</v>
       </c>
       <c r="I291" s="2" t="n">
         <v>34</v>
@@ -10692,10 +10752,10 @@
         <v>10</v>
       </c>
       <c r="D292" s="2" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E292" s="2" t="n">
-        <v>2e-06</v>
+        <v>3e-06</v>
       </c>
       <c r="F292" s="4" t="inlineStr">
         <is>
@@ -10703,10 +10763,10 @@
         </is>
       </c>
       <c r="G292" s="2" t="n">
-        <v>33.87</v>
+        <v>31.54</v>
       </c>
       <c r="H292" s="2" t="n">
-        <v>646.28</v>
+        <v>657.73</v>
       </c>
       <c r="I292" s="2" t="n">
         <v>6</v>
@@ -10728,10 +10788,10 @@
         <v>740</v>
       </c>
       <c r="D293" s="2" t="n">
-        <v>161500</v>
+        <v>668400</v>
       </c>
       <c r="E293" s="2" t="n">
-        <v>0.11951</v>
+        <v>0.494616</v>
       </c>
       <c r="F293" s="4" t="inlineStr">
         <is>
@@ -10739,10 +10799,10 @@
         </is>
       </c>
       <c r="G293" s="2" t="n">
-        <v>21.77</v>
+        <v>19.65</v>
       </c>
       <c r="H293" s="2" t="n">
-        <v>17.47</v>
+        <v>17.78</v>
       </c>
       <c r="I293" s="2" t="n">
         <v>133</v>
@@ -10755,15 +10815,19 @@
           <t>CVPB2609</t>
         </is>
       </c>
-      <c r="B294" s="2" t="inlineStr"/>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>+4.04%</t>
+        </is>
+      </c>
       <c r="C294" s="2" t="n">
-        <v>990</v>
+        <v>1030</v>
       </c>
       <c r="D294" s="2" t="n">
-        <v/>
+        <v>100</v>
       </c>
       <c r="E294" s="2" t="n">
-        <v/>
+        <v>0.000103</v>
       </c>
       <c r="F294" s="4" t="inlineStr">
         <is>
@@ -10771,10 +10835,10 @@
         </is>
       </c>
       <c r="G294" s="2" t="n">
-        <v>31.36</v>
+        <v>29.69</v>
       </c>
       <c r="H294" s="2" t="n">
-        <v>6.53</v>
+        <v>6.39</v>
       </c>
       <c r="I294" s="2" t="n">
         <v>171</v>
@@ -10789,17 +10853,17 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>+6.25%</t>
+          <t>+12.50%</t>
         </is>
       </c>
       <c r="C295" s="2" t="n">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="D295" s="2" t="n">
-        <v>5000</v>
+        <v>6100</v>
       </c>
       <c r="E295" s="2" t="n">
-        <v>0.0017</v>
+        <v>0.002196</v>
       </c>
       <c r="F295" s="4" t="inlineStr">
         <is>
@@ -10807,10 +10871,10 @@
         </is>
       </c>
       <c r="G295" s="2" t="n">
-        <v>17.44</v>
+        <v>15.7</v>
       </c>
       <c r="H295" s="2" t="n">
-        <v>19.01</v>
+        <v>18.27</v>
       </c>
       <c r="I295" s="2" t="n">
         <v>63</v>
@@ -10825,17 +10889,17 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>+6.35%</t>
+          <t>+15.87%</t>
         </is>
       </c>
       <c r="C296" s="2" t="n">
-        <v>670</v>
+        <v>730</v>
       </c>
       <c r="D296" s="2" t="n">
-        <v>27600</v>
+        <v>51300</v>
       </c>
       <c r="E296" s="2" t="n">
-        <v>0.018492</v>
+        <v>0.037449</v>
       </c>
       <c r="F296" s="4" t="inlineStr">
         <is>
@@ -10843,10 +10907,10 @@
         </is>
       </c>
       <c r="G296" s="2" t="n">
-        <v>22.36</v>
+        <v>21.16</v>
       </c>
       <c r="H296" s="2" t="n">
-        <v>9.48</v>
+        <v>8.85</v>
       </c>
       <c r="I296" s="2" t="n">
         <v>163</v>
@@ -10861,17 +10925,17 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>+8.70%</t>
+          <t>+26.09%</t>
         </is>
       </c>
       <c r="C297" s="2" t="n">
-        <v>250</v>
+        <v>290</v>
       </c>
       <c r="D297" s="2" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E297" s="2" t="n">
-        <v>2.5e-05</v>
+        <v>8.7e-05</v>
       </c>
       <c r="F297" s="4" t="inlineStr">
         <is>
@@ -10879,10 +10943,10 @@
         </is>
       </c>
       <c r="G297" s="2" t="n">
-        <v>30.9</v>
+        <v>29.4</v>
       </c>
       <c r="H297" s="2" t="n">
-        <v>20.32</v>
+        <v>17.83</v>
       </c>
       <c r="I297" s="2" t="n">
         <v>33</v>
@@ -10911,10 +10975,10 @@
         </is>
       </c>
       <c r="G298" s="2" t="n">
-        <v>34.6</v>
+        <v>32.26</v>
       </c>
       <c r="H298" s="2" t="n">
-        <v>19.54</v>
+        <v>19.88</v>
       </c>
       <c r="I298" s="2" t="n">
         <v>78</v>
@@ -10929,17 +10993,17 @@
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>-3.23%</t>
+          <t>+45.16%</t>
         </is>
       </c>
       <c r="C299" s="2" t="n">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="D299" s="2" t="n">
-        <v>3800</v>
+        <v>664100</v>
       </c>
       <c r="E299" s="2" t="n">
-        <v>0.00114</v>
+        <v>0.298845</v>
       </c>
       <c r="F299" s="4" t="inlineStr">
         <is>
@@ -10947,10 +11011,10 @@
         </is>
       </c>
       <c r="G299" s="2" t="n">
-        <v>37.62</v>
+        <v>38.13</v>
       </c>
       <c r="H299" s="2" t="n">
-        <v>16.93</v>
+        <v>11.49</v>
       </c>
       <c r="I299" s="2" t="n">
         <v>98</v>
@@ -10965,17 +11029,17 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>+1.41%</t>
+          <t>+5.63%</t>
         </is>
       </c>
       <c r="C300" s="2" t="n">
-        <v>720</v>
+        <v>750</v>
       </c>
       <c r="D300" s="2" t="n">
-        <v>172500</v>
+        <v>1012700</v>
       </c>
       <c r="E300" s="2" t="n">
-        <v>0.1242</v>
+        <v>0.759525</v>
       </c>
       <c r="F300" s="4" t="inlineStr">
         <is>
@@ -10983,10 +11047,10 @@
         </is>
       </c>
       <c r="G300" s="2" t="n">
-        <v>17.87</v>
+        <v>16.05</v>
       </c>
       <c r="H300" s="2" t="n">
-        <v>17.64</v>
+        <v>17.23</v>
       </c>
       <c r="I300" s="2" t="n">
         <v>135</v>
@@ -11001,17 +11065,17 @@
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>+8.55%</t>
+          <t>+13.82%</t>
         </is>
       </c>
       <c r="C301" s="2" t="n">
-        <v>1650</v>
+        <v>1730</v>
       </c>
       <c r="D301" s="2" t="n">
-        <v>36300</v>
+        <v>49200</v>
       </c>
       <c r="E301" s="2" t="n">
-        <v>0.059895</v>
+        <v>0.085116</v>
       </c>
       <c r="F301" s="3" t="inlineStr">
         <is>
@@ -11019,10 +11083,10 @@
         </is>
       </c>
       <c r="G301" s="2" t="n">
-        <v>11.42</v>
+        <v>10.1</v>
       </c>
       <c r="H301" s="2" t="n">
-        <v>7.7</v>
+        <v>7.47</v>
       </c>
       <c r="I301" s="2" t="n">
         <v>90</v>
@@ -11037,28 +11101,28 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>+4.38%</t>
         </is>
       </c>
       <c r="C302" s="2" t="n">
-        <v>1360</v>
+        <v>1430</v>
       </c>
       <c r="D302" s="2" t="n">
-        <v>65400</v>
+        <v>370000</v>
       </c>
       <c r="E302" s="2" t="n">
-        <v>0.088944</v>
-      </c>
-      <c r="F302" s="2" t="inlineStr">
-        <is>
-          <t>ATM</t>
+        <v>0.5291</v>
+      </c>
+      <c r="F302" s="3" t="inlineStr">
+        <is>
+          <t>ITM</t>
         </is>
       </c>
       <c r="G302" s="2" t="n">
-        <v>16.46</v>
+        <v>15.24</v>
       </c>
       <c r="H302" s="2" t="n">
-        <v>6.23</v>
+        <v>6.03</v>
       </c>
       <c r="I302" s="2" t="n">
         <v>154</v>
@@ -11073,17 +11137,17 @@
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>+4.62%</t>
+          <t>+9.23%</t>
         </is>
       </c>
       <c r="C303" s="2" t="n">
-        <v>2040</v>
+        <v>2130</v>
       </c>
       <c r="D303" s="2" t="n">
-        <v>309200</v>
+        <v>616700</v>
       </c>
       <c r="E303" s="2" t="n">
-        <v>0.630768</v>
+        <v>1.313571</v>
       </c>
       <c r="F303" s="4" t="inlineStr">
         <is>
@@ -11091,10 +11155,10 @@
         </is>
       </c>
       <c r="G303" s="2" t="n">
-        <v>23.15</v>
+        <v>21.7</v>
       </c>
       <c r="H303" s="2" t="n">
-        <v>6.23</v>
+        <v>6.07</v>
       </c>
       <c r="I303" s="2" t="n">
         <v>186</v>
@@ -11109,17 +11173,17 @@
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>+12.73%</t>
+          <t>+5.45%</t>
         </is>
       </c>
       <c r="C304" s="2" t="n">
-        <v>620</v>
+        <v>580</v>
       </c>
       <c r="D304" s="2" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="E304" s="2" t="n">
-        <v>0.00124</v>
+        <v>0.00232</v>
       </c>
       <c r="F304" s="4" t="inlineStr">
         <is>
@@ -11127,10 +11191,10 @@
         </is>
       </c>
       <c r="G304" s="2" t="n">
-        <v>21.5</v>
+        <v>18.92</v>
       </c>
       <c r="H304" s="2" t="n">
-        <v>13.66</v>
+        <v>14.86</v>
       </c>
       <c r="I304" s="2" t="n">
         <v>103</v>
@@ -11145,17 +11209,17 @@
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>+2.17%</t>
+          <t>+15.22%</t>
         </is>
       </c>
       <c r="C305" s="2" t="n">
-        <v>470</v>
+        <v>530</v>
       </c>
       <c r="D305" s="2" t="n">
-        <v>20000</v>
+        <v>21300</v>
       </c>
       <c r="E305" s="2" t="n">
-        <v>0.0094</v>
+        <v>0.011289</v>
       </c>
       <c r="F305" s="4" t="inlineStr">
         <is>
@@ -11163,10 +11227,10 @@
         </is>
       </c>
       <c r="G305" s="2" t="n">
-        <v>17.64</v>
+        <v>16.52</v>
       </c>
       <c r="H305" s="2" t="n">
-        <v>13.51</v>
+        <v>12.19</v>
       </c>
       <c r="I305" s="2" t="n">
         <v>103</v>
@@ -11181,17 +11245,17 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>+7.46%</t>
+          <t>+10.45%</t>
         </is>
       </c>
       <c r="C306" s="2" t="n">
-        <v>720</v>
+        <v>740</v>
       </c>
       <c r="D306" s="2" t="n">
-        <v>2500</v>
+        <v>33000</v>
       </c>
       <c r="E306" s="2" t="n">
-        <v>0.0018</v>
+        <v>0.02442</v>
       </c>
       <c r="F306" s="4" t="inlineStr">
         <is>
@@ -11199,10 +11263,10 @@
         </is>
       </c>
       <c r="G306" s="2" t="n">
-        <v>21.57</v>
+        <v>19.77</v>
       </c>
       <c r="H306" s="2" t="n">
-        <v>8.82</v>
+        <v>8.73</v>
       </c>
       <c r="I306" s="2" t="n">
         <v>167</v>
@@ -11220,10 +11284,10 @@
         <v>260</v>
       </c>
       <c r="D307" s="2" t="n">
-        <v>1800</v>
+        <v>10600</v>
       </c>
       <c r="E307" s="2" t="n">
-        <v>0.000468</v>
+        <v>0.002756</v>
       </c>
       <c r="F307" s="4" t="inlineStr">
         <is>
@@ -11231,10 +11295,10 @@
         </is>
       </c>
       <c r="G307" s="2" t="n">
-        <v>86.09</v>
+        <v>85.36</v>
       </c>
       <c r="H307" s="2" t="n">
-        <v>25.34</v>
+        <v>25.44</v>
       </c>
       <c r="I307" s="2" t="n">
         <v>47</v>
@@ -11263,10 +11327,10 @@
         </is>
       </c>
       <c r="G308" s="2" t="n">
-        <v>94.20999999999999</v>
+        <v>93.45</v>
       </c>
       <c r="H308" s="2" t="n">
-        <v>15.69</v>
+        <v>15.75</v>
       </c>
       <c r="I308" s="2" t="n">
         <v>113</v>
@@ -11299,10 +11363,10 @@
         </is>
       </c>
       <c r="G309" s="2" t="n">
-        <v>45.97</v>
+        <v>45.4</v>
       </c>
       <c r="H309" s="2" t="n">
-        <v>329.41</v>
+        <v>330.7</v>
       </c>
       <c r="I309" s="2" t="n">
         <v>6</v>
@@ -11317,17 +11381,17 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>+4.31%</t>
+          <t>+2.59%</t>
         </is>
       </c>
       <c r="C310" s="2" t="n">
-        <v>1210</v>
+        <v>1190</v>
       </c>
       <c r="D310" s="2" t="n">
-        <v>76400</v>
+        <v>101600</v>
       </c>
       <c r="E310" s="2" t="n">
-        <v>0.092444</v>
+        <v>0.120904</v>
       </c>
       <c r="F310" s="4" t="inlineStr">
         <is>
@@ -11335,10 +11399,10 @@
         </is>
       </c>
       <c r="G310" s="2" t="n">
-        <v>31.41</v>
+        <v>30.67</v>
       </c>
       <c r="H310" s="2" t="n">
-        <v>7.26</v>
+        <v>7.41</v>
       </c>
       <c r="I310" s="2" t="n">
         <v>133</v>
@@ -11360,10 +11424,10 @@
         <v>490</v>
       </c>
       <c r="D311" s="2" t="n">
-        <v>15700</v>
+        <v>16000</v>
       </c>
       <c r="E311" s="2" t="n">
-        <v>0.007693</v>
+        <v>0.00784</v>
       </c>
       <c r="F311" s="4" t="inlineStr">
         <is>
@@ -11371,10 +11435,10 @@
         </is>
       </c>
       <c r="G311" s="2" t="n">
-        <v>45.9</v>
+        <v>45.33</v>
       </c>
       <c r="H311" s="2" t="n">
-        <v>10.76</v>
+        <v>10.8</v>
       </c>
       <c r="I311" s="2" t="n">
         <v>98</v>
@@ -11389,17 +11453,17 @@
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>+7.32%</t>
+          <t>+9.76%</t>
         </is>
       </c>
       <c r="C312" s="2" t="n">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="D312" s="2" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E312" s="2" t="n">
-        <v>4.4e-05</v>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="F312" s="4" t="inlineStr">
         <is>
@@ -11407,10 +11471,10 @@
         </is>
       </c>
       <c r="G312" s="2" t="n">
-        <v>50.48</v>
+        <v>50.08</v>
       </c>
       <c r="H312" s="2" t="n">
-        <v>11.98</v>
+        <v>11.76</v>
       </c>
       <c r="I312" s="2" t="n">
         <v>78</v>

--- a/docs/downloads/KetQuaGiaoDich_latest.xlsx
+++ b/docs/downloads/KetQuaGiaoDich_latest.xlsx
@@ -573,7 +573,7 @@
         <v>8.06</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
     </row>
@@ -609,7 +609,7 @@
         <v>328.36</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
     </row>
@@ -645,7 +645,7 @@
         <v>18.76</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
     </row>
@@ -677,7 +677,7 @@
         <v>38.63</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
     </row>
@@ -713,7 +713,7 @@
         <v>16.84</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
     </row>
@@ -749,7 +749,7 @@
         <v>29.19</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
     </row>
@@ -785,7 +785,7 @@
         <v>11.32</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
     </row>
@@ -821,7 +821,7 @@
         <v>12.51</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
     </row>
@@ -857,7 +857,7 @@
         <v>7.91</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
     </row>
@@ -893,7 +893,7 @@
         <v>8.01</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
     </row>
@@ -929,7 +929,7 @@
         <v>10.18</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
     </row>
@@ -961,7 +961,7 @@
         <v>21.02</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
     </row>
@@ -993,7 +993,7 @@
         <v>20.21</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
     </row>
@@ -1025,7 +1025,7 @@
         <v>13.83</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
     </row>
@@ -1061,7 +1061,7 @@
         <v>27.37</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
     </row>
@@ -1097,7 +1097,7 @@
         <v>437.98</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
     </row>
@@ -1129,7 +1129,7 @@
         <v>12.65</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
     </row>
@@ -1161,7 +1161,7 @@
         <v>6.15</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
     </row>
@@ -1197,7 +1197,7 @@
         <v>11.8</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
     </row>
@@ -1233,7 +1233,7 @@
         <v>12.72</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
     </row>
@@ -1269,7 +1269,7 @@
         <v>10.89</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
     </row>
@@ -1301,7 +1301,7 @@
         <v>850.29</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
     </row>
@@ -1337,7 +1337,7 @@
         <v>462.26</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
     </row>
@@ -1373,7 +1373,7 @@
         <v>23.71</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
     </row>
@@ -1409,7 +1409,7 @@
         <v>205.45</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
     </row>
@@ -1445,7 +1445,7 @@
         <v>30.82</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
     </row>
@@ -1481,7 +1481,7 @@
         <v>371.04</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
     </row>
@@ -1513,7 +1513,7 @@
         <v>37.1</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
     </row>
@@ -1549,7 +1549,7 @@
         <v>29.68</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
     </row>
@@ -1581,7 +1581,7 @@
         <v>371.04</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
     </row>
@@ -1613,7 +1613,7 @@
         <v>742.08</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
     </row>
@@ -1645,7 +1645,7 @@
         <v>23.19</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
     </row>
@@ -1681,7 +1681,7 @@
         <v>16.27</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
     </row>
@@ -1717,7 +1717,7 @@
         <v>5.9</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
     </row>
@@ -1753,7 +1753,7 @@
         <v>6.12</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
     </row>
@@ -1789,7 +1789,7 @@
         <v>19.26</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
     </row>
@@ -1825,7 +1825,7 @@
         <v>11.26</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
     </row>
@@ -1861,7 +1861,7 @@
         <v>7.21</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
     </row>
@@ -1897,7 +1897,7 @@
         <v>12.04</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
     </row>
@@ -1933,7 +1933,7 @@
         <v>10.64</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
     </row>
@@ -1969,7 +1969,7 @@
         <v>25.79</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
     </row>
@@ -2005,7 +2005,7 @@
         <v>75.20999999999999</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
     </row>
@@ -2037,7 +2037,7 @@
         <v>902.5</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
     </row>
@@ -2073,7 +2073,7 @@
         <v>7.97</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
     </row>
@@ -2109,7 +2109,7 @@
         <v>6.78</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
     </row>
@@ -2145,7 +2145,7 @@
         <v>6.78</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
     </row>
@@ -2181,7 +2181,7 @@
         <v>5.4</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
     </row>
@@ -2217,7 +2217,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
     </row>
@@ -2253,7 +2253,7 @@
         <v>7.47</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
     </row>
@@ -2289,7 +2289,7 @@
         <v>4.09</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
     </row>
@@ -2325,7 +2325,7 @@
         <v>4.52</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
     </row>
@@ -2361,7 +2361,7 @@
         <v>30.05</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
     </row>
@@ -2397,7 +2397,7 @@
         <v>6.43</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
     </row>
@@ -2433,7 +2433,7 @@
         <v>29.89</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
     </row>
@@ -2469,7 +2469,7 @@
         <v>5.19</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
     </row>
@@ -2505,7 +2505,7 @@
         <v>12.69</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
     </row>
@@ -2541,7 +2541,7 @@
         <v>9</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
     </row>
@@ -2577,7 +2577,7 @@
         <v>18.53</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
     </row>
@@ -2613,7 +2613,7 @@
         <v>10.22</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
     </row>
@@ -2649,7 +2649,7 @@
         <v>4.79</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
     </row>
@@ -2685,7 +2685,7 @@
         <v>3.34</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
     </row>
@@ -2717,7 +2717,7 @@
         <v>10.18</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
     </row>
@@ -2753,7 +2753,7 @@
         <v>8.42</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
     </row>
@@ -2789,7 +2789,7 @@
         <v>3.56</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
     </row>
@@ -2821,7 +2821,7 @@
         <v>4.51</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
     </row>
@@ -2857,7 +2857,7 @@
         <v>15.02</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
     </row>
@@ -2893,7 +2893,7 @@
         <v>1237.96</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
     </row>
@@ -2929,7 +2929,7 @@
         <v>16.96</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
     </row>
@@ -2965,7 +2965,7 @@
         <v>88.43000000000001</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
     </row>
@@ -3001,7 +3001,7 @@
         <v>19.97</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
     </row>
@@ -3037,7 +3037,7 @@
         <v>206.33</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
     </row>
@@ -3073,7 +3073,7 @@
         <v>19.34</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
     </row>
@@ -3105,7 +3105,7 @@
         <v>63.48</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
     </row>
@@ -3141,7 +3141,7 @@
         <v>16.29</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
     </row>
@@ -3177,7 +3177,7 @@
         <v>13.99</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
     </row>
@@ -3213,7 +3213,7 @@
         <v>95.23</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
     </row>
@@ -3249,7 +3249,7 @@
         <v>8.6</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
     </row>
@@ -3285,7 +3285,7 @@
         <v>14.39</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
     </row>
@@ -3317,7 +3317,7 @@
         <v>11.52</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
     </row>
@@ -3353,7 +3353,7 @@
         <v>44.22</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
     </row>
@@ -3389,7 +3389,7 @@
         <v>19.35</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
     </row>
@@ -3425,7 +3425,7 @@
         <v>14.17</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
     </row>
@@ -3461,7 +3461,7 @@
         <v>11.28</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
     </row>
@@ -3497,7 +3497,7 @@
         <v>13.81</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
     </row>
@@ -3533,7 +3533,7 @@
         <v>15.79</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
     </row>
@@ -3569,7 +3569,7 @@
         <v>27.62</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
     </row>
@@ -3601,7 +3601,7 @@
         <v>17.27</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
     </row>
@@ -3637,7 +3637,7 @@
         <v>1110</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
     </row>
@@ -3669,7 +3669,7 @@
         <v>1110</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
     </row>
@@ -3701,7 +3701,7 @@
         <v>1110</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
     </row>
@@ -3737,7 +3737,7 @@
         <v>18.73</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
     </row>
@@ -3773,7 +3773,7 @@
         <v>12.14</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
     </row>
@@ -3809,7 +3809,7 @@
         <v>8.630000000000001</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
     </row>
@@ -3845,7 +3845,7 @@
         <v>6.42</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
     </row>
@@ -3877,7 +3877,7 @@
         <v>10.83</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
     </row>
@@ -3909,7 +3909,7 @@
         <v>9.57</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
     </row>
@@ -3945,7 +3945,7 @@
         <v>17.27</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
     </row>
@@ -3981,7 +3981,7 @@
         <v>11.51</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
     </row>
@@ -4017,7 +4017,7 @@
         <v>7.47</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
     </row>
@@ -4053,7 +4053,7 @@
         <v>9.789999999999999</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
     </row>
@@ -4089,7 +4089,7 @@
         <v>9.68</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
     </row>
@@ -4125,7 +4125,7 @@
         <v>33.3</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
     </row>
@@ -4157,7 +4157,7 @@
         <v>20.14</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
     </row>
@@ -4193,7 +4193,7 @@
         <v>11.62</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
     </row>
@@ -4229,7 +4229,7 @@
         <v>23.56</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J106" s="2" t="inlineStr"/>
     </row>
@@ -4265,7 +4265,7 @@
         <v>4.57</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J107" s="2" t="inlineStr"/>
     </row>
@@ -4297,7 +4297,7 @@
         <v>3.34</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J108" s="2" t="inlineStr"/>
     </row>
@@ -4333,7 +4333,7 @@
         <v>3.65</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J109" s="2" t="inlineStr"/>
     </row>
@@ -4369,7 +4369,7 @@
         <v>364.86</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J110" s="2" t="inlineStr"/>
     </row>
@@ -4405,7 +4405,7 @@
         <v>10.73</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J111" s="2" t="inlineStr"/>
     </row>
@@ -4441,7 +4441,7 @@
         <v>23.8</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J112" s="2" t="inlineStr"/>
     </row>
@@ -4477,7 +4477,7 @@
         <v>10.52</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J113" s="2" t="inlineStr"/>
     </row>
@@ -4513,7 +4513,7 @@
         <v>19.55</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J114" s="2" t="inlineStr"/>
     </row>
@@ -4545,7 +4545,7 @@
         <v>9.69</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J115" s="2" t="inlineStr"/>
     </row>
@@ -4581,7 +4581,7 @@
         <v>20.27</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J116" s="2" t="inlineStr"/>
     </row>
@@ -4617,7 +4617,7 @@
         <v>13.51</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J117" s="2" t="inlineStr"/>
     </row>
@@ -4653,7 +4653,7 @@
         <v>6.57</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J118" s="2" t="inlineStr"/>
     </row>
@@ -4689,7 +4689,7 @@
         <v>19.55</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J119" s="2" t="inlineStr"/>
     </row>
@@ -4725,7 +4725,7 @@
         <v>16.58</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J120" s="2" t="inlineStr"/>
     </row>
@@ -4761,7 +4761,7 @@
         <v>6.95</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J121" s="2" t="inlineStr"/>
     </row>
@@ -4797,7 +4797,7 @@
         <v>11.52</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J122" s="2" t="inlineStr"/>
     </row>
@@ -4829,7 +4829,7 @@
         <v>20.27</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J123" s="2" t="inlineStr"/>
     </row>
@@ -4865,7 +4865,7 @@
         <v>136.82</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J124" s="2" t="inlineStr"/>
     </row>
@@ -4901,7 +4901,7 @@
         <v>12.73</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J125" s="2" t="inlineStr"/>
     </row>
@@ -4937,7 +4937,7 @@
         <v>7.26</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J126" s="2" t="inlineStr"/>
     </row>
@@ -4973,7 +4973,7 @@
         <v>6.26</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J127" s="2" t="inlineStr"/>
     </row>
@@ -5009,7 +5009,7 @@
         <v>5.13</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J128" s="2" t="inlineStr"/>
     </row>
@@ -5045,7 +5045,7 @@
         <v>3.19</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J129" s="2" t="inlineStr"/>
     </row>
@@ -5077,7 +5077,7 @@
         <v>2.86</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J130" s="2" t="inlineStr"/>
     </row>
@@ -5109,7 +5109,7 @@
         <v>3.25</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J131" s="2" t="inlineStr"/>
     </row>
@@ -5141,7 +5141,7 @@
         <v>26</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J132" s="2" t="inlineStr"/>
     </row>
@@ -5177,7 +5177,7 @@
         <v>19.5</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J133" s="2" t="inlineStr"/>
     </row>
@@ -5213,7 +5213,7 @@
         <v>877.5</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J134" s="2" t="inlineStr"/>
     </row>
@@ -5249,7 +5249,7 @@
         <v>100.29</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J135" s="2" t="inlineStr"/>
     </row>
@@ -5285,7 +5285,7 @@
         <v>15.13</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J136" s="2" t="inlineStr"/>
     </row>
@@ -5321,7 +5321,7 @@
         <v>33.43</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J137" s="2" t="inlineStr"/>
     </row>
@@ -5357,7 +5357,7 @@
         <v>9.970000000000001</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J138" s="2" t="inlineStr"/>
     </row>
@@ -5389,7 +5389,7 @@
         <v>12.9</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J139" s="2" t="inlineStr"/>
     </row>
@@ -5421,7 +5421,7 @@
         <v>28.08</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J140" s="2" t="inlineStr"/>
     </row>
@@ -5457,7 +5457,7 @@
         <v>17.12</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J141" s="2" t="inlineStr"/>
     </row>
@@ -5493,7 +5493,7 @@
         <v>14.94</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J142" s="2" t="inlineStr"/>
     </row>
@@ -5525,7 +5525,7 @@
         <v>1755</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J143" s="2" t="inlineStr"/>
     </row>
@@ -5557,7 +5557,7 @@
         <v>1755</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J144" s="2" t="inlineStr"/>
     </row>
@@ -5589,7 +5589,7 @@
         <v>1755</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J145" s="2" t="inlineStr"/>
     </row>
@@ -5625,7 +5625,7 @@
         <v>6.46</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J146" s="2" t="inlineStr"/>
     </row>
@@ -5661,7 +5661,7 @@
         <v>6.31</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J147" s="2" t="inlineStr"/>
     </row>
@@ -5697,7 +5697,7 @@
         <v>14.94</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J148" s="2" t="inlineStr"/>
     </row>
@@ -5733,7 +5733,7 @@
         <v>4.78</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J149" s="2" t="inlineStr"/>
     </row>
@@ -5769,7 +5769,7 @@
         <v>5.9</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J150" s="2" t="inlineStr"/>
     </row>
@@ -5801,7 +5801,7 @@
         <v>1904.18</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J151" s="2" t="inlineStr"/>
     </row>
@@ -5837,7 +5837,7 @@
         <v>8.73</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J152" s="2" t="inlineStr"/>
     </row>
@@ -5873,7 +5873,7 @@
         <v>50.11</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J153" s="2" t="inlineStr"/>
     </row>
@@ -5909,7 +5909,7 @@
         <v>16.14</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J154" s="2" t="inlineStr"/>
     </row>
@@ -5945,7 +5945,7 @@
         <v>380.84</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J155" s="2" t="inlineStr"/>
     </row>
@@ -5981,7 +5981,7 @@
         <v>21.76</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J156" s="2" t="inlineStr"/>
     </row>
@@ -6017,7 +6017,7 @@
         <v>51.82</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J157" s="2" t="inlineStr"/>
     </row>
@@ -6049,7 +6049,7 @@
         <v>963.53</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J158" s="2" t="inlineStr"/>
     </row>
@@ -6085,7 +6085,7 @@
         <v>169.26</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J159" s="2" t="inlineStr"/>
     </row>
@@ -6121,7 +6121,7 @@
         <v>35.26</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J160" s="2" t="inlineStr"/>
     </row>
@@ -6153,7 +6153,7 @@
         <v>12.09</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J161" s="2" t="inlineStr"/>
     </row>
@@ -6189,7 +6189,7 @@
         <v>7.21</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J162" s="2" t="inlineStr"/>
     </row>
@@ -6225,7 +6225,7 @@
         <v>64.23</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J163" s="2" t="inlineStr"/>
     </row>
@@ -6261,7 +6261,7 @@
         <v>963.52</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J164" s="2" t="inlineStr"/>
     </row>
@@ -6293,7 +6293,7 @@
         <v>1927.03</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J165" s="2" t="inlineStr"/>
     </row>
@@ -6329,7 +6329,7 @@
         <v>17.27</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J166" s="2" t="inlineStr"/>
     </row>
@@ -6365,7 +6365,7 @@
         <v>9.460000000000001</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J167" s="2" t="inlineStr"/>
     </row>
@@ -6401,7 +6401,7 @@
         <v>7.42</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J168" s="2" t="inlineStr"/>
     </row>
@@ -6437,7 +6437,7 @@
         <v>6.06</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J169" s="2" t="inlineStr"/>
     </row>
@@ -6473,7 +6473,7 @@
         <v>3.66</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J170" s="2" t="inlineStr"/>
     </row>
@@ -6509,7 +6509,7 @@
         <v>9.92</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J171" s="2" t="inlineStr"/>
     </row>
@@ -6545,7 +6545,7 @@
         <v>3.41</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J172" s="2" t="inlineStr"/>
     </row>
@@ -6581,7 +6581,7 @@
         <v>4.4</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J173" s="2" t="inlineStr"/>
     </row>
@@ -6617,7 +6617,7 @@
         <v>603.11</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J174" s="2" t="inlineStr"/>
     </row>
@@ -6649,7 +6649,7 @@
         <v>9.24</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J175" s="2" t="inlineStr"/>
     </row>
@@ -6685,7 +6685,7 @@
         <v>16.05</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J176" s="2" t="inlineStr"/>
     </row>
@@ -6717,7 +6717,7 @@
         <v>32.11</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J177" s="2" t="inlineStr"/>
     </row>
@@ -6753,7 +6753,7 @@
         <v>8.710000000000001</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J178" s="2" t="inlineStr"/>
     </row>
@@ -6789,7 +6789,7 @@
         <v>10.17</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J179" s="2" t="inlineStr"/>
     </row>
@@ -6821,7 +6821,7 @@
         <v>16.05</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J180" s="2" t="inlineStr"/>
     </row>
@@ -6857,7 +6857,7 @@
         <v>7.82</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J181" s="2" t="inlineStr"/>
     </row>
@@ -6893,7 +6893,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J182" s="2" t="inlineStr"/>
     </row>
@@ -6929,7 +6929,7 @@
         <v>5.26</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J183" s="2" t="inlineStr"/>
     </row>
@@ -6965,7 +6965,7 @@
         <v>19.06</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J184" s="2" t="inlineStr"/>
     </row>
@@ -7001,7 +7001,7 @@
         <v>26.52</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J185" s="2" t="inlineStr"/>
     </row>
@@ -7033,7 +7033,7 @@
         <v>13.86</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J186" s="2" t="inlineStr"/>
     </row>
@@ -7069,7 +7069,7 @@
         <v>3.63</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J187" s="2" t="inlineStr"/>
     </row>
@@ -7105,7 +7105,7 @@
         <v>7.37</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J188" s="2" t="inlineStr"/>
     </row>
@@ -7141,7 +7141,7 @@
         <v>7.92</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J189" s="2" t="inlineStr"/>
     </row>
@@ -7177,7 +7177,7 @@
         <v>13.36</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J190" s="2" t="inlineStr"/>
     </row>
@@ -7213,7 +7213,7 @@
         <v>10.43</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J191" s="2" t="inlineStr"/>
     </row>
@@ -7249,7 +7249,7 @@
         <v>10.57</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J192" s="2" t="inlineStr"/>
     </row>
@@ -7285,7 +7285,7 @@
         <v>5.35</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J193" s="2" t="inlineStr"/>
     </row>
@@ -7321,7 +7321,7 @@
         <v>5.38</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J194" s="2" t="inlineStr"/>
     </row>
@@ -7357,7 +7357,7 @@
         <v>4.63</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J195" s="2" t="inlineStr"/>
     </row>
@@ -7393,7 +7393,7 @@
         <v>2.85</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J196" s="2" t="inlineStr"/>
     </row>
@@ -7429,7 +7429,7 @@
         <v>2.78</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J197" s="2" t="inlineStr"/>
     </row>
@@ -7465,7 +7465,7 @@
         <v>4.52</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J198" s="2" t="inlineStr"/>
     </row>
@@ -7501,7 +7501,7 @@
         <v>5.19</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J199" s="2" t="inlineStr"/>
     </row>
@@ -7533,7 +7533,7 @@
         <v>4.92</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J200" s="2" t="inlineStr"/>
     </row>
@@ -7569,7 +7569,7 @@
         <v>6.49</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J201" s="2" t="inlineStr"/>
     </row>
@@ -7605,7 +7605,7 @@
         <v>6.91</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J202" s="2" t="inlineStr"/>
     </row>
@@ -7641,7 +7641,7 @@
         <v>7.23</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J203" s="2" t="inlineStr"/>
     </row>
@@ -7677,7 +7677,7 @@
         <v>14.98</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J204" s="2" t="inlineStr"/>
     </row>
@@ -7713,7 +7713,7 @@
         <v>37.75</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J205" s="2" t="inlineStr"/>
     </row>
@@ -7749,7 +7749,7 @@
         <v>20.97</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J206" s="2" t="inlineStr"/>
     </row>
@@ -7785,7 +7785,7 @@
         <v>12.38</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J207" s="2" t="inlineStr"/>
     </row>
@@ -7821,7 +7821,7 @@
         <v>10.21</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J208" s="2" t="inlineStr"/>
     </row>
@@ -7857,7 +7857,7 @@
         <v>11.85</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J209" s="2" t="inlineStr"/>
     </row>
@@ -7893,7 +7893,7 @@
         <v>14.13</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J210" s="2" t="inlineStr"/>
     </row>
@@ -7929,7 +7929,7 @@
         <v>17.98</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J211" s="2" t="inlineStr"/>
     </row>
@@ -7961,7 +7961,7 @@
         <v>6.65</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J212" s="2" t="inlineStr"/>
     </row>
@@ -7993,7 +7993,7 @@
         <v>5.57</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J213" s="2" t="inlineStr"/>
     </row>
@@ -8029,7 +8029,7 @@
         <v>6.32</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J214" s="2" t="inlineStr"/>
     </row>
@@ -8065,7 +8065,7 @@
         <v>5.4</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J215" s="2" t="inlineStr"/>
     </row>
@@ -8101,7 +8101,7 @@
         <v>10.86</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J216" s="2" t="inlineStr"/>
     </row>
@@ -8137,7 +8137,7 @@
         <v>41.94</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J217" s="2" t="inlineStr"/>
     </row>
@@ -8173,7 +8173,7 @@
         <v>3.14</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J218" s="2" t="inlineStr"/>
     </row>
@@ -8209,7 +8209,7 @@
         <v>4.35</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J219" s="2" t="inlineStr"/>
     </row>
@@ -8241,7 +8241,7 @@
         <v>1705.13</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J220" s="2" t="inlineStr"/>
     </row>
@@ -8277,7 +8277,7 @@
         <v>12.82</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J221" s="2" t="inlineStr"/>
     </row>
@@ -8309,7 +8309,7 @@
         <v>56.84</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J222" s="2" t="inlineStr"/>
     </row>
@@ -8345,7 +8345,7 @@
         <v>31.58</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J223" s="2" t="inlineStr"/>
     </row>
@@ -8381,7 +8381,7 @@
         <v>32.79</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J224" s="2" t="inlineStr"/>
     </row>
@@ -8417,7 +8417,7 @@
         <v>54.13</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J225" s="2" t="inlineStr"/>
     </row>
@@ -8453,7 +8453,7 @@
         <v>28.9</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J226" s="2" t="inlineStr"/>
     </row>
@@ -8489,7 +8489,7 @@
         <v>21.86</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J227" s="2" t="inlineStr"/>
     </row>
@@ -8525,7 +8525,7 @@
         <v>6.45</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J228" s="2" t="inlineStr"/>
     </row>
@@ -8561,7 +8561,7 @@
         <v>341</v>
       </c>
       <c r="I229" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J229" s="2" t="inlineStr"/>
     </row>
@@ -8593,7 +8593,7 @@
         <v>568.33</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J230" s="2" t="inlineStr"/>
     </row>
@@ -8625,7 +8625,7 @@
         <v>1705</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J231" s="2" t="inlineStr"/>
     </row>
@@ -8661,7 +8661,7 @@
         <v>13.41</v>
       </c>
       <c r="I232" s="2" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J232" s="2" t="inlineStr"/>
     </row>
@@ -8697,7 +8697,7 @@
         <v>6.25</v>
       </c>
       <c r="I233" s="2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J233" s="2" t="inlineStr"/>
     </row>
@@ -8733,7 +8733,7 @@
         <v>5.33</v>
       </c>
       <c r="I234" s="2" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J234" s="2" t="inlineStr"/>
     </row>
@@ -8769,7 +8769,7 @@
         <v>5.96</v>
       </c>
       <c r="I235" s="2" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J235" s="2" t="inlineStr"/>
     </row>
@@ -8805,7 +8805,7 @@
         <v>13.92</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J236" s="2" t="inlineStr"/>
     </row>
@@ -8841,7 +8841,7 @@
         <v>3.74</v>
       </c>
       <c r="I237" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J237" s="2" t="inlineStr"/>
     </row>
@@ -8877,7 +8877,7 @@
         <v>5.06</v>
       </c>
       <c r="I238" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J238" s="2" t="inlineStr"/>
     </row>
@@ -8909,7 +8909,7 @@
         <v>735</v>
       </c>
       <c r="I239" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J239" s="2" t="inlineStr"/>
     </row>
@@ -8945,7 +8945,7 @@
         <v>16.28</v>
       </c>
       <c r="I240" s="2" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J240" s="2" t="inlineStr"/>
     </row>
@@ -8977,7 +8977,7 @@
         <v>8.01</v>
       </c>
       <c r="I241" s="2" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J241" s="2" t="inlineStr"/>
     </row>
@@ -9009,7 +9009,7 @@
         <v>13.56</v>
       </c>
       <c r="I242" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J242" s="2" t="inlineStr"/>
     </row>
@@ -9045,7 +9045,7 @@
         <v>14.65</v>
       </c>
       <c r="I243" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J243" s="2" t="inlineStr"/>
     </row>
@@ -9081,7 +9081,7 @@
         <v>25.26</v>
       </c>
       <c r="I244" s="2" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J244" s="2" t="inlineStr"/>
     </row>
@@ -9117,7 +9117,7 @@
         <v>33.3</v>
       </c>
       <c r="I245" s="2" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J245" s="2" t="inlineStr"/>
     </row>
@@ -9149,7 +9149,7 @@
         <v>5.47</v>
       </c>
       <c r="I246" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J246" s="2" t="inlineStr"/>
     </row>
@@ -9181,7 +9181,7 @@
         <v>6.91</v>
       </c>
       <c r="I247" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J247" s="2" t="inlineStr"/>
     </row>
@@ -9217,7 +9217,7 @@
         <v>5.69</v>
       </c>
       <c r="I248" s="2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J248" s="2" t="inlineStr"/>
     </row>
@@ -9249,7 +9249,7 @@
         <v>3.94</v>
       </c>
       <c r="I249" s="2" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J249" s="2" t="inlineStr"/>
     </row>
@@ -9281,7 +9281,7 @@
         <v>2.74</v>
       </c>
       <c r="I250" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J250" s="2" t="inlineStr"/>
     </row>
@@ -9317,7 +9317,7 @@
         <v>2.56</v>
       </c>
       <c r="I251" s="2" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J251" s="2" t="inlineStr"/>
     </row>
@@ -9353,7 +9353,7 @@
         <v>2.8</v>
       </c>
       <c r="I252" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J252" s="2" t="inlineStr"/>
     </row>
@@ -9389,7 +9389,7 @@
         <v>6.74</v>
       </c>
       <c r="I253" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J253" s="2" t="inlineStr"/>
     </row>
@@ -9425,7 +9425,7 @@
         <v>3.7</v>
       </c>
       <c r="I254" s="2" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J254" s="2" t="inlineStr"/>
     </row>
@@ -9461,7 +9461,7 @@
         <v>11.49</v>
       </c>
       <c r="I255" s="2" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J255" s="2" t="inlineStr"/>
     </row>
@@ -9497,7 +9497,7 @@
         <v>7.46</v>
       </c>
       <c r="I256" s="2" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J256" s="2" t="inlineStr"/>
     </row>
@@ -9533,7 +9533,7 @@
         <v>28.08</v>
       </c>
       <c r="I257" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J257" s="2" t="inlineStr"/>
     </row>
@@ -9569,7 +9569,7 @@
         <v>13.07</v>
       </c>
       <c r="I258" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J258" s="2" t="inlineStr"/>
     </row>
@@ -9605,7 +9605,7 @@
         <v>11.66</v>
       </c>
       <c r="I259" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J259" s="2" t="inlineStr"/>
     </row>
@@ -9641,7 +9641,7 @@
         <v>6.61</v>
       </c>
       <c r="I260" s="2" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J260" s="2" t="inlineStr"/>
     </row>
@@ -9677,7 +9677,7 @@
         <v>3.09</v>
       </c>
       <c r="I261" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J261" s="2" t="inlineStr"/>
     </row>
@@ -9713,7 +9713,7 @@
         <v>3.35</v>
       </c>
       <c r="I262" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J262" s="2" t="inlineStr"/>
     </row>
@@ -9749,7 +9749,7 @@
         <v>35.84</v>
       </c>
       <c r="I263" s="2" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J263" s="2" t="inlineStr"/>
     </row>
@@ -9785,7 +9785,7 @@
         <v>13.59</v>
       </c>
       <c r="I264" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J264" s="2" t="inlineStr"/>
     </row>
@@ -9817,7 +9817,7 @@
         <v>523.84</v>
       </c>
       <c r="I265" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J265" s="2" t="inlineStr"/>
     </row>
@@ -9853,7 +9853,7 @@
         <v>16.06</v>
       </c>
       <c r="I266" s="2" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J266" s="2" t="inlineStr"/>
     </row>
@@ -9885,7 +9885,7 @@
         <v>12.46</v>
       </c>
       <c r="I267" s="2" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J267" s="2" t="inlineStr"/>
     </row>
@@ -9921,7 +9921,7 @@
         <v>23.36</v>
       </c>
       <c r="I268" s="2" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J268" s="2" t="inlineStr"/>
     </row>
@@ -9957,7 +9957,7 @@
         <v>4.3</v>
       </c>
       <c r="I269" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J269" s="2" t="inlineStr"/>
     </row>
@@ -9993,7 +9993,7 @@
         <v>5.84</v>
       </c>
       <c r="I270" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J270" s="2" t="inlineStr"/>
     </row>
@@ -10029,7 +10029,7 @@
         <v>1.84</v>
       </c>
       <c r="I271" s="2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J271" s="2" t="inlineStr"/>
     </row>
@@ -10065,7 +10065,7 @@
         <v>1.97</v>
       </c>
       <c r="I272" s="2" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J272" s="2" t="inlineStr"/>
     </row>
@@ -10101,7 +10101,7 @@
         <v>8.81</v>
       </c>
       <c r="I273" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J273" s="2" t="inlineStr"/>
     </row>
@@ -10137,7 +10137,7 @@
         <v>7.52</v>
       </c>
       <c r="I274" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J274" s="2" t="inlineStr"/>
     </row>
@@ -10173,7 +10173,7 @@
         <v>6.41</v>
       </c>
       <c r="I275" s="2" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J275" s="2" t="inlineStr"/>
     </row>
@@ -10209,7 +10209,7 @@
         <v>24.58</v>
       </c>
       <c r="I276" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J276" s="2" t="inlineStr"/>
     </row>
@@ -10245,7 +10245,7 @@
         <v>16.86</v>
       </c>
       <c r="I277" s="2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J277" s="2" t="inlineStr"/>
     </row>
@@ -10281,7 +10281,7 @@
         <v>4.99</v>
       </c>
       <c r="I278" s="2" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J278" s="2" t="inlineStr"/>
     </row>
@@ -10317,7 +10317,7 @@
         <v>2.83</v>
       </c>
       <c r="I279" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J279" s="2" t="inlineStr"/>
     </row>
@@ -10353,7 +10353,7 @@
         <v>3.16</v>
       </c>
       <c r="I280" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J280" s="2" t="inlineStr"/>
     </row>
@@ -10385,7 +10385,7 @@
         <v>32.51</v>
       </c>
       <c r="I281" s="2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J281" s="2" t="inlineStr"/>
     </row>
@@ -10421,7 +10421,7 @@
         <v>17.67</v>
       </c>
       <c r="I282" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J282" s="2" t="inlineStr"/>
     </row>
@@ -10457,7 +10457,7 @@
         <v>23.9</v>
       </c>
       <c r="I283" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J283" s="2" t="inlineStr"/>
     </row>
@@ -10493,7 +10493,7 @@
         <v>5</v>
       </c>
       <c r="I284" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J284" s="2" t="inlineStr"/>
     </row>
@@ -10529,7 +10529,7 @@
         <v>7.02</v>
       </c>
       <c r="I285" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J285" s="2" t="inlineStr"/>
     </row>
@@ -10565,7 +10565,7 @@
         <v>6.79</v>
       </c>
       <c r="I286" s="2" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J286" s="2" t="inlineStr"/>
     </row>
@@ -10601,7 +10601,7 @@
         <v>12.02</v>
       </c>
       <c r="I287" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J287" s="2" t="inlineStr"/>
     </row>
@@ -10637,7 +10637,7 @@
         <v>9.57</v>
       </c>
       <c r="I288" s="2" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J288" s="2" t="inlineStr"/>
     </row>
@@ -10673,7 +10673,7 @@
         <v>13.74</v>
       </c>
       <c r="I289" s="2" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J289" s="2" t="inlineStr"/>
     </row>
@@ -10705,7 +10705,7 @@
         <v>6.7</v>
       </c>
       <c r="I290" s="2" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J290" s="2" t="inlineStr"/>
     </row>
@@ -10741,7 +10741,7 @@
         <v>11.28</v>
       </c>
       <c r="I291" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J291" s="2" t="inlineStr"/>
     </row>
@@ -10777,7 +10777,7 @@
         <v>24.72</v>
       </c>
       <c r="I292" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J292" s="2" t="inlineStr"/>
     </row>
@@ -10813,7 +10813,7 @@
         <v>16.07</v>
       </c>
       <c r="I293" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J293" s="2" t="inlineStr"/>
     </row>
@@ -10849,7 +10849,7 @@
         <v>8.27</v>
       </c>
       <c r="I294" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J294" s="2" t="inlineStr"/>
     </row>
@@ -10885,7 +10885,7 @@
         <v>11.24</v>
       </c>
       <c r="I295" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J295" s="2" t="inlineStr"/>
     </row>
@@ -10921,7 +10921,7 @@
         <v>17.36</v>
       </c>
       <c r="I296" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J296" s="2" t="inlineStr"/>
     </row>
@@ -10957,7 +10957,7 @@
         <v>6.59</v>
       </c>
       <c r="I297" s="2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J297" s="2" t="inlineStr"/>
     </row>
@@ -10989,7 +10989,7 @@
         <v>5.44</v>
       </c>
       <c r="I298" s="2" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J298" s="2" t="inlineStr"/>
     </row>
@@ -11025,7 +11025,7 @@
         <v>3.79</v>
       </c>
       <c r="I299" s="2" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J299" s="2" t="inlineStr"/>
     </row>
@@ -11061,7 +11061,7 @@
         <v>8.42</v>
       </c>
       <c r="I300" s="2" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J300" s="2" t="inlineStr"/>
     </row>
@@ -11097,7 +11097,7 @@
         <v>27.74</v>
       </c>
       <c r="I301" s="2" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J301" s="2" t="inlineStr"/>
     </row>
@@ -11133,7 +11133,7 @@
         <v>30.75</v>
       </c>
       <c r="I302" s="2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J302" s="2" t="inlineStr"/>
     </row>
@@ -11169,7 +11169,7 @@
         <v>11.99</v>
       </c>
       <c r="I303" s="2" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J303" s="2" t="inlineStr"/>
     </row>
@@ -11205,7 +11205,7 @@
         <v>56.59</v>
       </c>
       <c r="I304" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J304" s="2" t="inlineStr"/>
     </row>
@@ -11241,7 +11241,7 @@
         <v>14.15</v>
       </c>
       <c r="I305" s="2" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J305" s="2" t="inlineStr"/>
     </row>
@@ -11277,7 +11277,7 @@
         <v>34.5</v>
       </c>
       <c r="I306" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J306" s="2" t="inlineStr"/>
     </row>
@@ -11313,7 +11313,7 @@
         <v>18.61</v>
       </c>
       <c r="I307" s="2" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J307" s="2" t="inlineStr"/>
     </row>
@@ -11349,7 +11349,7 @@
         <v>5.66</v>
       </c>
       <c r="I308" s="2" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J308" s="2" t="inlineStr"/>
     </row>
@@ -11385,7 +11385,7 @@
         <v>15.72</v>
       </c>
       <c r="I309" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J309" s="2" t="inlineStr"/>
     </row>
@@ -11421,7 +11421,7 @@
         <v>7.72</v>
       </c>
       <c r="I310" s="2" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J310" s="2" t="inlineStr"/>
     </row>
@@ -11457,7 +11457,7 @@
         <v>19.86</v>
       </c>
       <c r="I311" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J311" s="2" t="inlineStr"/>
     </row>
@@ -11493,7 +11493,7 @@
         <v>13.56</v>
       </c>
       <c r="I312" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J312" s="2" t="inlineStr"/>
     </row>
@@ -11529,7 +11529,7 @@
         <v>10.3</v>
       </c>
       <c r="I313" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J313" s="2" t="inlineStr"/>
     </row>
@@ -11565,7 +11565,7 @@
         <v>17.16</v>
       </c>
       <c r="I314" s="2" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J314" s="2" t="inlineStr"/>
     </row>
@@ -11601,7 +11601,7 @@
         <v>6.47</v>
       </c>
       <c r="I315" s="2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J315" s="2" t="inlineStr"/>
     </row>
@@ -11637,7 +11637,7 @@
         <v>5.52</v>
       </c>
       <c r="I316" s="2" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J316" s="2" t="inlineStr"/>
     </row>
@@ -11673,7 +11673,7 @@
         <v>5.25</v>
       </c>
       <c r="I317" s="2" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J317" s="2" t="inlineStr"/>
     </row>
@@ -11709,7 +11709,7 @@
         <v>11.44</v>
       </c>
       <c r="I318" s="2" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J318" s="2" t="inlineStr"/>
     </row>
@@ -11745,7 +11745,7 @@
         <v>10.53</v>
       </c>
       <c r="I319" s="2" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J319" s="2" t="inlineStr"/>
     </row>
@@ -11781,7 +11781,7 @@
         <v>16.95</v>
       </c>
       <c r="I320" s="2" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J320" s="2" t="inlineStr"/>
     </row>
@@ -11813,7 +11813,7 @@
         <v>3.28</v>
       </c>
       <c r="I321" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J321" s="2" t="inlineStr"/>
     </row>
@@ -11849,7 +11849,7 @@
         <v>4.06</v>
       </c>
       <c r="I322" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J322" s="2" t="inlineStr"/>
     </row>
@@ -11881,7 +11881,7 @@
         <v>42.23</v>
       </c>
       <c r="I323" s="2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J323" s="2" t="inlineStr"/>
     </row>
@@ -11913,7 +11913,7 @@
         <v>24.13</v>
       </c>
       <c r="I324" s="2" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J324" s="2" t="inlineStr"/>
     </row>
@@ -11949,7 +11949,7 @@
         <v>7.57</v>
       </c>
       <c r="I325" s="2" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J325" s="2" t="inlineStr"/>
     </row>
@@ -11985,7 +11985,7 @@
         <v>11.5</v>
       </c>
       <c r="I326" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J326" s="2" t="inlineStr"/>
     </row>
@@ -12017,7 +12017,7 @@
         <v>14.61</v>
       </c>
       <c r="I327" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J327" s="2" t="inlineStr"/>
     </row>
@@ -12053,7 +12053,7 @@
         <v>3.47</v>
       </c>
       <c r="I328" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J328" s="2" t="inlineStr"/>
     </row>
@@ -12089,7 +12089,7 @@
         <v>5.32</v>
       </c>
       <c r="I329" s="2" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J329" s="2" t="inlineStr"/>
     </row>

--- a/docs/downloads/KetQuaGiaoDich_latest.xlsx
+++ b/docs/downloads/KetQuaGiaoDich_latest.xlsx
@@ -573,7 +573,7 @@
         <v>8.06</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
     </row>
@@ -609,7 +609,7 @@
         <v>328.36</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
     </row>
@@ -645,7 +645,7 @@
         <v>18.76</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
     </row>
@@ -677,7 +677,7 @@
         <v>38.63</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
     </row>
@@ -713,7 +713,7 @@
         <v>16.84</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
     </row>
@@ -749,7 +749,7 @@
         <v>29.19</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
     </row>
@@ -785,7 +785,7 @@
         <v>11.32</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
     </row>
@@ -821,7 +821,7 @@
         <v>12.51</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
     </row>
@@ -857,7 +857,7 @@
         <v>7.91</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
     </row>
@@ -893,7 +893,7 @@
         <v>8.01</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
     </row>
@@ -929,7 +929,7 @@
         <v>10.18</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
     </row>
@@ -961,7 +961,7 @@
         <v>21.02</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
     </row>
@@ -993,7 +993,7 @@
         <v>20.21</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
     </row>
@@ -1025,7 +1025,7 @@
         <v>13.83</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
     </row>
@@ -1061,7 +1061,7 @@
         <v>27.37</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
     </row>
@@ -1097,7 +1097,7 @@
         <v>437.98</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
     </row>
@@ -1129,7 +1129,7 @@
         <v>12.65</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
     </row>
@@ -1161,7 +1161,7 @@
         <v>6.15</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
     </row>
@@ -1197,7 +1197,7 @@
         <v>11.8</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
     </row>
@@ -1233,7 +1233,7 @@
         <v>12.72</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
     </row>
@@ -1269,7 +1269,7 @@
         <v>10.89</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
     </row>
@@ -1301,7 +1301,7 @@
         <v>850.29</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
     </row>
@@ -1337,7 +1337,7 @@
         <v>462.26</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
     </row>
@@ -1373,7 +1373,7 @@
         <v>23.71</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
     </row>
@@ -1409,7 +1409,7 @@
         <v>205.45</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
     </row>
@@ -1445,7 +1445,7 @@
         <v>30.82</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
     </row>
@@ -1481,7 +1481,7 @@
         <v>371.04</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
     </row>
@@ -1513,7 +1513,7 @@
         <v>37.1</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
     </row>
@@ -1549,7 +1549,7 @@
         <v>29.68</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
     </row>
@@ -1581,7 +1581,7 @@
         <v>371.04</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
     </row>
@@ -1613,7 +1613,7 @@
         <v>742.08</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
     </row>
@@ -1645,7 +1645,7 @@
         <v>23.19</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
     </row>
@@ -1681,7 +1681,7 @@
         <v>16.27</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
     </row>
@@ -1717,7 +1717,7 @@
         <v>5.9</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
     </row>
@@ -1753,7 +1753,7 @@
         <v>6.12</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
     </row>
@@ -1789,7 +1789,7 @@
         <v>19.26</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
     </row>
@@ -1825,7 +1825,7 @@
         <v>11.26</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
     </row>
@@ -1861,7 +1861,7 @@
         <v>7.21</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
     </row>
@@ -1897,7 +1897,7 @@
         <v>12.04</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
     </row>
@@ -1933,7 +1933,7 @@
         <v>10.64</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
     </row>
@@ -1969,7 +1969,7 @@
         <v>25.79</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
     </row>
@@ -2005,7 +2005,7 @@
         <v>75.20999999999999</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
     </row>
@@ -2037,7 +2037,7 @@
         <v>902.5</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
     </row>
@@ -2073,7 +2073,7 @@
         <v>7.97</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
     </row>
@@ -2109,7 +2109,7 @@
         <v>6.78</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
     </row>
@@ -2145,7 +2145,7 @@
         <v>6.78</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
     </row>
@@ -2181,7 +2181,7 @@
         <v>5.4</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
     </row>
@@ -2217,7 +2217,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
     </row>
@@ -2253,7 +2253,7 @@
         <v>7.47</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
     </row>
@@ -2289,7 +2289,7 @@
         <v>4.09</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
     </row>
@@ -2325,7 +2325,7 @@
         <v>4.52</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
     </row>
@@ -2361,7 +2361,7 @@
         <v>30.05</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
     </row>
@@ -2397,7 +2397,7 @@
         <v>6.43</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
     </row>
@@ -2433,7 +2433,7 @@
         <v>29.89</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
     </row>
@@ -2469,7 +2469,7 @@
         <v>5.19</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
     </row>
@@ -2505,7 +2505,7 @@
         <v>12.69</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
     </row>
@@ -2541,7 +2541,7 @@
         <v>9</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
     </row>
@@ -2577,7 +2577,7 @@
         <v>18.53</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
     </row>
@@ -2613,7 +2613,7 @@
         <v>10.22</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
     </row>
@@ -2649,7 +2649,7 @@
         <v>4.79</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
     </row>
@@ -2685,7 +2685,7 @@
         <v>3.34</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
     </row>
@@ -2717,7 +2717,7 @@
         <v>10.18</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
     </row>
@@ -2753,7 +2753,7 @@
         <v>8.42</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
     </row>
@@ -2789,7 +2789,7 @@
         <v>3.56</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
     </row>
@@ -2821,7 +2821,7 @@
         <v>4.51</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
     </row>
@@ -2857,7 +2857,7 @@
         <v>15.02</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
     </row>
@@ -2893,7 +2893,7 @@
         <v>1237.96</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
     </row>
@@ -2929,7 +2929,7 @@
         <v>16.96</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
     </row>
@@ -2965,7 +2965,7 @@
         <v>88.43000000000001</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
     </row>
@@ -3001,7 +3001,7 @@
         <v>19.97</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
     </row>
@@ -3037,7 +3037,7 @@
         <v>206.33</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
     </row>
@@ -3073,7 +3073,7 @@
         <v>19.34</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
     </row>
@@ -3105,7 +3105,7 @@
         <v>63.48</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
     </row>
@@ -3141,7 +3141,7 @@
         <v>16.29</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
     </row>
@@ -3177,7 +3177,7 @@
         <v>13.99</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
     </row>
@@ -3213,7 +3213,7 @@
         <v>95.23</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
     </row>
@@ -3249,7 +3249,7 @@
         <v>8.6</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
     </row>
@@ -3285,7 +3285,7 @@
         <v>14.39</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
     </row>
@@ -3317,7 +3317,7 @@
         <v>11.52</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
     </row>
@@ -3353,7 +3353,7 @@
         <v>44.22</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
     </row>
@@ -3389,7 +3389,7 @@
         <v>19.35</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
     </row>
@@ -3425,7 +3425,7 @@
         <v>14.17</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
     </row>
@@ -3461,7 +3461,7 @@
         <v>11.28</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
     </row>
@@ -3497,7 +3497,7 @@
         <v>13.81</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
     </row>
@@ -3533,7 +3533,7 @@
         <v>15.79</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
     </row>
@@ -3569,7 +3569,7 @@
         <v>27.62</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
     </row>
@@ -3601,7 +3601,7 @@
         <v>17.27</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
     </row>
@@ -3637,7 +3637,7 @@
         <v>1110</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
     </row>
@@ -3669,7 +3669,7 @@
         <v>1110</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
     </row>
@@ -3701,7 +3701,7 @@
         <v>1110</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
     </row>
@@ -3737,7 +3737,7 @@
         <v>18.73</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
     </row>
@@ -3773,7 +3773,7 @@
         <v>12.14</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
     </row>
@@ -3809,7 +3809,7 @@
         <v>8.630000000000001</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
     </row>
@@ -3845,7 +3845,7 @@
         <v>6.42</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
     </row>
@@ -3877,7 +3877,7 @@
         <v>10.83</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
     </row>
@@ -3909,7 +3909,7 @@
         <v>9.57</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
     </row>
@@ -3945,7 +3945,7 @@
         <v>17.27</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
     </row>
@@ -3981,7 +3981,7 @@
         <v>11.51</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
     </row>
@@ -4017,7 +4017,7 @@
         <v>7.47</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
     </row>
@@ -4053,7 +4053,7 @@
         <v>9.789999999999999</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
     </row>
@@ -4089,7 +4089,7 @@
         <v>9.68</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
     </row>
@@ -4125,7 +4125,7 @@
         <v>33.3</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
     </row>
@@ -4157,7 +4157,7 @@
         <v>20.14</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
     </row>
@@ -4193,7 +4193,7 @@
         <v>11.62</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
     </row>
@@ -4229,7 +4229,7 @@
         <v>23.56</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J106" s="2" t="inlineStr"/>
     </row>
@@ -4265,7 +4265,7 @@
         <v>4.57</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J107" s="2" t="inlineStr"/>
     </row>
@@ -4297,7 +4297,7 @@
         <v>3.34</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J108" s="2" t="inlineStr"/>
     </row>
@@ -4333,7 +4333,7 @@
         <v>3.65</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J109" s="2" t="inlineStr"/>
     </row>
@@ -4369,7 +4369,7 @@
         <v>364.86</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J110" s="2" t="inlineStr"/>
     </row>
@@ -4405,7 +4405,7 @@
         <v>10.73</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J111" s="2" t="inlineStr"/>
     </row>
@@ -4441,7 +4441,7 @@
         <v>23.8</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J112" s="2" t="inlineStr"/>
     </row>
@@ -4477,7 +4477,7 @@
         <v>10.52</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J113" s="2" t="inlineStr"/>
     </row>
@@ -4513,7 +4513,7 @@
         <v>19.55</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J114" s="2" t="inlineStr"/>
     </row>
@@ -4545,7 +4545,7 @@
         <v>9.69</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J115" s="2" t="inlineStr"/>
     </row>
@@ -4581,7 +4581,7 @@
         <v>20.27</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J116" s="2" t="inlineStr"/>
     </row>
@@ -4617,7 +4617,7 @@
         <v>13.51</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J117" s="2" t="inlineStr"/>
     </row>
@@ -4653,7 +4653,7 @@
         <v>6.57</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J118" s="2" t="inlineStr"/>
     </row>
@@ -4689,7 +4689,7 @@
         <v>19.55</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J119" s="2" t="inlineStr"/>
     </row>
@@ -4725,7 +4725,7 @@
         <v>16.58</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J120" s="2" t="inlineStr"/>
     </row>
@@ -4761,7 +4761,7 @@
         <v>6.95</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J121" s="2" t="inlineStr"/>
     </row>
@@ -4797,7 +4797,7 @@
         <v>11.52</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J122" s="2" t="inlineStr"/>
     </row>
@@ -4829,7 +4829,7 @@
         <v>20.27</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J123" s="2" t="inlineStr"/>
     </row>
@@ -4865,7 +4865,7 @@
         <v>136.82</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J124" s="2" t="inlineStr"/>
     </row>
@@ -4901,7 +4901,7 @@
         <v>12.73</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J125" s="2" t="inlineStr"/>
     </row>
@@ -4937,7 +4937,7 @@
         <v>7.26</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J126" s="2" t="inlineStr"/>
     </row>
@@ -4973,7 +4973,7 @@
         <v>6.26</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J127" s="2" t="inlineStr"/>
     </row>
@@ -5009,7 +5009,7 @@
         <v>5.13</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J128" s="2" t="inlineStr"/>
     </row>
@@ -5045,7 +5045,7 @@
         <v>3.19</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J129" s="2" t="inlineStr"/>
     </row>
@@ -5077,7 +5077,7 @@
         <v>2.86</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J130" s="2" t="inlineStr"/>
     </row>
@@ -5109,7 +5109,7 @@
         <v>3.25</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J131" s="2" t="inlineStr"/>
     </row>
@@ -5141,7 +5141,7 @@
         <v>26</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J132" s="2" t="inlineStr"/>
     </row>
@@ -5177,7 +5177,7 @@
         <v>19.5</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J133" s="2" t="inlineStr"/>
     </row>
@@ -5213,7 +5213,7 @@
         <v>877.5</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J134" s="2" t="inlineStr"/>
     </row>
@@ -5249,7 +5249,7 @@
         <v>100.29</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J135" s="2" t="inlineStr"/>
     </row>
@@ -5285,7 +5285,7 @@
         <v>15.13</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J136" s="2" t="inlineStr"/>
     </row>
@@ -5321,7 +5321,7 @@
         <v>33.43</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J137" s="2" t="inlineStr"/>
     </row>
@@ -5357,7 +5357,7 @@
         <v>9.970000000000001</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J138" s="2" t="inlineStr"/>
     </row>
@@ -5389,7 +5389,7 @@
         <v>12.9</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J139" s="2" t="inlineStr"/>
     </row>
@@ -5421,7 +5421,7 @@
         <v>28.08</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J140" s="2" t="inlineStr"/>
     </row>
@@ -5457,7 +5457,7 @@
         <v>17.12</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J141" s="2" t="inlineStr"/>
     </row>
@@ -5493,7 +5493,7 @@
         <v>14.94</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J142" s="2" t="inlineStr"/>
     </row>
@@ -5525,7 +5525,7 @@
         <v>1755</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J143" s="2" t="inlineStr"/>
     </row>
@@ -5557,7 +5557,7 @@
         <v>1755</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J144" s="2" t="inlineStr"/>
     </row>
@@ -5589,7 +5589,7 @@
         <v>1755</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J145" s="2" t="inlineStr"/>
     </row>
@@ -5625,7 +5625,7 @@
         <v>6.46</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J146" s="2" t="inlineStr"/>
     </row>
@@ -5661,7 +5661,7 @@
         <v>6.31</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J147" s="2" t="inlineStr"/>
     </row>
@@ -5697,7 +5697,7 @@
         <v>14.94</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J148" s="2" t="inlineStr"/>
     </row>
@@ -5733,7 +5733,7 @@
         <v>4.78</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J149" s="2" t="inlineStr"/>
     </row>
@@ -5769,7 +5769,7 @@
         <v>5.9</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J150" s="2" t="inlineStr"/>
     </row>
@@ -5801,7 +5801,7 @@
         <v>1904.18</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J151" s="2" t="inlineStr"/>
     </row>
@@ -5837,7 +5837,7 @@
         <v>8.73</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J152" s="2" t="inlineStr"/>
     </row>
@@ -5873,7 +5873,7 @@
         <v>50.11</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J153" s="2" t="inlineStr"/>
     </row>
@@ -5909,7 +5909,7 @@
         <v>16.14</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J154" s="2" t="inlineStr"/>
     </row>
@@ -5945,7 +5945,7 @@
         <v>380.84</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J155" s="2" t="inlineStr"/>
     </row>
@@ -5981,7 +5981,7 @@
         <v>21.76</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J156" s="2" t="inlineStr"/>
     </row>
@@ -6017,7 +6017,7 @@
         <v>51.82</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J157" s="2" t="inlineStr"/>
     </row>
@@ -6049,7 +6049,7 @@
         <v>963.53</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J158" s="2" t="inlineStr"/>
     </row>
@@ -6085,7 +6085,7 @@
         <v>169.26</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J159" s="2" t="inlineStr"/>
     </row>
@@ -6121,7 +6121,7 @@
         <v>35.26</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J160" s="2" t="inlineStr"/>
     </row>
@@ -6153,7 +6153,7 @@
         <v>12.09</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J161" s="2" t="inlineStr"/>
     </row>
@@ -6189,7 +6189,7 @@
         <v>7.21</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J162" s="2" t="inlineStr"/>
     </row>
@@ -6225,7 +6225,7 @@
         <v>64.23</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J163" s="2" t="inlineStr"/>
     </row>
@@ -6261,7 +6261,7 @@
         <v>963.52</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J164" s="2" t="inlineStr"/>
     </row>
@@ -6293,7 +6293,7 @@
         <v>1927.03</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J165" s="2" t="inlineStr"/>
     </row>
@@ -6329,7 +6329,7 @@
         <v>17.27</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J166" s="2" t="inlineStr"/>
     </row>
@@ -6365,7 +6365,7 @@
         <v>9.460000000000001</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J167" s="2" t="inlineStr"/>
     </row>
@@ -6401,7 +6401,7 @@
         <v>7.42</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J168" s="2" t="inlineStr"/>
     </row>
@@ -6437,7 +6437,7 @@
         <v>6.06</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J169" s="2" t="inlineStr"/>
     </row>
@@ -6473,7 +6473,7 @@
         <v>3.66</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J170" s="2" t="inlineStr"/>
     </row>
@@ -6509,7 +6509,7 @@
         <v>9.92</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J171" s="2" t="inlineStr"/>
     </row>
@@ -6545,7 +6545,7 @@
         <v>3.41</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J172" s="2" t="inlineStr"/>
     </row>
@@ -6581,7 +6581,7 @@
         <v>4.4</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J173" s="2" t="inlineStr"/>
     </row>
@@ -6617,7 +6617,7 @@
         <v>603.11</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J174" s="2" t="inlineStr"/>
     </row>
@@ -6649,7 +6649,7 @@
         <v>9.24</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J175" s="2" t="inlineStr"/>
     </row>
@@ -6685,7 +6685,7 @@
         <v>16.05</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J176" s="2" t="inlineStr"/>
     </row>
@@ -6717,7 +6717,7 @@
         <v>32.11</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J177" s="2" t="inlineStr"/>
     </row>
@@ -6753,7 +6753,7 @@
         <v>8.710000000000001</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J178" s="2" t="inlineStr"/>
     </row>
@@ -6789,7 +6789,7 @@
         <v>10.17</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J179" s="2" t="inlineStr"/>
     </row>
@@ -6821,7 +6821,7 @@
         <v>16.05</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J180" s="2" t="inlineStr"/>
     </row>
@@ -6857,7 +6857,7 @@
         <v>7.82</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J181" s="2" t="inlineStr"/>
     </row>
@@ -6893,7 +6893,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J182" s="2" t="inlineStr"/>
     </row>
@@ -6929,7 +6929,7 @@
         <v>5.26</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J183" s="2" t="inlineStr"/>
     </row>
@@ -6965,7 +6965,7 @@
         <v>19.06</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J184" s="2" t="inlineStr"/>
     </row>
@@ -7001,7 +7001,7 @@
         <v>26.52</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J185" s="2" t="inlineStr"/>
     </row>
@@ -7033,7 +7033,7 @@
         <v>13.86</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J186" s="2" t="inlineStr"/>
     </row>
@@ -7069,7 +7069,7 @@
         <v>3.63</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J187" s="2" t="inlineStr"/>
     </row>
@@ -7105,7 +7105,7 @@
         <v>7.37</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J188" s="2" t="inlineStr"/>
     </row>
@@ -7141,7 +7141,7 @@
         <v>7.92</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J189" s="2" t="inlineStr"/>
     </row>
@@ -7177,7 +7177,7 @@
         <v>13.36</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J190" s="2" t="inlineStr"/>
     </row>
@@ -7213,7 +7213,7 @@
         <v>10.43</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J191" s="2" t="inlineStr"/>
     </row>
@@ -7249,7 +7249,7 @@
         <v>10.57</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J192" s="2" t="inlineStr"/>
     </row>
@@ -7285,7 +7285,7 @@
         <v>5.35</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J193" s="2" t="inlineStr"/>
     </row>
@@ -7321,7 +7321,7 @@
         <v>5.38</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J194" s="2" t="inlineStr"/>
     </row>
@@ -7357,7 +7357,7 @@
         <v>4.63</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J195" s="2" t="inlineStr"/>
     </row>
@@ -7393,7 +7393,7 @@
         <v>2.85</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J196" s="2" t="inlineStr"/>
     </row>
@@ -7429,7 +7429,7 @@
         <v>2.78</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J197" s="2" t="inlineStr"/>
     </row>
@@ -7465,7 +7465,7 @@
         <v>4.52</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J198" s="2" t="inlineStr"/>
     </row>
@@ -7501,7 +7501,7 @@
         <v>5.19</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J199" s="2" t="inlineStr"/>
     </row>
@@ -7533,7 +7533,7 @@
         <v>4.92</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J200" s="2" t="inlineStr"/>
     </row>
@@ -7569,7 +7569,7 @@
         <v>6.49</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J201" s="2" t="inlineStr"/>
     </row>
@@ -7605,7 +7605,7 @@
         <v>6.91</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J202" s="2" t="inlineStr"/>
     </row>
@@ -7641,7 +7641,7 @@
         <v>7.23</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J203" s="2" t="inlineStr"/>
     </row>
@@ -7677,7 +7677,7 @@
         <v>14.98</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J204" s="2" t="inlineStr"/>
     </row>
@@ -7713,7 +7713,7 @@
         <v>37.75</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J205" s="2" t="inlineStr"/>
     </row>
@@ -7749,7 +7749,7 @@
         <v>20.97</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J206" s="2" t="inlineStr"/>
     </row>
@@ -7785,7 +7785,7 @@
         <v>12.38</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J207" s="2" t="inlineStr"/>
     </row>
@@ -7821,7 +7821,7 @@
         <v>10.21</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J208" s="2" t="inlineStr"/>
     </row>
@@ -7857,7 +7857,7 @@
         <v>11.85</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J209" s="2" t="inlineStr"/>
     </row>
@@ -7893,7 +7893,7 @@
         <v>14.13</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J210" s="2" t="inlineStr"/>
     </row>
@@ -7929,7 +7929,7 @@
         <v>17.98</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J211" s="2" t="inlineStr"/>
     </row>
@@ -7961,7 +7961,7 @@
         <v>6.65</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J212" s="2" t="inlineStr"/>
     </row>
@@ -7993,7 +7993,7 @@
         <v>5.57</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J213" s="2" t="inlineStr"/>
     </row>
@@ -8029,7 +8029,7 @@
         <v>6.32</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J214" s="2" t="inlineStr"/>
     </row>
@@ -8065,7 +8065,7 @@
         <v>5.4</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J215" s="2" t="inlineStr"/>
     </row>
@@ -8101,7 +8101,7 @@
         <v>10.86</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J216" s="2" t="inlineStr"/>
     </row>
@@ -8137,7 +8137,7 @@
         <v>41.94</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J217" s="2" t="inlineStr"/>
     </row>
@@ -8173,7 +8173,7 @@
         <v>3.14</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J218" s="2" t="inlineStr"/>
     </row>
@@ -8209,7 +8209,7 @@
         <v>4.35</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J219" s="2" t="inlineStr"/>
     </row>
@@ -8241,7 +8241,7 @@
         <v>1705.13</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J220" s="2" t="inlineStr"/>
     </row>
@@ -8277,7 +8277,7 @@
         <v>12.82</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J221" s="2" t="inlineStr"/>
     </row>
@@ -8309,7 +8309,7 @@
         <v>56.84</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J222" s="2" t="inlineStr"/>
     </row>
@@ -8345,7 +8345,7 @@
         <v>31.58</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J223" s="2" t="inlineStr"/>
     </row>
@@ -8381,7 +8381,7 @@
         <v>32.79</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J224" s="2" t="inlineStr"/>
     </row>
@@ -8417,7 +8417,7 @@
         <v>54.13</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J225" s="2" t="inlineStr"/>
     </row>
@@ -8453,7 +8453,7 @@
         <v>28.9</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J226" s="2" t="inlineStr"/>
     </row>
@@ -8489,7 +8489,7 @@
         <v>21.86</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J227" s="2" t="inlineStr"/>
     </row>
@@ -8525,7 +8525,7 @@
         <v>6.45</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J228" s="2" t="inlineStr"/>
     </row>
@@ -8561,7 +8561,7 @@
         <v>341</v>
       </c>
       <c r="I229" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J229" s="2" t="inlineStr"/>
     </row>
@@ -8593,7 +8593,7 @@
         <v>568.33</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J230" s="2" t="inlineStr"/>
     </row>
@@ -8625,7 +8625,7 @@
         <v>1705</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J231" s="2" t="inlineStr"/>
     </row>
@@ -8661,7 +8661,7 @@
         <v>13.41</v>
       </c>
       <c r="I232" s="2" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J232" s="2" t="inlineStr"/>
     </row>
@@ -8697,7 +8697,7 @@
         <v>6.25</v>
       </c>
       <c r="I233" s="2" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J233" s="2" t="inlineStr"/>
     </row>
@@ -8733,7 +8733,7 @@
         <v>5.33</v>
       </c>
       <c r="I234" s="2" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J234" s="2" t="inlineStr"/>
     </row>
@@ -8769,7 +8769,7 @@
         <v>5.96</v>
       </c>
       <c r="I235" s="2" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J235" s="2" t="inlineStr"/>
     </row>
@@ -8805,7 +8805,7 @@
         <v>13.92</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J236" s="2" t="inlineStr"/>
     </row>
@@ -8841,7 +8841,7 @@
         <v>3.74</v>
       </c>
       <c r="I237" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J237" s="2" t="inlineStr"/>
     </row>
@@ -8877,7 +8877,7 @@
         <v>5.06</v>
       </c>
       <c r="I238" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J238" s="2" t="inlineStr"/>
     </row>
@@ -8909,7 +8909,7 @@
         <v>735</v>
       </c>
       <c r="I239" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J239" s="2" t="inlineStr"/>
     </row>
@@ -8945,7 +8945,7 @@
         <v>16.28</v>
       </c>
       <c r="I240" s="2" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J240" s="2" t="inlineStr"/>
     </row>
@@ -8977,7 +8977,7 @@
         <v>8.01</v>
       </c>
       <c r="I241" s="2" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J241" s="2" t="inlineStr"/>
     </row>
@@ -9009,7 +9009,7 @@
         <v>13.56</v>
       </c>
       <c r="I242" s="2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J242" s="2" t="inlineStr"/>
     </row>
@@ -9045,7 +9045,7 @@
         <v>14.65</v>
       </c>
       <c r="I243" s="2" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J243" s="2" t="inlineStr"/>
     </row>
@@ -9081,7 +9081,7 @@
         <v>25.26</v>
       </c>
       <c r="I244" s="2" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J244" s="2" t="inlineStr"/>
     </row>
@@ -9117,7 +9117,7 @@
         <v>33.3</v>
       </c>
       <c r="I245" s="2" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J245" s="2" t="inlineStr"/>
     </row>
@@ -9149,7 +9149,7 @@
         <v>5.47</v>
       </c>
       <c r="I246" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J246" s="2" t="inlineStr"/>
     </row>
@@ -9181,7 +9181,7 @@
         <v>6.91</v>
       </c>
       <c r="I247" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J247" s="2" t="inlineStr"/>
     </row>
@@ -9217,7 +9217,7 @@
         <v>5.69</v>
       </c>
       <c r="I248" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J248" s="2" t="inlineStr"/>
     </row>
@@ -9249,7 +9249,7 @@
         <v>3.94</v>
       </c>
       <c r="I249" s="2" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J249" s="2" t="inlineStr"/>
     </row>
@@ -9281,7 +9281,7 @@
         <v>2.74</v>
       </c>
       <c r="I250" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J250" s="2" t="inlineStr"/>
     </row>
@@ -9317,7 +9317,7 @@
         <v>2.56</v>
       </c>
       <c r="I251" s="2" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J251" s="2" t="inlineStr"/>
     </row>
@@ -9353,7 +9353,7 @@
         <v>2.8</v>
       </c>
       <c r="I252" s="2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J252" s="2" t="inlineStr"/>
     </row>
@@ -9389,7 +9389,7 @@
         <v>6.74</v>
       </c>
       <c r="I253" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J253" s="2" t="inlineStr"/>
     </row>
@@ -9425,7 +9425,7 @@
         <v>3.7</v>
       </c>
       <c r="I254" s="2" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J254" s="2" t="inlineStr"/>
     </row>
@@ -9461,7 +9461,7 @@
         <v>11.49</v>
       </c>
       <c r="I255" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J255" s="2" t="inlineStr"/>
     </row>
@@ -9497,7 +9497,7 @@
         <v>7.46</v>
       </c>
       <c r="I256" s="2" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J256" s="2" t="inlineStr"/>
     </row>
@@ -9533,7 +9533,7 @@
         <v>28.08</v>
       </c>
       <c r="I257" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J257" s="2" t="inlineStr"/>
     </row>
@@ -9569,7 +9569,7 @@
         <v>13.07</v>
       </c>
       <c r="I258" s="2" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J258" s="2" t="inlineStr"/>
     </row>
@@ -9605,7 +9605,7 @@
         <v>11.66</v>
       </c>
       <c r="I259" s="2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J259" s="2" t="inlineStr"/>
     </row>
@@ -9641,7 +9641,7 @@
         <v>6.61</v>
       </c>
       <c r="I260" s="2" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J260" s="2" t="inlineStr"/>
     </row>
@@ -9677,7 +9677,7 @@
         <v>3.09</v>
       </c>
       <c r="I261" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J261" s="2" t="inlineStr"/>
     </row>
@@ -9713,7 +9713,7 @@
         <v>3.35</v>
       </c>
       <c r="I262" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J262" s="2" t="inlineStr"/>
     </row>
@@ -9749,7 +9749,7 @@
         <v>35.84</v>
       </c>
       <c r="I263" s="2" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J263" s="2" t="inlineStr"/>
     </row>
@@ -9785,7 +9785,7 @@
         <v>13.59</v>
       </c>
       <c r="I264" s="2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J264" s="2" t="inlineStr"/>
     </row>
@@ -9817,7 +9817,7 @@
         <v>523.84</v>
       </c>
       <c r="I265" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J265" s="2" t="inlineStr"/>
     </row>
@@ -9853,7 +9853,7 @@
         <v>16.06</v>
       </c>
       <c r="I266" s="2" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J266" s="2" t="inlineStr"/>
     </row>
@@ -9885,7 +9885,7 @@
         <v>12.46</v>
       </c>
       <c r="I267" s="2" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J267" s="2" t="inlineStr"/>
     </row>
@@ -9921,7 +9921,7 @@
         <v>23.36</v>
       </c>
       <c r="I268" s="2" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J268" s="2" t="inlineStr"/>
     </row>
@@ -9957,7 +9957,7 @@
         <v>4.3</v>
       </c>
       <c r="I269" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J269" s="2" t="inlineStr"/>
     </row>
@@ -9993,7 +9993,7 @@
         <v>5.84</v>
       </c>
       <c r="I270" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J270" s="2" t="inlineStr"/>
     </row>
@@ -10029,7 +10029,7 @@
         <v>1.84</v>
       </c>
       <c r="I271" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J271" s="2" t="inlineStr"/>
     </row>
@@ -10065,7 +10065,7 @@
         <v>1.97</v>
       </c>
       <c r="I272" s="2" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J272" s="2" t="inlineStr"/>
     </row>
@@ -10101,7 +10101,7 @@
         <v>8.81</v>
       </c>
       <c r="I273" s="2" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J273" s="2" t="inlineStr"/>
     </row>
@@ -10137,7 +10137,7 @@
         <v>7.52</v>
       </c>
       <c r="I274" s="2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J274" s="2" t="inlineStr"/>
     </row>
@@ -10173,7 +10173,7 @@
         <v>6.41</v>
       </c>
       <c r="I275" s="2" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J275" s="2" t="inlineStr"/>
     </row>
@@ -10209,7 +10209,7 @@
         <v>24.58</v>
       </c>
       <c r="I276" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J276" s="2" t="inlineStr"/>
     </row>
@@ -10245,7 +10245,7 @@
         <v>16.86</v>
       </c>
       <c r="I277" s="2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J277" s="2" t="inlineStr"/>
     </row>
@@ -10281,7 +10281,7 @@
         <v>4.99</v>
       </c>
       <c r="I278" s="2" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J278" s="2" t="inlineStr"/>
     </row>
@@ -10317,7 +10317,7 @@
         <v>2.83</v>
       </c>
       <c r="I279" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J279" s="2" t="inlineStr"/>
     </row>
@@ -10353,7 +10353,7 @@
         <v>3.16</v>
       </c>
       <c r="I280" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J280" s="2" t="inlineStr"/>
     </row>
@@ -10385,7 +10385,7 @@
         <v>32.51</v>
       </c>
       <c r="I281" s="2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J281" s="2" t="inlineStr"/>
     </row>
@@ -10421,7 +10421,7 @@
         <v>17.67</v>
       </c>
       <c r="I282" s="2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J282" s="2" t="inlineStr"/>
     </row>
@@ -10457,7 +10457,7 @@
         <v>23.9</v>
       </c>
       <c r="I283" s="2" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J283" s="2" t="inlineStr"/>
     </row>
@@ -10493,7 +10493,7 @@
         <v>5</v>
       </c>
       <c r="I284" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J284" s="2" t="inlineStr"/>
     </row>
@@ -10529,7 +10529,7 @@
         <v>7.02</v>
       </c>
       <c r="I285" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J285" s="2" t="inlineStr"/>
     </row>
@@ -10565,7 +10565,7 @@
         <v>6.79</v>
       </c>
       <c r="I286" s="2" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J286" s="2" t="inlineStr"/>
     </row>
@@ -10601,7 +10601,7 @@
         <v>12.02</v>
       </c>
       <c r="I287" s="2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J287" s="2" t="inlineStr"/>
     </row>
@@ -10637,7 +10637,7 @@
         <v>9.57</v>
       </c>
       <c r="I288" s="2" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J288" s="2" t="inlineStr"/>
     </row>
@@ -10673,7 +10673,7 @@
         <v>13.74</v>
       </c>
       <c r="I289" s="2" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J289" s="2" t="inlineStr"/>
     </row>
@@ -10705,7 +10705,7 @@
         <v>6.7</v>
       </c>
       <c r="I290" s="2" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J290" s="2" t="inlineStr"/>
     </row>
@@ -10741,7 +10741,7 @@
         <v>11.28</v>
       </c>
       <c r="I291" s="2" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J291" s="2" t="inlineStr"/>
     </row>
@@ -10777,7 +10777,7 @@
         <v>24.72</v>
       </c>
       <c r="I292" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J292" s="2" t="inlineStr"/>
     </row>
@@ -10813,7 +10813,7 @@
         <v>16.07</v>
       </c>
       <c r="I293" s="2" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J293" s="2" t="inlineStr"/>
     </row>
@@ -10849,7 +10849,7 @@
         <v>8.27</v>
       </c>
       <c r="I294" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J294" s="2" t="inlineStr"/>
     </row>
@@ -10885,7 +10885,7 @@
         <v>11.24</v>
       </c>
       <c r="I295" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J295" s="2" t="inlineStr"/>
     </row>
@@ -10921,7 +10921,7 @@
         <v>17.36</v>
       </c>
       <c r="I296" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J296" s="2" t="inlineStr"/>
     </row>
@@ -10957,7 +10957,7 @@
         <v>6.59</v>
       </c>
       <c r="I297" s="2" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J297" s="2" t="inlineStr"/>
     </row>
@@ -10989,7 +10989,7 @@
         <v>5.44</v>
       </c>
       <c r="I298" s="2" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J298" s="2" t="inlineStr"/>
     </row>
@@ -11025,7 +11025,7 @@
         <v>3.79</v>
       </c>
       <c r="I299" s="2" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J299" s="2" t="inlineStr"/>
     </row>
@@ -11061,7 +11061,7 @@
         <v>8.42</v>
       </c>
       <c r="I300" s="2" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J300" s="2" t="inlineStr"/>
     </row>
@@ -11097,7 +11097,7 @@
         <v>27.74</v>
       </c>
       <c r="I301" s="2" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J301" s="2" t="inlineStr"/>
     </row>
@@ -11133,7 +11133,7 @@
         <v>30.75</v>
       </c>
       <c r="I302" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J302" s="2" t="inlineStr"/>
     </row>
@@ -11169,7 +11169,7 @@
         <v>11.99</v>
       </c>
       <c r="I303" s="2" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J303" s="2" t="inlineStr"/>
     </row>
@@ -11205,7 +11205,7 @@
         <v>56.59</v>
       </c>
       <c r="I304" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J304" s="2" t="inlineStr"/>
     </row>
@@ -11241,7 +11241,7 @@
         <v>14.15</v>
       </c>
       <c r="I305" s="2" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J305" s="2" t="inlineStr"/>
     </row>
@@ -11277,7 +11277,7 @@
         <v>34.5</v>
       </c>
       <c r="I306" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J306" s="2" t="inlineStr"/>
     </row>
@@ -11313,7 +11313,7 @@
         <v>18.61</v>
       </c>
       <c r="I307" s="2" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J307" s="2" t="inlineStr"/>
     </row>
@@ -11349,7 +11349,7 @@
         <v>5.66</v>
       </c>
       <c r="I308" s="2" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J308" s="2" t="inlineStr"/>
     </row>
@@ -11385,7 +11385,7 @@
         <v>15.72</v>
       </c>
       <c r="I309" s="2" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J309" s="2" t="inlineStr"/>
     </row>
@@ -11421,7 +11421,7 @@
         <v>7.72</v>
       </c>
       <c r="I310" s="2" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J310" s="2" t="inlineStr"/>
     </row>
@@ -11457,7 +11457,7 @@
         <v>19.86</v>
       </c>
       <c r="I311" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J311" s="2" t="inlineStr"/>
     </row>
@@ -11493,7 +11493,7 @@
         <v>13.56</v>
       </c>
       <c r="I312" s="2" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J312" s="2" t="inlineStr"/>
     </row>
@@ -11529,7 +11529,7 @@
         <v>10.3</v>
       </c>
       <c r="I313" s="2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J313" s="2" t="inlineStr"/>
     </row>
@@ -11565,7 +11565,7 @@
         <v>17.16</v>
       </c>
       <c r="I314" s="2" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J314" s="2" t="inlineStr"/>
     </row>
@@ -11601,7 +11601,7 @@
         <v>6.47</v>
       </c>
       <c r="I315" s="2" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J315" s="2" t="inlineStr"/>
     </row>
@@ -11637,7 +11637,7 @@
         <v>5.52</v>
       </c>
       <c r="I316" s="2" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J316" s="2" t="inlineStr"/>
     </row>
@@ -11673,7 +11673,7 @@
         <v>5.25</v>
       </c>
       <c r="I317" s="2" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J317" s="2" t="inlineStr"/>
     </row>
@@ -11709,7 +11709,7 @@
         <v>11.44</v>
       </c>
       <c r="I318" s="2" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J318" s="2" t="inlineStr"/>
     </row>
@@ -11745,7 +11745,7 @@
         <v>10.53</v>
       </c>
       <c r="I319" s="2" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J319" s="2" t="inlineStr"/>
     </row>
@@ -11781,7 +11781,7 @@
         <v>16.95</v>
       </c>
       <c r="I320" s="2" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J320" s="2" t="inlineStr"/>
     </row>
@@ -11813,7 +11813,7 @@
         <v>3.28</v>
       </c>
       <c r="I321" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J321" s="2" t="inlineStr"/>
     </row>
@@ -11849,7 +11849,7 @@
         <v>4.06</v>
       </c>
       <c r="I322" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J322" s="2" t="inlineStr"/>
     </row>
@@ -11881,7 +11881,7 @@
         <v>42.23</v>
       </c>
       <c r="I323" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J323" s="2" t="inlineStr"/>
     </row>
@@ -11913,7 +11913,7 @@
         <v>24.13</v>
       </c>
       <c r="I324" s="2" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J324" s="2" t="inlineStr"/>
     </row>
@@ -11949,7 +11949,7 @@
         <v>7.57</v>
       </c>
       <c r="I325" s="2" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J325" s="2" t="inlineStr"/>
     </row>
@@ -11985,7 +11985,7 @@
         <v>11.5</v>
       </c>
       <c r="I326" s="2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J326" s="2" t="inlineStr"/>
     </row>
@@ -12017,7 +12017,7 @@
         <v>14.61</v>
       </c>
       <c r="I327" s="2" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J327" s="2" t="inlineStr"/>
     </row>
@@ -12053,7 +12053,7 @@
         <v>3.47</v>
       </c>
       <c r="I328" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J328" s="2" t="inlineStr"/>
     </row>
@@ -12089,7 +12089,7 @@
         <v>5.32</v>
       </c>
       <c r="I329" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J329" s="2" t="inlineStr"/>
     </row>
